--- a/data/auto_buyer_picks.xlsx
+++ b/data/auto_buyer_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP17" headerRowCount="1">
-  <autoFilter ref="A1:DP17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP54" headerRowCount="1">
+  <autoFilter ref="A1:DP54"/>
   <tableColumns count="120">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -779,19 +779,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$54)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$54,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$54,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")/(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$54)/SUM('Picks'!$BX$2:$BX$54),0)</f>
         <v/>
       </c>
     </row>
@@ -859,19 +859,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$54)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$54,"&lt;&gt;",'Picks'!$AB$2:$AB$54),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$54,'Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -942,11 +942,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -957,15 +957,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -973,11 +973,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -988,15 +988,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1004,11 +1004,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DP17"/>
+  <dimension ref="A1:DP54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>401816735</t>
+          <t>tsc-mlb-kc-cle-2026-08-30-7pt5</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1810,9 +1810,7 @@
           <t>over</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1830,15 +1828,11 @@
       <c r="O2" s="28" t="n">
         <v>0.5246</v>
       </c>
-      <c r="P2" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
         <v>0.0392</v>
       </c>
-      <c r="R2" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R2" s="26" t="n"/>
       <c r="S2" s="29" t="n">
         <v>1</v>
       </c>
@@ -1849,32 +1843,38 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>11</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB2" s="28" t="n"/>
       <c r="AC2" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="24" t="n"/>
+        <v>1.08</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67Z6DT08KDG (1.0 sh @ $0.48) on tsc-mlb-kc-cle-2026-08-30-7pt5 (long)</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67Z6DT08KDG on tsc-mlb-kc-cle-2026-08-30-7pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="n"/>
       <c r="AG2" s="24" t="n"/>
       <c r="AH2" s="24" t="n"/>
       <c r="AI2" s="31" t="n"/>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>401816738</t>
+          <t>tsc-mlb-sd-tb-2026-08-30-7pt5</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -2024,9 +2024,7 @@
           <t>over</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2044,15 +2042,11 @@
       <c r="O3" s="28" t="n">
         <v>0.5128</v>
       </c>
-      <c r="P3" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
         <v>0.0477</v>
       </c>
-      <c r="R3" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R3" s="26" t="n"/>
       <c r="S3" s="29" t="n">
         <v>1</v>
       </c>
@@ -2063,32 +2057,38 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB3" s="28" t="n"/>
       <c r="AC3" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="24" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67YHJR2YKDF (1.0 sh @ $0.47) on tsc-mlb-sd-tb-2026-08-30-7pt5 (long)</t>
-        </is>
-      </c>
-      <c r="AF3" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67YHJR2YKDF on tsc-mlb-sd-tb-2026-08-30-7pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="n"/>
       <c r="AG3" s="24" t="n"/>
       <c r="AH3" s="24" t="n"/>
       <c r="AI3" s="31" t="n"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>401816742</t>
+          <t>tsc-mlb-pit-stl-2026-08-30-8pt5</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2238,9 +2238,7 @@
           <t>over</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2258,15 +2256,11 @@
       <c r="O4" s="28" t="n">
         <v>0.5098</v>
       </c>
-      <c r="P4" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
         <v>0.0654</v>
       </c>
-      <c r="R4" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R4" s="26" t="n"/>
       <c r="S4" s="29" t="n">
         <v>1.25</v>
       </c>
@@ -2277,32 +2271,38 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB4" s="28" t="n"/>
       <c r="AC4" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="24" t="n"/>
+        <v>1.53</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:29:23.578191Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67YHJ9BAKDN (1.0 sh @ $0.45) on tsc-mlb-pit-stl-2026-08-30-8pt5 (long)</t>
-        </is>
-      </c>
-      <c r="AF4" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67YHJ9BAKDN on tsc-mlb-pit-stl-2026-08-30-8pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="n"/>
       <c r="AG4" s="24" t="n"/>
       <c r="AH4" s="24" t="n"/>
       <c r="AI4" s="31" t="n"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182593</t>
+          <t>aec-wta-renzar-poliat-2026-08-30</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2470,15 +2470,11 @@
       <c r="O5" s="28" t="n">
         <v>0.5933</v>
       </c>
-      <c r="P5" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
         <v>0.1325</v>
       </c>
-      <c r="R5" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" s="26" t="n"/>
       <c r="S5" s="29" t="n">
         <v>1.5</v>
       </c>
@@ -2489,32 +2485,36 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X5" s="26" t="n"/>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="24" t="n"/>
+        <v>1.83</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZBV5R6KDK (1.0 sh @ $0.45) on aec-wta-renzar-poliat-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF5" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZBV5R6KDK on aec-wta-renzar-poliat-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="n"/>
       <c r="AG5" s="24" t="n"/>
       <c r="AH5" s="24" t="n"/>
       <c r="AI5" s="31" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182634</t>
+          <t>aec-wta-lucste-dayyas-2026-08-30</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2682,15 +2682,11 @@
       <c r="O6" s="28" t="n">
         <v>0.5391</v>
       </c>
-      <c r="P6" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
         <v>0.1189</v>
       </c>
-      <c r="R6" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R6" s="26" t="n"/>
       <c r="S6" s="29" t="n">
         <v>1.5</v>
       </c>
@@ -2701,32 +2697,36 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB6" s="28" t="n"/>
       <c r="AC6" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="24" t="n"/>
+        <v>2.07</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67YX9ESEKDE (1.0 sh @ $0.42) on aec-wta-lucste-dayyas-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF6" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67YX9ESEKDE on aec-wta-lucste-dayyas-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="n"/>
       <c r="AG6" s="24" t="n"/>
       <c r="AH6" s="24" t="n"/>
       <c r="AI6" s="31" t="n"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182646</t>
+          <t>aec-wta-carlee-katbou-2026-08-30</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2894,15 +2894,11 @@
       <c r="O7" s="28" t="n">
         <v>0.6772</v>
       </c>
-      <c r="P7" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
         <v>0.0974</v>
       </c>
-      <c r="R7" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R7" s="26" t="n"/>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
       </c>
@@ -2913,32 +2909,36 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X7" s="26" t="n"/>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB7" s="28" t="n"/>
       <c r="AC7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="24" t="n"/>
+        <v>0.91</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67XS5EYPKDD (1.0 sh @ $0.58) on aec-wta-carlee-katbou-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF7" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67XS5EYPKDD on aec-wta-carlee-katbou-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="n"/>
       <c r="AG7" s="24" t="n"/>
       <c r="AH7" s="24" t="n"/>
       <c r="AI7" s="31" t="n"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182594</t>
+          <t>aec-wta-hanvan-karpli-2026-08-30</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3106,15 +3106,11 @@
       <c r="O8" s="28" t="n">
         <v>0.5505</v>
       </c>
-      <c r="P8" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
         <v>0.0505</v>
       </c>
-      <c r="R8" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" s="26" t="n"/>
       <c r="S8" s="29" t="n">
         <v>1</v>
       </c>
@@ -3125,32 +3121,36 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X8" s="26" t="n"/>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB8" s="28" t="n"/>
       <c r="AC8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="24" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:30:23.932460Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZBV63GKDK (1.0 sh @ $0.50) on aec-wta-hanvan-karpli-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZBV63GKDK on aec-wta-hanvan-karpli-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="n"/>
       <c r="AG8" s="24" t="n"/>
       <c r="AH8" s="24" t="n"/>
       <c r="AI8" s="31" t="n"/>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182758</t>
+          <t>aec-atp-kammaj-hammed-2026-08-30</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3318,15 +3318,11 @@
       <c r="O9" s="28" t="n">
         <v>0.5909</v>
       </c>
-      <c r="P9" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
         <v>0.0413</v>
       </c>
-      <c r="R9" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R9" s="26" t="n"/>
       <c r="S9" s="29" t="n">
         <v>1</v>
       </c>
@@ -3337,32 +3333,36 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB9" s="28" t="n"/>
       <c r="AC9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="24" t="n"/>
+        <v>0.82</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:13:23.815760Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZDSFV0KDM (1.0 sh @ $0.55) on aec-atp-kammaj-hammed-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZDSFV0KDM on aec-atp-kammaj-hammed-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="n"/>
       <c r="AG9" s="24" t="n"/>
       <c r="AH9" s="24" t="n"/>
       <c r="AI9" s="31" t="n"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182678</t>
+          <t>aec-atp-lucass-camnor-2026-08-30</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3530,15 +3530,11 @@
       <c r="O10" s="28" t="n">
         <v>0.7139</v>
       </c>
-      <c r="P10" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
         <v>0.0439</v>
       </c>
-      <c r="R10" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R10" s="26" t="n"/>
       <c r="S10" s="29" t="n">
         <v>1</v>
       </c>
@@ -3549,32 +3545,36 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB10" s="28" t="n"/>
       <c r="AC10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="24" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67Z38H1EKDC (1.0 sh @ $0.67) on aec-atp-lucass-camnor-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67Z38H1EKDC on aec-atp-lucass-camnor-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="n"/>
       <c r="AG10" s="24" t="n"/>
       <c r="AH10" s="24" t="n"/>
       <c r="AI10" s="31" t="n"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182657</t>
+          <t>aec-atp-tobsam-tommac-2026-08-30</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -3742,15 +3742,11 @@
       <c r="O11" s="28" t="n">
         <v>0.5571</v>
       </c>
-      <c r="P11" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
         <v>0.1166</v>
       </c>
-      <c r="R11" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R11" s="26" t="n"/>
       <c r="S11" s="29" t="n">
         <v>1.5</v>
       </c>
@@ -3761,32 +3757,36 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB11" s="28" t="n"/>
       <c r="AC11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="24" t="n"/>
+        <v>-1.5</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZDSG88KDM (1.0 sh @ $0.44) on aec-atp-tobsam-tommac-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZDSG88KDM on aec-atp-tobsam-tommac-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="n"/>
       <c r="AG11" s="24" t="n"/>
       <c r="AH11" s="24" t="n"/>
       <c r="AI11" s="31" t="n"/>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182774</t>
+          <t>aec-atp-jaumun-teratm-2026-08-30</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -3954,15 +3954,11 @@
       <c r="O12" s="28" t="n">
         <v>0.5177</v>
       </c>
-      <c r="P12" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
         <v>0.1473</v>
       </c>
-      <c r="R12" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R12" s="26" t="n"/>
       <c r="S12" s="29" t="n">
         <v>1.75</v>
       </c>
@@ -3973,32 +3969,36 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB12" s="28" t="n"/>
       <c r="AC12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="24" t="n"/>
+        <v>2.86</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67YHJAPJKDN (1.0 sh @ $0.38) on aec-atp-jaumun-teratm-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67YHJAPJKDN on aec-atp-jaumun-teratm-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="n"/>
       <c r="AG12" s="24" t="n"/>
       <c r="AH12" s="24" t="n"/>
       <c r="AI12" s="31" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182665</t>
+          <t>aec-atp-jaifar-jenbro-2026-08-30</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4166,15 +4166,11 @@
       <c r="O13" s="28" t="n">
         <v>0.611</v>
       </c>
-      <c r="P13" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
         <v>0.1302</v>
       </c>
-      <c r="R13" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R13" s="26" t="n"/>
       <c r="S13" s="29" t="n">
         <v>1.5</v>
       </c>
@@ -4185,32 +4181,36 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB13" s="28" t="n"/>
       <c r="AC13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="24" t="n"/>
+        <v>1.56</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZDSGFTKDM (1.0 sh @ $0.49) on aec-atp-jaifar-jenbro-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZDSGFTKDM on aec-atp-jaifar-jenbro-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="n"/>
       <c r="AG13" s="24" t="n"/>
       <c r="AH13" s="24" t="n"/>
       <c r="AI13" s="31" t="n"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>401857186</t>
+          <t>aec-wnba-min-atl-2026-08-30</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4378,15 +4378,11 @@
       <c r="O14" s="28" t="n">
         <v>0.6181</v>
       </c>
-      <c r="P14" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
         <v>0.0473</v>
       </c>
-      <c r="R14" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R14" s="26" t="n"/>
       <c r="S14" s="29" t="n">
         <v>1</v>
       </c>
@@ -4397,32 +4393,38 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>89</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB14" s="28" t="n"/>
       <c r="AC14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="24" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:29:23.578191Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C67ZBV73MKDK (1.0 sh @ $0.57) on aec-wnba-min-atl-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF14" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C67ZBV73MKDK on aec-wnba-min-atl-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="n"/>
       <c r="AG14" s="24" t="n"/>
       <c r="AH14" s="24" t="n"/>
       <c r="AI14" s="31" t="n"/>
@@ -4544,7 +4546,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>401816746</t>
+          <t>tsc-mlb-phi-laa-2026-08-30-8pt5</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -4572,9 +4574,7 @@
           <t>over</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4592,15 +4592,11 @@
       <c r="O15" s="28" t="n">
         <v>0.5269</v>
       </c>
-      <c r="P15" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
         <v>0.0569</v>
       </c>
-      <c r="R15" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R15" s="26" t="n"/>
       <c r="S15" s="29" t="n">
         <v>1</v>
       </c>
@@ -4611,32 +4607,38 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB15" s="28" t="n"/>
       <c r="AC15" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="24" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6820XSTTKDH (1.0 sh @ $0.47) on tsc-mlb-phi-laa-2026-08-30-8pt5 (long)</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C6820XSTTKDH on tsc-mlb-phi-laa-2026-08-30-8pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="n"/>
       <c r="AG15" s="24" t="n"/>
       <c r="AH15" s="24" t="n"/>
       <c r="AI15" s="31" t="n"/>
@@ -4758,7 +4760,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182596</t>
+          <t>aec-wta-taypre-alypar-2026-08-30</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -4804,15 +4806,11 @@
       <c r="O16" s="28" t="n">
         <v>0.6473</v>
       </c>
-      <c r="P16" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
         <v>0.1373</v>
       </c>
-      <c r="R16" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R16" s="26" t="n"/>
       <c r="S16" s="29" t="n">
         <v>1.5</v>
       </c>
@@ -4823,32 +4821,36 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB16" s="28" t="n"/>
       <c r="AC16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="24" t="n"/>
+        <v>-1.5</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C692W60FGKDN (1.0 sh @ $0.51) on aec-wta-taypre-alypar-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C692W60FGKDN on aec-wta-taypre-alypar-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="n"/>
       <c r="AG16" s="24" t="n"/>
       <c r="AH16" s="24" t="n"/>
       <c r="AI16" s="31" t="n"/>
@@ -4970,7 +4972,7 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>189-2026:182621</t>
+          <t>aec-wta-kimbir-petmar-2026-08-30</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5016,15 +5018,11 @@
       <c r="O17" s="28" t="n">
         <v>0.5659</v>
       </c>
-      <c r="P17" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
         <v>0.0559</v>
       </c>
-      <c r="R17" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R17" s="26" t="n"/>
       <c r="S17" s="29" t="n">
         <v>1</v>
       </c>
@@ -5035,32 +5033,36 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB17" s="28" t="n"/>
       <c r="AC17" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="24" t="n"/>
+        <v>0.96</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:41:38.707356Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C692JEFHCKDF (1.0 sh @ $0.51) on aec-wta-kimbir-petmar-2026-08-30 (long)</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C692JEFHCKDF on aec-wta-kimbir-petmar-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="n"/>
       <c r="AG17" s="24" t="n"/>
       <c r="AH17" s="24" t="n"/>
       <c r="AI17" s="31" t="n"/>
@@ -5164,6 +5166,7698 @@
       <c r="DO17" s="24" t="n"/>
       <c r="DP17" s="24" t="n"/>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>31dd4e8b89f9429b</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:14:53.453516Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>aec-wnba-gsv-por-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.4926</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.7121</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="R18" s="26" t="n"/>
+      <c r="S18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:47:49.455874Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GTC588TKDK on aec-wnba-gsv-por-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="n"/>
+      <c r="AG18" s="24" t="n"/>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="n"/>
+      <c r="AL18" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="n"/>
+      <c r="AQ18" s="24" t="n"/>
+      <c r="AR18" s="24" t="n"/>
+      <c r="AS18" s="24" t="n"/>
+      <c r="AT18" s="24" t="n"/>
+      <c r="AU18" s="24" t="n"/>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="n"/>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="n"/>
+      <c r="BA18" s="24" t="n"/>
+      <c r="BB18" s="24" t="n"/>
+      <c r="BC18" s="24" t="n"/>
+      <c r="BD18" s="24" t="n"/>
+      <c r="BE18" s="24" t="n"/>
+      <c r="BF18" s="24" t="n"/>
+      <c r="BG18" s="24" t="n"/>
+      <c r="BH18" s="24" t="n"/>
+      <c r="BI18" s="24" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n"/>
+      <c r="BL18" s="27" t="n"/>
+      <c r="BM18" s="28" t="n"/>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
+      <c r="CT18" s="24" t="n"/>
+      <c r="CU18" s="24" t="n"/>
+      <c r="CV18" s="24" t="n"/>
+      <c r="CW18" s="24" t="n"/>
+      <c r="CX18" s="24" t="n"/>
+      <c r="CY18" s="24" t="n"/>
+      <c r="CZ18" s="24" t="n"/>
+      <c r="DA18" s="24" t="n"/>
+      <c r="DB18" s="24" t="n"/>
+      <c r="DC18" s="24" t="n"/>
+      <c r="DD18" s="24" t="n"/>
+      <c r="DE18" s="24" t="n"/>
+      <c r="DF18" s="24" t="n"/>
+      <c r="DG18" s="24" t="n"/>
+      <c r="DH18" s="24" t="n"/>
+      <c r="DI18" s="24" t="n"/>
+      <c r="DJ18" s="24" t="n"/>
+      <c r="DK18" s="24" t="n"/>
+      <c r="DL18" s="24" t="n"/>
+      <c r="DM18" s="24" t="n"/>
+      <c r="DN18" s="24" t="n"/>
+      <c r="DO18" s="24" t="n"/>
+      <c r="DP18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>5fddbdd2e6544bb6</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:14:53.453516Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T00:30Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-alebub-jjwol-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>J.J. Wolf</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Alexander Bublik</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.4484</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="R19" s="26" t="n"/>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:59:03.295568Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GTQAX2AKDH on aec-atp-alebub-jjwol-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="n"/>
+      <c r="AG19" s="24" t="n"/>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="n"/>
+      <c r="AL19" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="n"/>
+      <c r="AQ19" s="24" t="n"/>
+      <c r="AR19" s="24" t="n"/>
+      <c r="AS19" s="24" t="n"/>
+      <c r="AT19" s="24" t="n"/>
+      <c r="AU19" s="24" t="n"/>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="n"/>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="n"/>
+      <c r="BA19" s="24" t="n"/>
+      <c r="BB19" s="24" t="n"/>
+      <c r="BC19" s="24" t="n"/>
+      <c r="BD19" s="24" t="n"/>
+      <c r="BE19" s="24" t="n"/>
+      <c r="BF19" s="24" t="n"/>
+      <c r="BG19" s="24" t="n"/>
+      <c r="BH19" s="24" t="n"/>
+      <c r="BI19" s="24" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n"/>
+      <c r="BL19" s="27" t="n"/>
+      <c r="BM19" s="28" t="n"/>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="n"/>
+      <c r="CT19" s="24" t="n"/>
+      <c r="CU19" s="24" t="n"/>
+      <c r="CV19" s="24" t="n"/>
+      <c r="CW19" s="24" t="n"/>
+      <c r="CX19" s="24" t="n"/>
+      <c r="CY19" s="24" t="n"/>
+      <c r="CZ19" s="24" t="n"/>
+      <c r="DA19" s="24" t="n"/>
+      <c r="DB19" s="24" t="n"/>
+      <c r="DC19" s="24" t="n"/>
+      <c r="DD19" s="24" t="n"/>
+      <c r="DE19" s="24" t="n"/>
+      <c r="DF19" s="24" t="n"/>
+      <c r="DG19" s="24" t="n"/>
+      <c r="DH19" s="24" t="n"/>
+      <c r="DI19" s="24" t="n"/>
+      <c r="DJ19" s="24" t="n"/>
+      <c r="DK19" s="24" t="n"/>
+      <c r="DL19" s="24" t="n"/>
+      <c r="DM19" s="24" t="n"/>
+      <c r="DN19" s="24" t="n"/>
+      <c r="DO19" s="24" t="n"/>
+      <c r="DP19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>a6060a3849e2447f</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-ts-furia-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>FURIA</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Spirit</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="R20" s="26" t="n"/>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:02:25.134027Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GXVJ778KDG on aec-cs2-ts-furia-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="n"/>
+      <c r="AG20" s="24" t="n"/>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="n"/>
+      <c r="AL20" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="n"/>
+      <c r="AQ20" s="24" t="n"/>
+      <c r="AR20" s="24" t="n"/>
+      <c r="AS20" s="24" t="n"/>
+      <c r="AT20" s="24" t="n"/>
+      <c r="AU20" s="24" t="n"/>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="n"/>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="n"/>
+      <c r="BA20" s="24" t="n"/>
+      <c r="BB20" s="24" t="n"/>
+      <c r="BC20" s="24" t="n"/>
+      <c r="BD20" s="24" t="n"/>
+      <c r="BE20" s="24" t="n"/>
+      <c r="BF20" s="24" t="n"/>
+      <c r="BG20" s="24" t="n"/>
+      <c r="BH20" s="24" t="n"/>
+      <c r="BI20" s="24" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n"/>
+      <c r="BL20" s="27" t="n"/>
+      <c r="BM20" s="28" t="n"/>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="n"/>
+      <c r="CT20" s="24" t="n"/>
+      <c r="CU20" s="24" t="n"/>
+      <c r="CV20" s="24" t="n"/>
+      <c r="CW20" s="24" t="n"/>
+      <c r="CX20" s="24" t="n"/>
+      <c r="CY20" s="24" t="n"/>
+      <c r="CZ20" s="24" t="n"/>
+      <c r="DA20" s="24" t="n"/>
+      <c r="DB20" s="24" t="n"/>
+      <c r="DC20" s="24" t="n"/>
+      <c r="DD20" s="24" t="n"/>
+      <c r="DE20" s="24" t="n"/>
+      <c r="DF20" s="24" t="n"/>
+      <c r="DG20" s="24" t="n"/>
+      <c r="DH20" s="24" t="n"/>
+      <c r="DI20" s="24" t="n"/>
+      <c r="DJ20" s="24" t="n"/>
+      <c r="DK20" s="24" t="n"/>
+      <c r="DL20" s="24" t="n"/>
+      <c r="DM20" s="24" t="n"/>
+      <c r="DN20" s="24" t="n"/>
+      <c r="DO20" s="24" t="n"/>
+      <c r="DP20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>2d250bfe28394dcd</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-pcific-atr-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="R21" s="26" t="n"/>
+      <c r="S21" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:02:34.026411Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GYB4MW4KDH on aec-cs2-pcific-atr-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="n"/>
+      <c r="AG21" s="24" t="n"/>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="n"/>
+      <c r="AL21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="n"/>
+      <c r="AQ21" s="24" t="n"/>
+      <c r="AR21" s="24" t="n"/>
+      <c r="AS21" s="24" t="n"/>
+      <c r="AT21" s="24" t="n"/>
+      <c r="AU21" s="24" t="n"/>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="n"/>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="n"/>
+      <c r="BA21" s="24" t="n"/>
+      <c r="BB21" s="24" t="n"/>
+      <c r="BC21" s="24" t="n"/>
+      <c r="BD21" s="24" t="n"/>
+      <c r="BE21" s="24" t="n"/>
+      <c r="BF21" s="24" t="n"/>
+      <c r="BG21" s="24" t="n"/>
+      <c r="BH21" s="24" t="n"/>
+      <c r="BI21" s="24" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n"/>
+      <c r="BL21" s="27" t="n"/>
+      <c r="BM21" s="28" t="n"/>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="n"/>
+      <c r="CT21" s="24" t="n"/>
+      <c r="CU21" s="24" t="n"/>
+      <c r="CV21" s="24" t="n"/>
+      <c r="CW21" s="24" t="n"/>
+      <c r="CX21" s="24" t="n"/>
+      <c r="CY21" s="24" t="n"/>
+      <c r="CZ21" s="24" t="n"/>
+      <c r="DA21" s="24" t="n"/>
+      <c r="DB21" s="24" t="n"/>
+      <c r="DC21" s="24" t="n"/>
+      <c r="DD21" s="24" t="n"/>
+      <c r="DE21" s="24" t="n"/>
+      <c r="DF21" s="24" t="n"/>
+      <c r="DG21" s="24" t="n"/>
+      <c r="DH21" s="24" t="n"/>
+      <c r="DI21" s="24" t="n"/>
+      <c r="DJ21" s="24" t="n"/>
+      <c r="DK21" s="24" t="n"/>
+      <c r="DL21" s="24" t="n"/>
+      <c r="DM21" s="24" t="n"/>
+      <c r="DN21" s="24" t="n"/>
+      <c r="DO21" s="24" t="n"/>
+      <c r="DP21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>43a1c1f036ca46ac</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-ezt-bw-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>ex-Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.9259</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.6874</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="R22" s="26" t="n"/>
+      <c r="S22" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:01:24.010499Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GXGZS7TKDC on aec-cs2-ezt-bw-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="n"/>
+      <c r="AG22" s="24" t="n"/>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="n"/>
+      <c r="AL22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="n"/>
+      <c r="AQ22" s="24" t="n"/>
+      <c r="AR22" s="24" t="n"/>
+      <c r="AS22" s="24" t="n"/>
+      <c r="AT22" s="24" t="n"/>
+      <c r="AU22" s="24" t="n"/>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="n"/>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="n"/>
+      <c r="BA22" s="24" t="n"/>
+      <c r="BB22" s="24" t="n"/>
+      <c r="BC22" s="24" t="n"/>
+      <c r="BD22" s="24" t="n"/>
+      <c r="BE22" s="24" t="n"/>
+      <c r="BF22" s="24" t="n"/>
+      <c r="BG22" s="24" t="n"/>
+      <c r="BH22" s="24" t="n"/>
+      <c r="BI22" s="24" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n"/>
+      <c r="BL22" s="27" t="n"/>
+      <c r="BM22" s="28" t="n"/>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="n"/>
+      <c r="CT22" s="24" t="n"/>
+      <c r="CU22" s="24" t="n"/>
+      <c r="CV22" s="24" t="n"/>
+      <c r="CW22" s="24" t="n"/>
+      <c r="CX22" s="24" t="n"/>
+      <c r="CY22" s="24" t="n"/>
+      <c r="CZ22" s="24" t="n"/>
+      <c r="DA22" s="24" t="n"/>
+      <c r="DB22" s="24" t="n"/>
+      <c r="DC22" s="24" t="n"/>
+      <c r="DD22" s="24" t="n"/>
+      <c r="DE22" s="24" t="n"/>
+      <c r="DF22" s="24" t="n"/>
+      <c r="DG22" s="24" t="n"/>
+      <c r="DH22" s="24" t="n"/>
+      <c r="DI22" s="24" t="n"/>
+      <c r="DJ22" s="24" t="n"/>
+      <c r="DK22" s="24" t="n"/>
+      <c r="DL22" s="24" t="n"/>
+      <c r="DM22" s="24" t="n"/>
+      <c r="DN22" s="24" t="n"/>
+      <c r="DO22" s="24" t="n"/>
+      <c r="DP22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>66aa5ccd50684177</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-shin-fxw7-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Fluxo W7M</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.5913</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="R23" s="26" t="n"/>
+      <c r="S23" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:01:24.010499Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GXP0Y34KDK on aec-cs2-shin-fxw7-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="n"/>
+      <c r="AG23" s="24" t="n"/>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="n"/>
+      <c r="AL23" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="n"/>
+      <c r="AQ23" s="24" t="n"/>
+      <c r="AR23" s="24" t="n"/>
+      <c r="AS23" s="24" t="n"/>
+      <c r="AT23" s="24" t="n"/>
+      <c r="AU23" s="24" t="n"/>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="n"/>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="n"/>
+      <c r="BA23" s="24" t="n"/>
+      <c r="BB23" s="24" t="n"/>
+      <c r="BC23" s="24" t="n"/>
+      <c r="BD23" s="24" t="n"/>
+      <c r="BE23" s="24" t="n"/>
+      <c r="BF23" s="24" t="n"/>
+      <c r="BG23" s="24" t="n"/>
+      <c r="BH23" s="24" t="n"/>
+      <c r="BI23" s="24" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n"/>
+      <c r="BL23" s="27" t="n"/>
+      <c r="BM23" s="28" t="n"/>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="n"/>
+      <c r="CT23" s="24" t="n"/>
+      <c r="CU23" s="24" t="n"/>
+      <c r="CV23" s="24" t="n"/>
+      <c r="CW23" s="24" t="n"/>
+      <c r="CX23" s="24" t="n"/>
+      <c r="CY23" s="24" t="n"/>
+      <c r="CZ23" s="24" t="n"/>
+      <c r="DA23" s="24" t="n"/>
+      <c r="DB23" s="24" t="n"/>
+      <c r="DC23" s="24" t="n"/>
+      <c r="DD23" s="24" t="n"/>
+      <c r="DE23" s="24" t="n"/>
+      <c r="DF23" s="24" t="n"/>
+      <c r="DG23" s="24" t="n"/>
+      <c r="DH23" s="24" t="n"/>
+      <c r="DI23" s="24" t="n"/>
+      <c r="DJ23" s="24" t="n"/>
+      <c r="DK23" s="24" t="n"/>
+      <c r="DL23" s="24" t="n"/>
+      <c r="DM23" s="24" t="n"/>
+      <c r="DN23" s="24" t="n"/>
+      <c r="DO23" s="24" t="n"/>
+      <c r="DP23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>251a40c2423d4eda</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-fnc-gx-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="R24" s="26" t="n"/>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:02:34.026411Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GXP0YCWKDK on aec-lol-fnc-gx-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="n"/>
+      <c r="AG24" s="24" t="n"/>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="n"/>
+      <c r="AL24" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="n"/>
+      <c r="AQ24" s="24" t="n"/>
+      <c r="AR24" s="24" t="n"/>
+      <c r="AS24" s="24" t="n"/>
+      <c r="AT24" s="24" t="n"/>
+      <c r="AU24" s="24" t="n"/>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="n"/>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="n"/>
+      <c r="BA24" s="24" t="n"/>
+      <c r="BB24" s="24" t="n"/>
+      <c r="BC24" s="24" t="n"/>
+      <c r="BD24" s="24" t="n"/>
+      <c r="BE24" s="24" t="n"/>
+      <c r="BF24" s="24" t="n"/>
+      <c r="BG24" s="24" t="n"/>
+      <c r="BH24" s="24" t="n"/>
+      <c r="BI24" s="24" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n"/>
+      <c r="BL24" s="27" t="n"/>
+      <c r="BM24" s="28" t="n"/>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="n"/>
+      <c r="CT24" s="24" t="n"/>
+      <c r="CU24" s="24" t="n"/>
+      <c r="CV24" s="24" t="n"/>
+      <c r="CW24" s="24" t="n"/>
+      <c r="CX24" s="24" t="n"/>
+      <c r="CY24" s="24" t="n"/>
+      <c r="CZ24" s="24" t="n"/>
+      <c r="DA24" s="24" t="n"/>
+      <c r="DB24" s="24" t="n"/>
+      <c r="DC24" s="24" t="n"/>
+      <c r="DD24" s="24" t="n"/>
+      <c r="DE24" s="24" t="n"/>
+      <c r="DF24" s="24" t="n"/>
+      <c r="DG24" s="24" t="n"/>
+      <c r="DH24" s="24" t="n"/>
+      <c r="DI24" s="24" t="n"/>
+      <c r="DJ24" s="24" t="n"/>
+      <c r="DK24" s="24" t="n"/>
+      <c r="DL24" s="24" t="n"/>
+      <c r="DM24" s="24" t="n"/>
+      <c r="DN24" s="24" t="n"/>
+      <c r="DO24" s="24" t="n"/>
+      <c r="DP24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>42a282ce16a14139</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:22:08.406596Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-ly-tl-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.5115</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="R25" s="26" t="n"/>
+      <c r="S25" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:01:24.010499Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6GYB4PFAKDH on aec-lol-ly-tl-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="n"/>
+      <c r="AG25" s="24" t="n"/>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="n"/>
+      <c r="AL25" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="n"/>
+      <c r="AQ25" s="24" t="n"/>
+      <c r="AR25" s="24" t="n"/>
+      <c r="AS25" s="24" t="n"/>
+      <c r="AT25" s="24" t="n"/>
+      <c r="AU25" s="24" t="n"/>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="n"/>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="n"/>
+      <c r="BA25" s="24" t="n"/>
+      <c r="BB25" s="24" t="n"/>
+      <c r="BC25" s="24" t="n"/>
+      <c r="BD25" s="24" t="n"/>
+      <c r="BE25" s="24" t="n"/>
+      <c r="BF25" s="24" t="n"/>
+      <c r="BG25" s="24" t="n"/>
+      <c r="BH25" s="24" t="n"/>
+      <c r="BI25" s="24" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n"/>
+      <c r="BL25" s="27" t="n"/>
+      <c r="BM25" s="28" t="n"/>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="n"/>
+      <c r="CT25" s="24" t="n"/>
+      <c r="CU25" s="24" t="n"/>
+      <c r="CV25" s="24" t="n"/>
+      <c r="CW25" s="24" t="n"/>
+      <c r="CX25" s="24" t="n"/>
+      <c r="CY25" s="24" t="n"/>
+      <c r="CZ25" s="24" t="n"/>
+      <c r="DA25" s="24" t="n"/>
+      <c r="DB25" s="24" t="n"/>
+      <c r="DC25" s="24" t="n"/>
+      <c r="DD25" s="24" t="n"/>
+      <c r="DE25" s="24" t="n"/>
+      <c r="DF25" s="24" t="n"/>
+      <c r="DG25" s="24" t="n"/>
+      <c r="DH25" s="24" t="n"/>
+      <c r="DI25" s="24" t="n"/>
+      <c r="DJ25" s="24" t="n"/>
+      <c r="DK25" s="24" t="n"/>
+      <c r="DL25" s="24" t="n"/>
+      <c r="DM25" s="24" t="n"/>
+      <c r="DN25" s="24" t="n"/>
+      <c r="DO25" s="24" t="n"/>
+      <c r="DP25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>5b497c15be7b4575</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T16:35:16.369606Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T17:40Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-kc-cle-2026-08-30-7pt5</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5256</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="R26" s="26" t="n"/>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:02:17.739705Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6H504ZW6KDF on tsc-mlb-kc-cle-2026-08-30-7pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="n"/>
+      <c r="AG26" s="24" t="n"/>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="n"/>
+      <c r="AL26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="n"/>
+      <c r="AQ26" s="24" t="n"/>
+      <c r="AR26" s="24" t="n"/>
+      <c r="AS26" s="24" t="n"/>
+      <c r="AT26" s="24" t="n"/>
+      <c r="AU26" s="24" t="n"/>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="n"/>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="n"/>
+      <c r="BA26" s="24" t="n"/>
+      <c r="BB26" s="24" t="n"/>
+      <c r="BC26" s="24" t="n"/>
+      <c r="BD26" s="24" t="n"/>
+      <c r="BE26" s="24" t="n"/>
+      <c r="BF26" s="24" t="n"/>
+      <c r="BG26" s="24" t="n"/>
+      <c r="BH26" s="24" t="n"/>
+      <c r="BI26" s="24" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n"/>
+      <c r="BL26" s="27" t="n"/>
+      <c r="BM26" s="28" t="n"/>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="n"/>
+      <c r="CT26" s="24" t="n"/>
+      <c r="CU26" s="24" t="n"/>
+      <c r="CV26" s="24" t="n"/>
+      <c r="CW26" s="24" t="n"/>
+      <c r="CX26" s="24" t="n"/>
+      <c r="CY26" s="24" t="n"/>
+      <c r="CZ26" s="24" t="n"/>
+      <c r="DA26" s="24" t="n"/>
+      <c r="DB26" s="24" t="n"/>
+      <c r="DC26" s="24" t="n"/>
+      <c r="DD26" s="24" t="n"/>
+      <c r="DE26" s="24" t="n"/>
+      <c r="DF26" s="24" t="n"/>
+      <c r="DG26" s="24" t="n"/>
+      <c r="DH26" s="24" t="n"/>
+      <c r="DI26" s="24" t="n"/>
+      <c r="DJ26" s="24" t="n"/>
+      <c r="DK26" s="24" t="n"/>
+      <c r="DL26" s="24" t="n"/>
+      <c r="DM26" s="24" t="n"/>
+      <c r="DN26" s="24" t="n"/>
+      <c r="DO26" s="24" t="n"/>
+      <c r="DP26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>3514efbef314473c</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:05Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-ath-tex-2026-08-31-7pt5</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="R27" s="26" t="n"/>
+      <c r="S27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABJQRKDK on tsc-mlb-ath-tex-2026-08-31-7pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="n"/>
+      <c r="AG27" s="24" t="n"/>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="n"/>
+      <c r="AL27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="n"/>
+      <c r="AQ27" s="24" t="n"/>
+      <c r="AR27" s="24" t="n"/>
+      <c r="AS27" s="24" t="n"/>
+      <c r="AT27" s="24" t="n"/>
+      <c r="AU27" s="24" t="n"/>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="n"/>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="n"/>
+      <c r="BA27" s="24" t="n"/>
+      <c r="BB27" s="24" t="n"/>
+      <c r="BC27" s="24" t="n"/>
+      <c r="BD27" s="24" t="n"/>
+      <c r="BE27" s="24" t="n"/>
+      <c r="BF27" s="24" t="n"/>
+      <c r="BG27" s="24" t="n"/>
+      <c r="BH27" s="24" t="n"/>
+      <c r="BI27" s="24" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n"/>
+      <c r="BL27" s="27" t="n"/>
+      <c r="BM27" s="28" t="n"/>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="n"/>
+      <c r="CT27" s="24" t="n"/>
+      <c r="CU27" s="24" t="n"/>
+      <c r="CV27" s="24" t="n"/>
+      <c r="CW27" s="24" t="n"/>
+      <c r="CX27" s="24" t="n"/>
+      <c r="CY27" s="24" t="n"/>
+      <c r="CZ27" s="24" t="n"/>
+      <c r="DA27" s="24" t="n"/>
+      <c r="DB27" s="24" t="n"/>
+      <c r="DC27" s="24" t="n"/>
+      <c r="DD27" s="24" t="n"/>
+      <c r="DE27" s="24" t="n"/>
+      <c r="DF27" s="24" t="n"/>
+      <c r="DG27" s="24" t="n"/>
+      <c r="DH27" s="24" t="n"/>
+      <c r="DI27" s="24" t="n"/>
+      <c r="DJ27" s="24" t="n"/>
+      <c r="DK27" s="24" t="n"/>
+      <c r="DL27" s="24" t="n"/>
+      <c r="DM27" s="24" t="n"/>
+      <c r="DN27" s="24" t="n"/>
+      <c r="DO27" s="24" t="n"/>
+      <c r="DP27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>1366137b9f7f4139</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:40Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-bal-col-2026-08-31-10pt5</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="R28" s="26" t="n"/>
+      <c r="S28" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFYJRFCKDF on tsc-mlb-bal-col-2026-08-31-10pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="n"/>
+      <c r="AG28" s="24" t="n"/>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="n"/>
+      <c r="AL28" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="n"/>
+      <c r="AQ28" s="24" t="n"/>
+      <c r="AR28" s="24" t="n"/>
+      <c r="AS28" s="24" t="n"/>
+      <c r="AT28" s="24" t="n"/>
+      <c r="AU28" s="24" t="n"/>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="n"/>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="n"/>
+      <c r="BA28" s="24" t="n"/>
+      <c r="BB28" s="24" t="n"/>
+      <c r="BC28" s="24" t="n"/>
+      <c r="BD28" s="24" t="n"/>
+      <c r="BE28" s="24" t="n"/>
+      <c r="BF28" s="24" t="n"/>
+      <c r="BG28" s="24" t="n"/>
+      <c r="BH28" s="24" t="n"/>
+      <c r="BI28" s="24" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n"/>
+      <c r="BL28" s="27" t="n"/>
+      <c r="BM28" s="28" t="n"/>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="n"/>
+      <c r="CT28" s="24" t="n"/>
+      <c r="CU28" s="24" t="n"/>
+      <c r="CV28" s="24" t="n"/>
+      <c r="CW28" s="24" t="n"/>
+      <c r="CX28" s="24" t="n"/>
+      <c r="CY28" s="24" t="n"/>
+      <c r="CZ28" s="24" t="n"/>
+      <c r="DA28" s="24" t="n"/>
+      <c r="DB28" s="24" t="n"/>
+      <c r="DC28" s="24" t="n"/>
+      <c r="DD28" s="24" t="n"/>
+      <c r="DE28" s="24" t="n"/>
+      <c r="DF28" s="24" t="n"/>
+      <c r="DG28" s="24" t="n"/>
+      <c r="DH28" s="24" t="n"/>
+      <c r="DI28" s="24" t="n"/>
+      <c r="DJ28" s="24" t="n"/>
+      <c r="DK28" s="24" t="n"/>
+      <c r="DL28" s="24" t="n"/>
+      <c r="DM28" s="24" t="n"/>
+      <c r="DN28" s="24" t="n"/>
+      <c r="DO28" s="24" t="n"/>
+      <c r="DP28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>6a99a099dcfa4a08</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>aec-wta-mansaw-panudv-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Panna Udvardy</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Mananchaya Sawangkaew</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="R29" s="26" t="n"/>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:41:38.707356Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFDE70CKDN on aec-wta-mansaw-panudv-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="n"/>
+      <c r="AG29" s="24" t="n"/>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="n"/>
+      <c r="AL29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="n"/>
+      <c r="AQ29" s="24" t="n"/>
+      <c r="AR29" s="24" t="n"/>
+      <c r="AS29" s="24" t="n"/>
+      <c r="AT29" s="24" t="n"/>
+      <c r="AU29" s="24" t="n"/>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="n"/>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="n"/>
+      <c r="BA29" s="24" t="n"/>
+      <c r="BB29" s="24" t="n"/>
+      <c r="BC29" s="24" t="n"/>
+      <c r="BD29" s="24" t="n"/>
+      <c r="BE29" s="24" t="n"/>
+      <c r="BF29" s="24" t="n"/>
+      <c r="BG29" s="24" t="n"/>
+      <c r="BH29" s="24" t="n"/>
+      <c r="BI29" s="24" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n"/>
+      <c r="BL29" s="27" t="n"/>
+      <c r="BM29" s="28" t="n"/>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="n"/>
+      <c r="CT29" s="24" t="n"/>
+      <c r="CU29" s="24" t="n"/>
+      <c r="CV29" s="24" t="n"/>
+      <c r="CW29" s="24" t="n"/>
+      <c r="CX29" s="24" t="n"/>
+      <c r="CY29" s="24" t="n"/>
+      <c r="CZ29" s="24" t="n"/>
+      <c r="DA29" s="24" t="n"/>
+      <c r="DB29" s="24" t="n"/>
+      <c r="DC29" s="24" t="n"/>
+      <c r="DD29" s="24" t="n"/>
+      <c r="DE29" s="24" t="n"/>
+      <c r="DF29" s="24" t="n"/>
+      <c r="DG29" s="24" t="n"/>
+      <c r="DH29" s="24" t="n"/>
+      <c r="DI29" s="24" t="n"/>
+      <c r="DJ29" s="24" t="n"/>
+      <c r="DK29" s="24" t="n"/>
+      <c r="DL29" s="24" t="n"/>
+      <c r="DM29" s="24" t="n"/>
+      <c r="DN29" s="24" t="n"/>
+      <c r="DO29" s="24" t="n"/>
+      <c r="DP29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>8b833b3bf6574b26</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>aec-wta-tamzid-martim-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Maria Timofeeva</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Tamara Zidansek</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="R30" s="26" t="n"/>
+      <c r="S30" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFNH8ZYKDJ on aec-wta-tamzid-martim-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="n"/>
+      <c r="AG30" s="24" t="n"/>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="n"/>
+      <c r="AL30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="n"/>
+      <c r="AQ30" s="24" t="n"/>
+      <c r="AR30" s="24" t="n"/>
+      <c r="AS30" s="24" t="n"/>
+      <c r="AT30" s="24" t="n"/>
+      <c r="AU30" s="24" t="n"/>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="n"/>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="n"/>
+      <c r="BA30" s="24" t="n"/>
+      <c r="BB30" s="24" t="n"/>
+      <c r="BC30" s="24" t="n"/>
+      <c r="BD30" s="24" t="n"/>
+      <c r="BE30" s="24" t="n"/>
+      <c r="BF30" s="24" t="n"/>
+      <c r="BG30" s="24" t="n"/>
+      <c r="BH30" s="24" t="n"/>
+      <c r="BI30" s="24" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n"/>
+      <c r="BL30" s="27" t="n"/>
+      <c r="BM30" s="28" t="n"/>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="n"/>
+      <c r="CT30" s="24" t="n"/>
+      <c r="CU30" s="24" t="n"/>
+      <c r="CV30" s="24" t="n"/>
+      <c r="CW30" s="24" t="n"/>
+      <c r="CX30" s="24" t="n"/>
+      <c r="CY30" s="24" t="n"/>
+      <c r="CZ30" s="24" t="n"/>
+      <c r="DA30" s="24" t="n"/>
+      <c r="DB30" s="24" t="n"/>
+      <c r="DC30" s="24" t="n"/>
+      <c r="DD30" s="24" t="n"/>
+      <c r="DE30" s="24" t="n"/>
+      <c r="DF30" s="24" t="n"/>
+      <c r="DG30" s="24" t="n"/>
+      <c r="DH30" s="24" t="n"/>
+      <c r="DI30" s="24" t="n"/>
+      <c r="DJ30" s="24" t="n"/>
+      <c r="DK30" s="24" t="n"/>
+      <c r="DL30" s="24" t="n"/>
+      <c r="DM30" s="24" t="n"/>
+      <c r="DN30" s="24" t="n"/>
+      <c r="DO30" s="24" t="n"/>
+      <c r="DP30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>55dfd65193ae4c3d</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-valvac-alekov-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Aleksandar Kovacevic</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Valentin Vacherot</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.9259</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="R31" s="26" t="n"/>
+      <c r="S31" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:41:38.707356Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFNH9JYKDJ on aec-atp-valvac-alekov-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="n"/>
+      <c r="AG31" s="24" t="n"/>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="n"/>
+      <c r="AL31" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="n"/>
+      <c r="AQ31" s="24" t="n"/>
+      <c r="AR31" s="24" t="n"/>
+      <c r="AS31" s="24" t="n"/>
+      <c r="AT31" s="24" t="n"/>
+      <c r="AU31" s="24" t="n"/>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="n"/>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="n"/>
+      <c r="BA31" s="24" t="n"/>
+      <c r="BB31" s="24" t="n"/>
+      <c r="BC31" s="24" t="n"/>
+      <c r="BD31" s="24" t="n"/>
+      <c r="BE31" s="24" t="n"/>
+      <c r="BF31" s="24" t="n"/>
+      <c r="BG31" s="24" t="n"/>
+      <c r="BH31" s="24" t="n"/>
+      <c r="BI31" s="24" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n"/>
+      <c r="BL31" s="27" t="n"/>
+      <c r="BM31" s="28" t="n"/>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="n"/>
+      <c r="CT31" s="24" t="n"/>
+      <c r="CU31" s="24" t="n"/>
+      <c r="CV31" s="24" t="n"/>
+      <c r="CW31" s="24" t="n"/>
+      <c r="CX31" s="24" t="n"/>
+      <c r="CY31" s="24" t="n"/>
+      <c r="CZ31" s="24" t="n"/>
+      <c r="DA31" s="24" t="n"/>
+      <c r="DB31" s="24" t="n"/>
+      <c r="DC31" s="24" t="n"/>
+      <c r="DD31" s="24" t="n"/>
+      <c r="DE31" s="24" t="n"/>
+      <c r="DF31" s="24" t="n"/>
+      <c r="DG31" s="24" t="n"/>
+      <c r="DH31" s="24" t="n"/>
+      <c r="DI31" s="24" t="n"/>
+      <c r="DJ31" s="24" t="n"/>
+      <c r="DK31" s="24" t="n"/>
+      <c r="DL31" s="24" t="n"/>
+      <c r="DM31" s="24" t="n"/>
+      <c r="DN31" s="24" t="n"/>
+      <c r="DO31" s="24" t="n"/>
+      <c r="DP31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>525d5353a78b4b49</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-matarn-jamduc-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>James Duckworth</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Matteo Arnaldi</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="R32" s="26" t="n"/>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFCN0FYKDG on aec-atp-matarn-jamduc-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="n"/>
+      <c r="AG32" s="24" t="n"/>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="n"/>
+      <c r="AL32" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="n"/>
+      <c r="AQ32" s="24" t="n"/>
+      <c r="AR32" s="24" t="n"/>
+      <c r="AS32" s="24" t="n"/>
+      <c r="AT32" s="24" t="n"/>
+      <c r="AU32" s="24" t="n"/>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="n"/>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="n"/>
+      <c r="BA32" s="24" t="n"/>
+      <c r="BB32" s="24" t="n"/>
+      <c r="BC32" s="24" t="n"/>
+      <c r="BD32" s="24" t="n"/>
+      <c r="BE32" s="24" t="n"/>
+      <c r="BF32" s="24" t="n"/>
+      <c r="BG32" s="24" t="n"/>
+      <c r="BH32" s="24" t="n"/>
+      <c r="BI32" s="24" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n"/>
+      <c r="BL32" s="27" t="n"/>
+      <c r="BM32" s="28" t="n"/>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="n"/>
+      <c r="CT32" s="24" t="n"/>
+      <c r="CU32" s="24" t="n"/>
+      <c r="CV32" s="24" t="n"/>
+      <c r="CW32" s="24" t="n"/>
+      <c r="CX32" s="24" t="n"/>
+      <c r="CY32" s="24" t="n"/>
+      <c r="CZ32" s="24" t="n"/>
+      <c r="DA32" s="24" t="n"/>
+      <c r="DB32" s="24" t="n"/>
+      <c r="DC32" s="24" t="n"/>
+      <c r="DD32" s="24" t="n"/>
+      <c r="DE32" s="24" t="n"/>
+      <c r="DF32" s="24" t="n"/>
+      <c r="DG32" s="24" t="n"/>
+      <c r="DH32" s="24" t="n"/>
+      <c r="DI32" s="24" t="n"/>
+      <c r="DJ32" s="24" t="n"/>
+      <c r="DK32" s="24" t="n"/>
+      <c r="DL32" s="24" t="n"/>
+      <c r="DM32" s="24" t="n"/>
+      <c r="DN32" s="24" t="n"/>
+      <c r="DO32" s="24" t="n"/>
+      <c r="DP32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>62563810a67a4509</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-romsaf-caralc-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Carlos Alcaraz</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Roman Safiullin</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-488</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.2049</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="R33" s="26" t="n"/>
+      <c r="S33" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABM5CKDK on aec-atp-romsaf-caralc-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="n"/>
+      <c r="AG33" s="24" t="n"/>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="n"/>
+      <c r="AL33" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="n"/>
+      <c r="AQ33" s="24" t="n"/>
+      <c r="AR33" s="24" t="n"/>
+      <c r="AS33" s="24" t="n"/>
+      <c r="AT33" s="24" t="n"/>
+      <c r="AU33" s="24" t="n"/>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="n"/>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="n"/>
+      <c r="BA33" s="24" t="n"/>
+      <c r="BB33" s="24" t="n"/>
+      <c r="BC33" s="24" t="n"/>
+      <c r="BD33" s="24" t="n"/>
+      <c r="BE33" s="24" t="n"/>
+      <c r="BF33" s="24" t="n"/>
+      <c r="BG33" s="24" t="n"/>
+      <c r="BH33" s="24" t="n"/>
+      <c r="BI33" s="24" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n"/>
+      <c r="BL33" s="27" t="n"/>
+      <c r="BM33" s="28" t="n"/>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="n"/>
+      <c r="CT33" s="24" t="n"/>
+      <c r="CU33" s="24" t="n"/>
+      <c r="CV33" s="24" t="n"/>
+      <c r="CW33" s="24" t="n"/>
+      <c r="CX33" s="24" t="n"/>
+      <c r="CY33" s="24" t="n"/>
+      <c r="CZ33" s="24" t="n"/>
+      <c r="DA33" s="24" t="n"/>
+      <c r="DB33" s="24" t="n"/>
+      <c r="DC33" s="24" t="n"/>
+      <c r="DD33" s="24" t="n"/>
+      <c r="DE33" s="24" t="n"/>
+      <c r="DF33" s="24" t="n"/>
+      <c r="DG33" s="24" t="n"/>
+      <c r="DH33" s="24" t="n"/>
+      <c r="DI33" s="24" t="n"/>
+      <c r="DJ33" s="24" t="n"/>
+      <c r="DK33" s="24" t="n"/>
+      <c r="DL33" s="24" t="n"/>
+      <c r="DM33" s="24" t="n"/>
+      <c r="DN33" s="24" t="n"/>
+      <c r="DO33" s="24" t="n"/>
+      <c r="DP33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>a405afb6c6f7469b</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-dalsvr-valroy-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Valentin Royer</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Dalibor Svrcina</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="R34" s="26" t="n"/>
+      <c r="S34" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VEZ2T7JKDC on aec-atp-dalsvr-valroy-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="n"/>
+      <c r="AG34" s="24" t="n"/>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="n"/>
+      <c r="AL34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="n"/>
+      <c r="AQ34" s="24" t="n"/>
+      <c r="AR34" s="24" t="n"/>
+      <c r="AS34" s="24" t="n"/>
+      <c r="AT34" s="24" t="n"/>
+      <c r="AU34" s="24" t="n"/>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="n"/>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="n"/>
+      <c r="BA34" s="24" t="n"/>
+      <c r="BB34" s="24" t="n"/>
+      <c r="BC34" s="24" t="n"/>
+      <c r="BD34" s="24" t="n"/>
+      <c r="BE34" s="24" t="n"/>
+      <c r="BF34" s="24" t="n"/>
+      <c r="BG34" s="24" t="n"/>
+      <c r="BH34" s="24" t="n"/>
+      <c r="BI34" s="24" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n"/>
+      <c r="BL34" s="27" t="n"/>
+      <c r="BM34" s="28" t="n"/>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="n"/>
+      <c r="CT34" s="24" t="n"/>
+      <c r="CU34" s="24" t="n"/>
+      <c r="CV34" s="24" t="n"/>
+      <c r="CW34" s="24" t="n"/>
+      <c r="CX34" s="24" t="n"/>
+      <c r="CY34" s="24" t="n"/>
+      <c r="CZ34" s="24" t="n"/>
+      <c r="DA34" s="24" t="n"/>
+      <c r="DB34" s="24" t="n"/>
+      <c r="DC34" s="24" t="n"/>
+      <c r="DD34" s="24" t="n"/>
+      <c r="DE34" s="24" t="n"/>
+      <c r="DF34" s="24" t="n"/>
+      <c r="DG34" s="24" t="n"/>
+      <c r="DH34" s="24" t="n"/>
+      <c r="DI34" s="24" t="n"/>
+      <c r="DJ34" s="24" t="n"/>
+      <c r="DK34" s="24" t="n"/>
+      <c r="DL34" s="24" t="n"/>
+      <c r="DM34" s="24" t="n"/>
+      <c r="DN34" s="24" t="n"/>
+      <c r="DO34" s="24" t="n"/>
+      <c r="DP34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>34d64f0e02e04343</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:30Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-jurrod-gioper-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Giovanni Mpetshi Perricard</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Jurij Rodionov</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="R35" s="26" t="n"/>
+      <c r="S35" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VF7S7KGKDM on aec-atp-jurrod-gioper-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="n"/>
+      <c r="AG35" s="24" t="n"/>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="n"/>
+      <c r="AL35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="n"/>
+      <c r="AQ35" s="24" t="n"/>
+      <c r="AR35" s="24" t="n"/>
+      <c r="AS35" s="24" t="n"/>
+      <c r="AT35" s="24" t="n"/>
+      <c r="AU35" s="24" t="n"/>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="n"/>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="n"/>
+      <c r="BA35" s="24" t="n"/>
+      <c r="BB35" s="24" t="n"/>
+      <c r="BC35" s="24" t="n"/>
+      <c r="BD35" s="24" t="n"/>
+      <c r="BE35" s="24" t="n"/>
+      <c r="BF35" s="24" t="n"/>
+      <c r="BG35" s="24" t="n"/>
+      <c r="BH35" s="24" t="n"/>
+      <c r="BI35" s="24" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n"/>
+      <c r="BL35" s="27" t="n"/>
+      <c r="BM35" s="28" t="n"/>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="n"/>
+      <c r="CT35" s="24" t="n"/>
+      <c r="CU35" s="24" t="n"/>
+      <c r="CV35" s="24" t="n"/>
+      <c r="CW35" s="24" t="n"/>
+      <c r="CX35" s="24" t="n"/>
+      <c r="CY35" s="24" t="n"/>
+      <c r="CZ35" s="24" t="n"/>
+      <c r="DA35" s="24" t="n"/>
+      <c r="DB35" s="24" t="n"/>
+      <c r="DC35" s="24" t="n"/>
+      <c r="DD35" s="24" t="n"/>
+      <c r="DE35" s="24" t="n"/>
+      <c r="DF35" s="24" t="n"/>
+      <c r="DG35" s="24" t="n"/>
+      <c r="DH35" s="24" t="n"/>
+      <c r="DI35" s="24" t="n"/>
+      <c r="DJ35" s="24" t="n"/>
+      <c r="DK35" s="24" t="n"/>
+      <c r="DL35" s="24" t="n"/>
+      <c r="DM35" s="24" t="n"/>
+      <c r="DN35" s="24" t="n"/>
+      <c r="DO35" s="24" t="n"/>
+      <c r="DP35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>f138da48996b4c4e</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T20:30Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-yanhan-aletab-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="R36" s="26" t="n"/>
+      <c r="S36" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VEZ2V6CKDC on aec-atp-yanhan-aletab-2026-08-30 (long)</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="n"/>
+      <c r="AG36" s="24" t="n"/>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="n"/>
+      <c r="AL36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="n"/>
+      <c r="AQ36" s="24" t="n"/>
+      <c r="AR36" s="24" t="n"/>
+      <c r="AS36" s="24" t="n"/>
+      <c r="AT36" s="24" t="n"/>
+      <c r="AU36" s="24" t="n"/>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="n"/>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="n"/>
+      <c r="BA36" s="24" t="n"/>
+      <c r="BB36" s="24" t="n"/>
+      <c r="BC36" s="24" t="n"/>
+      <c r="BD36" s="24" t="n"/>
+      <c r="BE36" s="24" t="n"/>
+      <c r="BF36" s="24" t="n"/>
+      <c r="BG36" s="24" t="n"/>
+      <c r="BH36" s="24" t="n"/>
+      <c r="BI36" s="24" t="n"/>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n"/>
+      <c r="BL36" s="27" t="n"/>
+      <c r="BM36" s="28" t="n"/>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="n"/>
+      <c r="CT36" s="24" t="n"/>
+      <c r="CU36" s="24" t="n"/>
+      <c r="CV36" s="24" t="n"/>
+      <c r="CW36" s="24" t="n"/>
+      <c r="CX36" s="24" t="n"/>
+      <c r="CY36" s="24" t="n"/>
+      <c r="CZ36" s="24" t="n"/>
+      <c r="DA36" s="24" t="n"/>
+      <c r="DB36" s="24" t="n"/>
+      <c r="DC36" s="24" t="n"/>
+      <c r="DD36" s="24" t="n"/>
+      <c r="DE36" s="24" t="n"/>
+      <c r="DF36" s="24" t="n"/>
+      <c r="DG36" s="24" t="n"/>
+      <c r="DH36" s="24" t="n"/>
+      <c r="DI36" s="24" t="n"/>
+      <c r="DJ36" s="24" t="n"/>
+      <c r="DK36" s="24" t="n"/>
+      <c r="DL36" s="24" t="n"/>
+      <c r="DM36" s="24" t="n"/>
+      <c r="DN36" s="24" t="n"/>
+      <c r="DO36" s="24" t="n"/>
+      <c r="DP36" s="24" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>87994ded7cbc49d8</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-ssins-havu-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>HAVU</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Saint Sinners</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="R37" s="26" t="n"/>
+      <c r="S37" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:02:25.134027Z</t>
+        </is>
+      </c>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFCN1GAKDG on aec-cs2-ssins-havu-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="n"/>
+      <c r="AG37" s="24" t="n"/>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="n"/>
+      <c r="AL37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="n"/>
+      <c r="AQ37" s="24" t="n"/>
+      <c r="AR37" s="24" t="n"/>
+      <c r="AS37" s="24" t="n"/>
+      <c r="AT37" s="24" t="n"/>
+      <c r="AU37" s="24" t="n"/>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="n"/>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="n"/>
+      <c r="BA37" s="24" t="n"/>
+      <c r="BB37" s="24" t="n"/>
+      <c r="BC37" s="24" t="n"/>
+      <c r="BD37" s="24" t="n"/>
+      <c r="BE37" s="24" t="n"/>
+      <c r="BF37" s="24" t="n"/>
+      <c r="BG37" s="24" t="n"/>
+      <c r="BH37" s="24" t="n"/>
+      <c r="BI37" s="24" t="n"/>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n"/>
+      <c r="BL37" s="27" t="n"/>
+      <c r="BM37" s="28" t="n"/>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="n"/>
+      <c r="CT37" s="24" t="n"/>
+      <c r="CU37" s="24" t="n"/>
+      <c r="CV37" s="24" t="n"/>
+      <c r="CW37" s="24" t="n"/>
+      <c r="CX37" s="24" t="n"/>
+      <c r="CY37" s="24" t="n"/>
+      <c r="CZ37" s="24" t="n"/>
+      <c r="DA37" s="24" t="n"/>
+      <c r="DB37" s="24" t="n"/>
+      <c r="DC37" s="24" t="n"/>
+      <c r="DD37" s="24" t="n"/>
+      <c r="DE37" s="24" t="n"/>
+      <c r="DF37" s="24" t="n"/>
+      <c r="DG37" s="24" t="n"/>
+      <c r="DH37" s="24" t="n"/>
+      <c r="DI37" s="24" t="n"/>
+      <c r="DJ37" s="24" t="n"/>
+      <c r="DK37" s="24" t="n"/>
+      <c r="DL37" s="24" t="n"/>
+      <c r="DM37" s="24" t="n"/>
+      <c r="DN37" s="24" t="n"/>
+      <c r="DO37" s="24" t="n"/>
+      <c r="DP37" s="24" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>76d3b05a54a14e62</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-ff-mel-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="R38" s="26" t="n"/>
+      <c r="S38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABNFWKDK on aec-cs2-ff-mel-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="n"/>
+      <c r="AG38" s="24" t="n"/>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="n"/>
+      <c r="AL38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="n"/>
+      <c r="AQ38" s="24" t="n"/>
+      <c r="AR38" s="24" t="n"/>
+      <c r="AS38" s="24" t="n"/>
+      <c r="AT38" s="24" t="n"/>
+      <c r="AU38" s="24" t="n"/>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="n"/>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="n"/>
+      <c r="BA38" s="24" t="n"/>
+      <c r="BB38" s="24" t="n"/>
+      <c r="BC38" s="24" t="n"/>
+      <c r="BD38" s="24" t="n"/>
+      <c r="BE38" s="24" t="n"/>
+      <c r="BF38" s="24" t="n"/>
+      <c r="BG38" s="24" t="n"/>
+      <c r="BH38" s="24" t="n"/>
+      <c r="BI38" s="24" t="n"/>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n"/>
+      <c r="BL38" s="27" t="n"/>
+      <c r="BM38" s="28" t="n"/>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="n"/>
+      <c r="CT38" s="24" t="n"/>
+      <c r="CU38" s="24" t="n"/>
+      <c r="CV38" s="24" t="n"/>
+      <c r="CW38" s="24" t="n"/>
+      <c r="CX38" s="24" t="n"/>
+      <c r="CY38" s="24" t="n"/>
+      <c r="CZ38" s="24" t="n"/>
+      <c r="DA38" s="24" t="n"/>
+      <c r="DB38" s="24" t="n"/>
+      <c r="DC38" s="24" t="n"/>
+      <c r="DD38" s="24" t="n"/>
+      <c r="DE38" s="24" t="n"/>
+      <c r="DF38" s="24" t="n"/>
+      <c r="DG38" s="24" t="n"/>
+      <c r="DH38" s="24" t="n"/>
+      <c r="DI38" s="24" t="n"/>
+      <c r="DJ38" s="24" t="n"/>
+      <c r="DK38" s="24" t="n"/>
+      <c r="DL38" s="24" t="n"/>
+      <c r="DM38" s="24" t="n"/>
+      <c r="DN38" s="24" t="n"/>
+      <c r="DO38" s="24" t="n"/>
+      <c r="DP38" s="24" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>6d6be9d1964a4439</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:30:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-g2-aur-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Aurora Gaming</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.8197</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="R39" s="26" t="n"/>
+      <c r="S39" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AD39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:02:25.134027Z</t>
+        </is>
+      </c>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABNP6KDK on aec-cs2-g2-aur-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="n"/>
+      <c r="AG39" s="24" t="n"/>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="n"/>
+      <c r="AL39" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="n"/>
+      <c r="AQ39" s="24" t="n"/>
+      <c r="AR39" s="24" t="n"/>
+      <c r="AS39" s="24" t="n"/>
+      <c r="AT39" s="24" t="n"/>
+      <c r="AU39" s="24" t="n"/>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="n"/>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="n"/>
+      <c r="BA39" s="24" t="n"/>
+      <c r="BB39" s="24" t="n"/>
+      <c r="BC39" s="24" t="n"/>
+      <c r="BD39" s="24" t="n"/>
+      <c r="BE39" s="24" t="n"/>
+      <c r="BF39" s="24" t="n"/>
+      <c r="BG39" s="24" t="n"/>
+      <c r="BH39" s="24" t="n"/>
+      <c r="BI39" s="24" t="n"/>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n"/>
+      <c r="BL39" s="27" t="n"/>
+      <c r="BM39" s="28" t="n"/>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="n"/>
+      <c r="CT39" s="24" t="n"/>
+      <c r="CU39" s="24" t="n"/>
+      <c r="CV39" s="24" t="n"/>
+      <c r="CW39" s="24" t="n"/>
+      <c r="CX39" s="24" t="n"/>
+      <c r="CY39" s="24" t="n"/>
+      <c r="CZ39" s="24" t="n"/>
+      <c r="DA39" s="24" t="n"/>
+      <c r="DB39" s="24" t="n"/>
+      <c r="DC39" s="24" t="n"/>
+      <c r="DD39" s="24" t="n"/>
+      <c r="DE39" s="24" t="n"/>
+      <c r="DF39" s="24" t="n"/>
+      <c r="DG39" s="24" t="n"/>
+      <c r="DH39" s="24" t="n"/>
+      <c r="DI39" s="24" t="n"/>
+      <c r="DJ39" s="24" t="n"/>
+      <c r="DK39" s="24" t="n"/>
+      <c r="DL39" s="24" t="n"/>
+      <c r="DM39" s="24" t="n"/>
+      <c r="DN39" s="24" t="n"/>
+      <c r="DO39" s="24" t="n"/>
+      <c r="DP39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>69301f19746a4d8d</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-nem-ntr-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Team Nemesis</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFCN23GKDG on aec-cs2-nem-ntr-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="n"/>
+      <c r="AG40" s="24" t="n"/>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="n"/>
+      <c r="AL40" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="n"/>
+      <c r="AQ40" s="24" t="n"/>
+      <c r="AR40" s="24" t="n"/>
+      <c r="AS40" s="24" t="n"/>
+      <c r="AT40" s="24" t="n"/>
+      <c r="AU40" s="24" t="n"/>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="n"/>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="n"/>
+      <c r="BA40" s="24" t="n"/>
+      <c r="BB40" s="24" t="n"/>
+      <c r="BC40" s="24" t="n"/>
+      <c r="BD40" s="24" t="n"/>
+      <c r="BE40" s="24" t="n"/>
+      <c r="BF40" s="24" t="n"/>
+      <c r="BG40" s="24" t="n"/>
+      <c r="BH40" s="24" t="n"/>
+      <c r="BI40" s="24" t="n"/>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n"/>
+      <c r="BL40" s="27" t="n"/>
+      <c r="BM40" s="28" t="n"/>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="n"/>
+      <c r="CT40" s="24" t="n"/>
+      <c r="CU40" s="24" t="n"/>
+      <c r="CV40" s="24" t="n"/>
+      <c r="CW40" s="24" t="n"/>
+      <c r="CX40" s="24" t="n"/>
+      <c r="CY40" s="24" t="n"/>
+      <c r="CZ40" s="24" t="n"/>
+      <c r="DA40" s="24" t="n"/>
+      <c r="DB40" s="24" t="n"/>
+      <c r="DC40" s="24" t="n"/>
+      <c r="DD40" s="24" t="n"/>
+      <c r="DE40" s="24" t="n"/>
+      <c r="DF40" s="24" t="n"/>
+      <c r="DG40" s="24" t="n"/>
+      <c r="DH40" s="24" t="n"/>
+      <c r="DI40" s="24" t="n"/>
+      <c r="DJ40" s="24" t="n"/>
+      <c r="DK40" s="24" t="n"/>
+      <c r="DL40" s="24" t="n"/>
+      <c r="DM40" s="24" t="n"/>
+      <c r="DN40" s="24" t="n"/>
+      <c r="DO40" s="24" t="n"/>
+      <c r="DP40" s="24" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>08a9248313f04395</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:30:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-cw-5s-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>5star</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Chinggis Warriors</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.8197</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:02:25.134027Z</t>
+        </is>
+      </c>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFNHBQEKDJ on aec-cs2-cw-5s-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="n"/>
+      <c r="AG41" s="24" t="n"/>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="n"/>
+      <c r="AL41" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="n"/>
+      <c r="AQ41" s="24" t="n"/>
+      <c r="AR41" s="24" t="n"/>
+      <c r="AS41" s="24" t="n"/>
+      <c r="AT41" s="24" t="n"/>
+      <c r="AU41" s="24" t="n"/>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="n"/>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="n"/>
+      <c r="BA41" s="24" t="n"/>
+      <c r="BB41" s="24" t="n"/>
+      <c r="BC41" s="24" t="n"/>
+      <c r="BD41" s="24" t="n"/>
+      <c r="BE41" s="24" t="n"/>
+      <c r="BF41" s="24" t="n"/>
+      <c r="BG41" s="24" t="n"/>
+      <c r="BH41" s="24" t="n"/>
+      <c r="BI41" s="24" t="n"/>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n"/>
+      <c r="BL41" s="27" t="n"/>
+      <c r="BM41" s="28" t="n"/>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="n"/>
+      <c r="CT41" s="24" t="n"/>
+      <c r="CU41" s="24" t="n"/>
+      <c r="CV41" s="24" t="n"/>
+      <c r="CW41" s="24" t="n"/>
+      <c r="CX41" s="24" t="n"/>
+      <c r="CY41" s="24" t="n"/>
+      <c r="CZ41" s="24" t="n"/>
+      <c r="DA41" s="24" t="n"/>
+      <c r="DB41" s="24" t="n"/>
+      <c r="DC41" s="24" t="n"/>
+      <c r="DD41" s="24" t="n"/>
+      <c r="DE41" s="24" t="n"/>
+      <c r="DF41" s="24" t="n"/>
+      <c r="DG41" s="24" t="n"/>
+      <c r="DH41" s="24" t="n"/>
+      <c r="DI41" s="24" t="n"/>
+      <c r="DJ41" s="24" t="n"/>
+      <c r="DK41" s="24" t="n"/>
+      <c r="DL41" s="24" t="n"/>
+      <c r="DM41" s="24" t="n"/>
+      <c r="DN41" s="24" t="n"/>
+      <c r="DO41" s="24" t="n"/>
+      <c r="DP41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>10fe43507a894dff</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-mouz-fal-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.8197</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="R42" s="26" t="n"/>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VFCN32YKDG on aec-cs2-mouz-fal-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="n"/>
+      <c r="AG42" s="24" t="n"/>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="n"/>
+      <c r="AL42" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="n"/>
+      <c r="AQ42" s="24" t="n"/>
+      <c r="AR42" s="24" t="n"/>
+      <c r="AS42" s="24" t="n"/>
+      <c r="AT42" s="24" t="n"/>
+      <c r="AU42" s="24" t="n"/>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="n"/>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="n"/>
+      <c r="BA42" s="24" t="n"/>
+      <c r="BB42" s="24" t="n"/>
+      <c r="BC42" s="24" t="n"/>
+      <c r="BD42" s="24" t="n"/>
+      <c r="BE42" s="24" t="n"/>
+      <c r="BF42" s="24" t="n"/>
+      <c r="BG42" s="24" t="n"/>
+      <c r="BH42" s="24" t="n"/>
+      <c r="BI42" s="24" t="n"/>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n"/>
+      <c r="BL42" s="27" t="n"/>
+      <c r="BM42" s="28" t="n"/>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="n"/>
+      <c r="CT42" s="24" t="n"/>
+      <c r="CU42" s="24" t="n"/>
+      <c r="CV42" s="24" t="n"/>
+      <c r="CW42" s="24" t="n"/>
+      <c r="CX42" s="24" t="n"/>
+      <c r="CY42" s="24" t="n"/>
+      <c r="CZ42" s="24" t="n"/>
+      <c r="DA42" s="24" t="n"/>
+      <c r="DB42" s="24" t="n"/>
+      <c r="DC42" s="24" t="n"/>
+      <c r="DD42" s="24" t="n"/>
+      <c r="DE42" s="24" t="n"/>
+      <c r="DF42" s="24" t="n"/>
+      <c r="DG42" s="24" t="n"/>
+      <c r="DH42" s="24" t="n"/>
+      <c r="DI42" s="24" t="n"/>
+      <c r="DJ42" s="24" t="n"/>
+      <c r="DK42" s="24" t="n"/>
+      <c r="DL42" s="24" t="n"/>
+      <c r="DM42" s="24" t="n"/>
+      <c r="DN42" s="24" t="n"/>
+      <c r="DO42" s="24" t="n"/>
+      <c r="DP42" s="24" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>2888a62dd3ba4d78</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-fut-vit-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Vitality</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>FUT Esports</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.4695</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.6805</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.9538</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="R43" s="26" t="n"/>
+      <c r="S43" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABPXTKDK on aec-cs2-fut-vit-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="n"/>
+      <c r="AG43" s="24" t="n"/>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="n"/>
+      <c r="AL43" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="n"/>
+      <c r="AQ43" s="24" t="n"/>
+      <c r="AR43" s="24" t="n"/>
+      <c r="AS43" s="24" t="n"/>
+      <c r="AT43" s="24" t="n"/>
+      <c r="AU43" s="24" t="n"/>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="n"/>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="n"/>
+      <c r="BA43" s="24" t="n"/>
+      <c r="BB43" s="24" t="n"/>
+      <c r="BC43" s="24" t="n"/>
+      <c r="BD43" s="24" t="n"/>
+      <c r="BE43" s="24" t="n"/>
+      <c r="BF43" s="24" t="n"/>
+      <c r="BG43" s="24" t="n"/>
+      <c r="BH43" s="24" t="n"/>
+      <c r="BI43" s="24" t="n"/>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n"/>
+      <c r="BL43" s="27" t="n"/>
+      <c r="BM43" s="28" t="n"/>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="n"/>
+      <c r="CT43" s="24" t="n"/>
+      <c r="CU43" s="24" t="n"/>
+      <c r="CV43" s="24" t="n"/>
+      <c r="CW43" s="24" t="n"/>
+      <c r="CX43" s="24" t="n"/>
+      <c r="CY43" s="24" t="n"/>
+      <c r="CZ43" s="24" t="n"/>
+      <c r="DA43" s="24" t="n"/>
+      <c r="DB43" s="24" t="n"/>
+      <c r="DC43" s="24" t="n"/>
+      <c r="DD43" s="24" t="n"/>
+      <c r="DE43" s="24" t="n"/>
+      <c r="DF43" s="24" t="n"/>
+      <c r="DG43" s="24" t="n"/>
+      <c r="DH43" s="24" t="n"/>
+      <c r="DI43" s="24" t="n"/>
+      <c r="DJ43" s="24" t="n"/>
+      <c r="DK43" s="24" t="n"/>
+      <c r="DL43" s="24" t="n"/>
+      <c r="DM43" s="24" t="n"/>
+      <c r="DN43" s="24" t="n"/>
+      <c r="DO43" s="24" t="n"/>
+      <c r="DP43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>7a9087c46a114e9c</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T04:52:35.718859Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-hon-sawy-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="R44" s="26" t="n"/>
+      <c r="S44" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VGABQ8AKDK on aec-cs2-hon-sawy-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="n"/>
+      <c r="AG44" s="24" t="n"/>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="n"/>
+      <c r="AL44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="n"/>
+      <c r="AQ44" s="24" t="n"/>
+      <c r="AR44" s="24" t="n"/>
+      <c r="AS44" s="24" t="n"/>
+      <c r="AT44" s="24" t="n"/>
+      <c r="AU44" s="24" t="n"/>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="n"/>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="n"/>
+      <c r="BA44" s="24" t="n"/>
+      <c r="BB44" s="24" t="n"/>
+      <c r="BC44" s="24" t="n"/>
+      <c r="BD44" s="24" t="n"/>
+      <c r="BE44" s="24" t="n"/>
+      <c r="BF44" s="24" t="n"/>
+      <c r="BG44" s="24" t="n"/>
+      <c r="BH44" s="24" t="n"/>
+      <c r="BI44" s="24" t="n"/>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n"/>
+      <c r="BL44" s="27" t="n"/>
+      <c r="BM44" s="28" t="n"/>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="n"/>
+      <c r="CT44" s="24" t="n"/>
+      <c r="CU44" s="24" t="n"/>
+      <c r="CV44" s="24" t="n"/>
+      <c r="CW44" s="24" t="n"/>
+      <c r="CX44" s="24" t="n"/>
+      <c r="CY44" s="24" t="n"/>
+      <c r="CZ44" s="24" t="n"/>
+      <c r="DA44" s="24" t="n"/>
+      <c r="DB44" s="24" t="n"/>
+      <c r="DC44" s="24" t="n"/>
+      <c r="DD44" s="24" t="n"/>
+      <c r="DE44" s="24" t="n"/>
+      <c r="DF44" s="24" t="n"/>
+      <c r="DG44" s="24" t="n"/>
+      <c r="DH44" s="24" t="n"/>
+      <c r="DI44" s="24" t="n"/>
+      <c r="DJ44" s="24" t="n"/>
+      <c r="DK44" s="24" t="n"/>
+      <c r="DL44" s="24" t="n"/>
+      <c r="DM44" s="24" t="n"/>
+      <c r="DN44" s="24" t="n"/>
+      <c r="DO44" s="24" t="n"/>
+      <c r="DP44" s="24" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>48cccc66566349ce</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T05:28:12.217545Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>aec-mlb-sf-atl-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.6667</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.6571</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="R45" s="26" t="n"/>
+      <c r="S45" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6VZ1TQF4KDJ on aec-mlb-sf-atl-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="n"/>
+      <c r="AG45" s="24" t="n"/>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="n"/>
+      <c r="AL45" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="n"/>
+      <c r="AQ45" s="24" t="n"/>
+      <c r="AR45" s="24" t="n"/>
+      <c r="AS45" s="24" t="n"/>
+      <c r="AT45" s="24" t="n"/>
+      <c r="AU45" s="24" t="n"/>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="n"/>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="n"/>
+      <c r="BA45" s="24" t="n"/>
+      <c r="BB45" s="24" t="n"/>
+      <c r="BC45" s="24" t="n"/>
+      <c r="BD45" s="24" t="n"/>
+      <c r="BE45" s="24" t="n"/>
+      <c r="BF45" s="24" t="n"/>
+      <c r="BG45" s="24" t="n"/>
+      <c r="BH45" s="24" t="n"/>
+      <c r="BI45" s="24" t="n"/>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n"/>
+      <c r="BL45" s="27" t="n"/>
+      <c r="BM45" s="28" t="n"/>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="n"/>
+      <c r="CT45" s="24" t="n"/>
+      <c r="CU45" s="24" t="n"/>
+      <c r="CV45" s="24" t="n"/>
+      <c r="CW45" s="24" t="n"/>
+      <c r="CX45" s="24" t="n"/>
+      <c r="CY45" s="24" t="n"/>
+      <c r="CZ45" s="24" t="n"/>
+      <c r="DA45" s="24" t="n"/>
+      <c r="DB45" s="24" t="n"/>
+      <c r="DC45" s="24" t="n"/>
+      <c r="DD45" s="24" t="n"/>
+      <c r="DE45" s="24" t="n"/>
+      <c r="DF45" s="24" t="n"/>
+      <c r="DG45" s="24" t="n"/>
+      <c r="DH45" s="24" t="n"/>
+      <c r="DI45" s="24" t="n"/>
+      <c r="DJ45" s="24" t="n"/>
+      <c r="DK45" s="24" t="n"/>
+      <c r="DL45" s="24" t="n"/>
+      <c r="DM45" s="24" t="n"/>
+      <c r="DN45" s="24" t="n"/>
+      <c r="DO45" s="24" t="n"/>
+      <c r="DP45" s="24" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>d972531055904f04</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T05:28:12.217545Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>aec-mlb-det-min-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="R46" s="26" t="n"/>
+      <c r="S46" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C6W0RWB0MKDH on aec-mlb-det-min-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="n"/>
+      <c r="AG46" s="24" t="n"/>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="n"/>
+      <c r="AL46" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="n"/>
+      <c r="AQ46" s="24" t="n"/>
+      <c r="AR46" s="24" t="n"/>
+      <c r="AS46" s="24" t="n"/>
+      <c r="AT46" s="24" t="n"/>
+      <c r="AU46" s="24" t="n"/>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="n"/>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="n"/>
+      <c r="BA46" s="24" t="n"/>
+      <c r="BB46" s="24" t="n"/>
+      <c r="BC46" s="24" t="n"/>
+      <c r="BD46" s="24" t="n"/>
+      <c r="BE46" s="24" t="n"/>
+      <c r="BF46" s="24" t="n"/>
+      <c r="BG46" s="24" t="n"/>
+      <c r="BH46" s="24" t="n"/>
+      <c r="BI46" s="24" t="n"/>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n"/>
+      <c r="BL46" s="27" t="n"/>
+      <c r="BM46" s="28" t="n"/>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="n"/>
+      <c r="CT46" s="24" t="n"/>
+      <c r="CU46" s="24" t="n"/>
+      <c r="CV46" s="24" t="n"/>
+      <c r="CW46" s="24" t="n"/>
+      <c r="CX46" s="24" t="n"/>
+      <c r="CY46" s="24" t="n"/>
+      <c r="CZ46" s="24" t="n"/>
+      <c r="DA46" s="24" t="n"/>
+      <c r="DB46" s="24" t="n"/>
+      <c r="DC46" s="24" t="n"/>
+      <c r="DD46" s="24" t="n"/>
+      <c r="DE46" s="24" t="n"/>
+      <c r="DF46" s="24" t="n"/>
+      <c r="DG46" s="24" t="n"/>
+      <c r="DH46" s="24" t="n"/>
+      <c r="DI46" s="24" t="n"/>
+      <c r="DJ46" s="24" t="n"/>
+      <c r="DK46" s="24" t="n"/>
+      <c r="DL46" s="24" t="n"/>
+      <c r="DM46" s="24" t="n"/>
+      <c r="DN46" s="24" t="n"/>
+      <c r="DO46" s="24" t="n"/>
+      <c r="DP46" s="24" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>26a05e27c35344e1</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>aec-mlb-bal-col-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>1.7874</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.5982</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="R47" s="26" t="n"/>
+      <c r="S47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75CWYPPPKDC on aec-mlb-bal-col-2026-08-31 (long)</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="n"/>
+      <c r="AG47" s="24" t="n"/>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="n"/>
+      <c r="AL47" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="n"/>
+      <c r="AQ47" s="24" t="n"/>
+      <c r="AR47" s="24" t="n"/>
+      <c r="AS47" s="24" t="n"/>
+      <c r="AT47" s="24" t="n"/>
+      <c r="AU47" s="24" t="n"/>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="n"/>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="n"/>
+      <c r="BA47" s="24" t="n"/>
+      <c r="BB47" s="24" t="n"/>
+      <c r="BC47" s="24" t="n"/>
+      <c r="BD47" s="24" t="n"/>
+      <c r="BE47" s="24" t="n"/>
+      <c r="BF47" s="24" t="n"/>
+      <c r="BG47" s="24" t="n"/>
+      <c r="BH47" s="24" t="n"/>
+      <c r="BI47" s="24" t="n"/>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n"/>
+      <c r="BL47" s="27" t="n"/>
+      <c r="BM47" s="28" t="n"/>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="n"/>
+      <c r="CT47" s="24" t="n"/>
+      <c r="CU47" s="24" t="n"/>
+      <c r="CV47" s="24" t="n"/>
+      <c r="CW47" s="24" t="n"/>
+      <c r="CX47" s="24" t="n"/>
+      <c r="CY47" s="24" t="n"/>
+      <c r="CZ47" s="24" t="n"/>
+      <c r="DA47" s="24" t="n"/>
+      <c r="DB47" s="24" t="n"/>
+      <c r="DC47" s="24" t="n"/>
+      <c r="DD47" s="24" t="n"/>
+      <c r="DE47" s="24" t="n"/>
+      <c r="DF47" s="24" t="n"/>
+      <c r="DG47" s="24" t="n"/>
+      <c r="DH47" s="24" t="n"/>
+      <c r="DI47" s="24" t="n"/>
+      <c r="DJ47" s="24" t="n"/>
+      <c r="DK47" s="24" t="n"/>
+      <c r="DL47" s="24" t="n"/>
+      <c r="DM47" s="24" t="n"/>
+      <c r="DN47" s="24" t="n"/>
+      <c r="DO47" s="24" t="n"/>
+      <c r="DP47" s="24" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>7ee8b96d25fc46af</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T22:05Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-sf-atl-2026-08-31-8pt5</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="R48" s="26" t="n"/>
+      <c r="S48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75E2V3VPKDH on tsc-mlb-sf-atl-2026-08-31-8pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="n"/>
+      <c r="AG48" s="24" t="n"/>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="n"/>
+      <c r="AL48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="n"/>
+      <c r="AQ48" s="24" t="n"/>
+      <c r="AR48" s="24" t="n"/>
+      <c r="AS48" s="24" t="n"/>
+      <c r="AT48" s="24" t="n"/>
+      <c r="AU48" s="24" t="n"/>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="n"/>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="n"/>
+      <c r="BA48" s="24" t="n"/>
+      <c r="BB48" s="24" t="n"/>
+      <c r="BC48" s="24" t="n"/>
+      <c r="BD48" s="24" t="n"/>
+      <c r="BE48" s="24" t="n"/>
+      <c r="BF48" s="24" t="n"/>
+      <c r="BG48" s="24" t="n"/>
+      <c r="BH48" s="24" t="n"/>
+      <c r="BI48" s="24" t="n"/>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n"/>
+      <c r="BL48" s="27" t="n"/>
+      <c r="BM48" s="28" t="n"/>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="n"/>
+      <c r="CT48" s="24" t="n"/>
+      <c r="CU48" s="24" t="n"/>
+      <c r="CV48" s="24" t="n"/>
+      <c r="CW48" s="24" t="n"/>
+      <c r="CX48" s="24" t="n"/>
+      <c r="CY48" s="24" t="n"/>
+      <c r="CZ48" s="24" t="n"/>
+      <c r="DA48" s="24" t="n"/>
+      <c r="DB48" s="24" t="n"/>
+      <c r="DC48" s="24" t="n"/>
+      <c r="DD48" s="24" t="n"/>
+      <c r="DE48" s="24" t="n"/>
+      <c r="DF48" s="24" t="n"/>
+      <c r="DG48" s="24" t="n"/>
+      <c r="DH48" s="24" t="n"/>
+      <c r="DI48" s="24" t="n"/>
+      <c r="DJ48" s="24" t="n"/>
+      <c r="DK48" s="24" t="n"/>
+      <c r="DL48" s="24" t="n"/>
+      <c r="DM48" s="24" t="n"/>
+      <c r="DN48" s="24" t="n"/>
+      <c r="DO48" s="24" t="n"/>
+      <c r="DP48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>8e234c9a1aa54341</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T22:40Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-nym-tb-2026-08-31-8pt5</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="R49" s="26" t="n"/>
+      <c r="S49" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75E2V4FEKDH on tsc-mlb-nym-tb-2026-08-31-8pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="n"/>
+      <c r="AG49" s="24" t="n"/>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="n"/>
+      <c r="AL49" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="n"/>
+      <c r="AQ49" s="24" t="n"/>
+      <c r="AR49" s="24" t="n"/>
+      <c r="AS49" s="24" t="n"/>
+      <c r="AT49" s="24" t="n"/>
+      <c r="AU49" s="24" t="n"/>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="n"/>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="n"/>
+      <c r="BA49" s="24" t="n"/>
+      <c r="BB49" s="24" t="n"/>
+      <c r="BC49" s="24" t="n"/>
+      <c r="BD49" s="24" t="n"/>
+      <c r="BE49" s="24" t="n"/>
+      <c r="BF49" s="24" t="n"/>
+      <c r="BG49" s="24" t="n"/>
+      <c r="BH49" s="24" t="n"/>
+      <c r="BI49" s="24" t="n"/>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n"/>
+      <c r="BL49" s="27" t="n"/>
+      <c r="BM49" s="28" t="n"/>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="n"/>
+      <c r="CT49" s="24" t="n"/>
+      <c r="CU49" s="24" t="n"/>
+      <c r="CV49" s="24" t="n"/>
+      <c r="CW49" s="24" t="n"/>
+      <c r="CX49" s="24" t="n"/>
+      <c r="CY49" s="24" t="n"/>
+      <c r="CZ49" s="24" t="n"/>
+      <c r="DA49" s="24" t="n"/>
+      <c r="DB49" s="24" t="n"/>
+      <c r="DC49" s="24" t="n"/>
+      <c r="DD49" s="24" t="n"/>
+      <c r="DE49" s="24" t="n"/>
+      <c r="DF49" s="24" t="n"/>
+      <c r="DG49" s="24" t="n"/>
+      <c r="DH49" s="24" t="n"/>
+      <c r="DI49" s="24" t="n"/>
+      <c r="DJ49" s="24" t="n"/>
+      <c r="DK49" s="24" t="n"/>
+      <c r="DL49" s="24" t="n"/>
+      <c r="DM49" s="24" t="n"/>
+      <c r="DN49" s="24" t="n"/>
+      <c r="DO49" s="24" t="n"/>
+      <c r="DP49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>37aaf37c09f84e3f</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:40Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-mil-chc-2026-08-31-9pt5</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.9615</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="R50" s="26" t="n"/>
+      <c r="S50" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75E1JWMRKDG on tsc-mlb-mil-chc-2026-08-31-9pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="n"/>
+      <c r="AG50" s="24" t="n"/>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="n"/>
+      <c r="AL50" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="n"/>
+      <c r="AQ50" s="24" t="n"/>
+      <c r="AR50" s="24" t="n"/>
+      <c r="AS50" s="24" t="n"/>
+      <c r="AT50" s="24" t="n"/>
+      <c r="AU50" s="24" t="n"/>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="n"/>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="n"/>
+      <c r="BA50" s="24" t="n"/>
+      <c r="BB50" s="24" t="n"/>
+      <c r="BC50" s="24" t="n"/>
+      <c r="BD50" s="24" t="n"/>
+      <c r="BE50" s="24" t="n"/>
+      <c r="BF50" s="24" t="n"/>
+      <c r="BG50" s="24" t="n"/>
+      <c r="BH50" s="24" t="n"/>
+      <c r="BI50" s="24" t="n"/>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n"/>
+      <c r="BL50" s="27" t="n"/>
+      <c r="BM50" s="28" t="n"/>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="n"/>
+      <c r="CT50" s="24" t="n"/>
+      <c r="CU50" s="24" t="n"/>
+      <c r="CV50" s="24" t="n"/>
+      <c r="CW50" s="24" t="n"/>
+      <c r="CX50" s="24" t="n"/>
+      <c r="CY50" s="24" t="n"/>
+      <c r="CZ50" s="24" t="n"/>
+      <c r="DA50" s="24" t="n"/>
+      <c r="DB50" s="24" t="n"/>
+      <c r="DC50" s="24" t="n"/>
+      <c r="DD50" s="24" t="n"/>
+      <c r="DE50" s="24" t="n"/>
+      <c r="DF50" s="24" t="n"/>
+      <c r="DG50" s="24" t="n"/>
+      <c r="DH50" s="24" t="n"/>
+      <c r="DI50" s="24" t="n"/>
+      <c r="DJ50" s="24" t="n"/>
+      <c r="DK50" s="24" t="n"/>
+      <c r="DL50" s="24" t="n"/>
+      <c r="DM50" s="24" t="n"/>
+      <c r="DN50" s="24" t="n"/>
+      <c r="DO50" s="24" t="n"/>
+      <c r="DP50" s="24" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>8651501eb94f43b2</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-01T01:38Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>tsc-mlb-nyy-laa-2026-08-31-8pt5</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="R51" s="26" t="n"/>
+      <c r="S51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75D7932RKDD on tsc-mlb-nyy-laa-2026-08-31-8pt5 (long)</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="n"/>
+      <c r="AG51" s="24" t="n"/>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="n"/>
+      <c r="AL51" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="n"/>
+      <c r="AQ51" s="24" t="n"/>
+      <c r="AR51" s="24" t="n"/>
+      <c r="AS51" s="24" t="n"/>
+      <c r="AT51" s="24" t="n"/>
+      <c r="AU51" s="24" t="n"/>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="n"/>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="n"/>
+      <c r="BA51" s="24" t="n"/>
+      <c r="BB51" s="24" t="n"/>
+      <c r="BC51" s="24" t="n"/>
+      <c r="BD51" s="24" t="n"/>
+      <c r="BE51" s="24" t="n"/>
+      <c r="BF51" s="24" t="n"/>
+      <c r="BG51" s="24" t="n"/>
+      <c r="BH51" s="24" t="n"/>
+      <c r="BI51" s="24" t="n"/>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n"/>
+      <c r="BL51" s="27" t="n"/>
+      <c r="BM51" s="28" t="n"/>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="n"/>
+      <c r="CT51" s="24" t="n"/>
+      <c r="CU51" s="24" t="n"/>
+      <c r="CV51" s="24" t="n"/>
+      <c r="CW51" s="24" t="n"/>
+      <c r="CX51" s="24" t="n"/>
+      <c r="CY51" s="24" t="n"/>
+      <c r="CZ51" s="24" t="n"/>
+      <c r="DA51" s="24" t="n"/>
+      <c r="DB51" s="24" t="n"/>
+      <c r="DC51" s="24" t="n"/>
+      <c r="DD51" s="24" t="n"/>
+      <c r="DE51" s="24" t="n"/>
+      <c r="DF51" s="24" t="n"/>
+      <c r="DG51" s="24" t="n"/>
+      <c r="DH51" s="24" t="n"/>
+      <c r="DI51" s="24" t="n"/>
+      <c r="DJ51" s="24" t="n"/>
+      <c r="DK51" s="24" t="n"/>
+      <c r="DL51" s="24" t="n"/>
+      <c r="DM51" s="24" t="n"/>
+      <c r="DN51" s="24" t="n"/>
+      <c r="DO51" s="24" t="n"/>
+      <c r="DP51" s="24" t="n"/>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>816e58389cba4c61</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>aec-wta-vikgol-diapar-2026-08-30</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Diane Parry</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>1.9259</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="R52" s="26" t="n"/>
+      <c r="S52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75DSQ4KAKDM on aec-wta-vikgol-diapar-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="n"/>
+      <c r="AG52" s="24" t="n"/>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="n"/>
+      <c r="AL52" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="n"/>
+      <c r="AQ52" s="24" t="n"/>
+      <c r="AR52" s="24" t="n"/>
+      <c r="AS52" s="24" t="n"/>
+      <c r="AT52" s="24" t="n"/>
+      <c r="AU52" s="24" t="n"/>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="n"/>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="n"/>
+      <c r="BA52" s="24" t="n"/>
+      <c r="BB52" s="24" t="n"/>
+      <c r="BC52" s="24" t="n"/>
+      <c r="BD52" s="24" t="n"/>
+      <c r="BE52" s="24" t="n"/>
+      <c r="BF52" s="24" t="n"/>
+      <c r="BG52" s="24" t="n"/>
+      <c r="BH52" s="24" t="n"/>
+      <c r="BI52" s="24" t="n"/>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n"/>
+      <c r="BL52" s="27" t="n"/>
+      <c r="BM52" s="28" t="n"/>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="n"/>
+      <c r="CT52" s="24" t="n"/>
+      <c r="CU52" s="24" t="n"/>
+      <c r="CV52" s="24" t="n"/>
+      <c r="CW52" s="24" t="n"/>
+      <c r="CX52" s="24" t="n"/>
+      <c r="CY52" s="24" t="n"/>
+      <c r="CZ52" s="24" t="n"/>
+      <c r="DA52" s="24" t="n"/>
+      <c r="DB52" s="24" t="n"/>
+      <c r="DC52" s="24" t="n"/>
+      <c r="DD52" s="24" t="n"/>
+      <c r="DE52" s="24" t="n"/>
+      <c r="DF52" s="24" t="n"/>
+      <c r="DG52" s="24" t="n"/>
+      <c r="DH52" s="24" t="n"/>
+      <c r="DI52" s="24" t="n"/>
+      <c r="DJ52" s="24" t="n"/>
+      <c r="DK52" s="24" t="n"/>
+      <c r="DL52" s="24" t="n"/>
+      <c r="DM52" s="24" t="n"/>
+      <c r="DN52" s="24" t="n"/>
+      <c r="DO52" s="24" t="n"/>
+      <c r="DP52" s="24" t="n"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>b214bda284bc4f41</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-dam-zge-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Zetta Games</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Damajuana</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="R53" s="26" t="n"/>
+      <c r="S53" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75ED9T52KDF on aec-cs2-dam-zge-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="n"/>
+      <c r="AG53" s="24" t="n"/>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="n"/>
+      <c r="AL53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="n"/>
+      <c r="AQ53" s="24" t="n"/>
+      <c r="AR53" s="24" t="n"/>
+      <c r="AS53" s="24" t="n"/>
+      <c r="AT53" s="24" t="n"/>
+      <c r="AU53" s="24" t="n"/>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="n"/>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="n"/>
+      <c r="BA53" s="24" t="n"/>
+      <c r="BB53" s="24" t="n"/>
+      <c r="BC53" s="24" t="n"/>
+      <c r="BD53" s="24" t="n"/>
+      <c r="BE53" s="24" t="n"/>
+      <c r="BF53" s="24" t="n"/>
+      <c r="BG53" s="24" t="n"/>
+      <c r="BH53" s="24" t="n"/>
+      <c r="BI53" s="24" t="n"/>
+      <c r="BJ53" s="25" t="n"/>
+      <c r="BK53" s="26" t="n"/>
+      <c r="BL53" s="27" t="n"/>
+      <c r="BM53" s="28" t="n"/>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="n"/>
+      <c r="CT53" s="24" t="n"/>
+      <c r="CU53" s="24" t="n"/>
+      <c r="CV53" s="24" t="n"/>
+      <c r="CW53" s="24" t="n"/>
+      <c r="CX53" s="24" t="n"/>
+      <c r="CY53" s="24" t="n"/>
+      <c r="CZ53" s="24" t="n"/>
+      <c r="DA53" s="24" t="n"/>
+      <c r="DB53" s="24" t="n"/>
+      <c r="DC53" s="24" t="n"/>
+      <c r="DD53" s="24" t="n"/>
+      <c r="DE53" s="24" t="n"/>
+      <c r="DF53" s="24" t="n"/>
+      <c r="DG53" s="24" t="n"/>
+      <c r="DH53" s="24" t="n"/>
+      <c r="DI53" s="24" t="n"/>
+      <c r="DJ53" s="24" t="n"/>
+      <c r="DK53" s="24" t="n"/>
+      <c r="DL53" s="24" t="n"/>
+      <c r="DM53" s="24" t="n"/>
+      <c r="DN53" s="24" t="n"/>
+      <c r="DO53" s="24" t="n"/>
+      <c r="DP53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>fd008ef45af2480d</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:12:42.599391Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-mm-sdm-2026-08-31</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Semente do Mal</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Mansão Maromba</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="R54" s="26" t="n"/>
+      <c r="S54" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C75CWYWSTKDC on aec-cs2-mm-sdm-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="n"/>
+      <c r="AG54" s="24" t="n"/>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="n"/>
+      <c r="AL54" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="n"/>
+      <c r="AQ54" s="24" t="n"/>
+      <c r="AR54" s="24" t="n"/>
+      <c r="AS54" s="24" t="n"/>
+      <c r="AT54" s="24" t="n"/>
+      <c r="AU54" s="24" t="n"/>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="n"/>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="n"/>
+      <c r="BA54" s="24" t="n"/>
+      <c r="BB54" s="24" t="n"/>
+      <c r="BC54" s="24" t="n"/>
+      <c r="BD54" s="24" t="n"/>
+      <c r="BE54" s="24" t="n"/>
+      <c r="BF54" s="24" t="n"/>
+      <c r="BG54" s="24" t="n"/>
+      <c r="BH54" s="24" t="n"/>
+      <c r="BI54" s="24" t="n"/>
+      <c r="BJ54" s="25" t="n"/>
+      <c r="BK54" s="26" t="n"/>
+      <c r="BL54" s="27" t="n"/>
+      <c r="BM54" s="28" t="n"/>
+      <c r="BN54" s="28" t="n"/>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="n"/>
+      <c r="CD54" s="24" t="n"/>
+      <c r="CE54" s="24" t="n"/>
+      <c r="CF54" s="24" t="n"/>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="n"/>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="n"/>
+      <c r="CM54" s="24" t="n"/>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="n"/>
+      <c r="CT54" s="24" t="n"/>
+      <c r="CU54" s="24" t="n"/>
+      <c r="CV54" s="24" t="n"/>
+      <c r="CW54" s="24" t="n"/>
+      <c r="CX54" s="24" t="n"/>
+      <c r="CY54" s="24" t="n"/>
+      <c r="CZ54" s="24" t="n"/>
+      <c r="DA54" s="24" t="n"/>
+      <c r="DB54" s="24" t="n"/>
+      <c r="DC54" s="24" t="n"/>
+      <c r="DD54" s="24" t="n"/>
+      <c r="DE54" s="24" t="n"/>
+      <c r="DF54" s="24" t="n"/>
+      <c r="DG54" s="24" t="n"/>
+      <c r="DH54" s="24" t="n"/>
+      <c r="DI54" s="24" t="n"/>
+      <c r="DJ54" s="24" t="n"/>
+      <c r="DK54" s="24" t="n"/>
+      <c r="DL54" s="24" t="n"/>
+      <c r="DM54" s="24" t="n"/>
+      <c r="DN54" s="24" t="n"/>
+      <c r="DO54" s="24" t="n"/>
+      <c r="DP54" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/auto_buyer_picks.xlsx
+++ b/data/auto_buyer_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP54" headerRowCount="1">
-  <autoFilter ref="A1:DP54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP51" headerRowCount="1">
+  <autoFilter ref="A1:DP51"/>
   <tableColumns count="120">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -779,19 +779,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$54)</f>
+        <f>COUNTA('Picks'!$A$2:$A$51)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$54,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$54,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")/(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$54)/SUM('Picks'!$BX$2:$BX$54),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
         <v/>
       </c>
     </row>
@@ -859,19 +859,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$54)</f>
+        <f>SUM('Picks'!$BY$2:$BY$51)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$54,"&lt;&gt;",'Picks'!$AB$2:$AB$54),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$54,'Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -942,11 +942,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -957,15 +957,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -973,11 +973,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -988,15 +988,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1004,11 +1004,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DP54"/>
+  <dimension ref="A1:DP51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7069,7 +7069,7 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>3514efbef314473c</t>
+          <t>6a99a099dcfa4a08</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
@@ -7079,37 +7079,37 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T00:05Z</t>
+          <t>2026-08-31T15:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-ath-tex-2026-08-31-7pt5</t>
+          <t>aec-wta-mansaw-panudv-2026-08-30</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>TENNIS</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Panna Udvardy</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Mananchaya Sawangkaew</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J27" s="25" t="n"/>
@@ -7119,53 +7119,59 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.495</v>
+        <v>0.3906</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.5393</v>
+        <v>0.5028</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.0443</v>
+        <v>0.1128</v>
       </c>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
       <c r="AC27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="24" t="n"/>
+        <v>-1.5</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:41:38.707356Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABJQRKDK on tsc-mlb-ath-tex-2026-08-31-7pt5 (long)</t>
+          <t>Auto-Buyer order C6VFDE70CKDN on aec-wta-mansaw-panudv-2026-08-30 (short)</t>
         </is>
       </c>
       <c r="AF27" s="31" t="n"/>
@@ -7275,7 +7281,7 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>1366137b9f7f4139</t>
+          <t>8b833b3bf6574b26</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
@@ -7285,37 +7291,37 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T00:40Z</t>
+          <t>2026-08-31T17:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-bal-col-2026-08-31-10pt5</t>
+          <t>aec-wta-tamzid-martim-2026-08-30</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>TENNIS</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Maria Timofeeva</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Tamara Zidansek</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -7325,28 +7331,28 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.13</v>
+        <v>2.94</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.4695</v>
+        <v>0.3401</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.5286</v>
+        <v>0.5261</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.0586</v>
+        <v>0.1861</v>
       </c>
       <c r="R28" s="26" t="n"/>
       <c r="S28" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>tennis-surface-elo-v1</t>
         </is>
       </c>
       <c r="U28" s="24" t="inlineStr">
@@ -7371,7 +7377,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFYJRFCKDF on tsc-mlb-bal-col-2026-08-31-10pt5 (short)</t>
+          <t>Auto-Buyer order C6VFNH8ZYKDJ on aec-wta-tamzid-martim-2026-08-30 (long)</t>
         </is>
       </c>
       <c r="AF28" s="31" t="n"/>
@@ -7481,7 +7487,7 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>6a99a099dcfa4a08</t>
+          <t>55dfd65193ae4c3d</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
@@ -7496,7 +7502,7 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>aec-wta-mansaw-panudv-2026-08-30</t>
+          <t>aec-atp-valvac-alekov-2026-08-30</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -7506,12 +7512,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Panna Udvardy</t>
+          <t>Aleksandar Kovacevic</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Mananchaya Sawangkaew</t>
+          <t>Valentin Vacherot</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -7521,7 +7527,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -7531,20 +7537,20 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>156</v>
+        <v>-108</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.56</v>
+        <v>1.9259</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.3906</v>
+        <v>0.5192</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.5028</v>
+        <v>0.6385</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.1128</v>
+        <v>0.1185</v>
       </c>
       <c r="R29" s="26" t="n"/>
       <c r="S29" s="29" t="n">
@@ -7562,7 +7568,7 @@
       </c>
       <c r="V29" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W29" s="26" t="n"/>
@@ -7574,7 +7580,7 @@
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
       <c r="AC29" s="30" t="n">
-        <v>-1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
         <is>
@@ -7583,7 +7589,7 @@
       </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFDE70CKDN on aec-wta-mansaw-panudv-2026-08-30 (short)</t>
+          <t>Auto-Buyer order C6VFNH9JYKDJ on aec-atp-valvac-alekov-2026-08-30 (long)</t>
         </is>
       </c>
       <c r="AF29" s="31" t="n"/>
@@ -7693,7 +7699,7 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>8b833b3bf6574b26</t>
+          <t>525d5353a78b4b49</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
@@ -7708,7 +7714,7 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>aec-wta-tamzid-martim-2026-08-30</t>
+          <t>aec-atp-matarn-jamduc-2026-08-30</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -7718,12 +7724,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Maria Timofeeva</t>
+          <t>James Duckworth</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Tamara Zidansek</t>
+          <t>Matteo Arnaldi</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -7733,7 +7739,7 @@
       </c>
       <c r="I30" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J30" s="25" t="n"/>
@@ -7743,20 +7749,20 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.3401</v>
+        <v>0.3906</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.5261</v>
+        <v>0.5743</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.1861</v>
+        <v>0.1843</v>
       </c>
       <c r="R30" s="26" t="n"/>
       <c r="S30" s="29" t="n">
@@ -7789,7 +7795,7 @@
       <c r="AD30" s="24" t="n"/>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFNH8ZYKDJ on aec-wta-tamzid-martim-2026-08-30 (long)</t>
+          <t>Auto-Buyer order C6VFCN0FYKDG on aec-atp-matarn-jamduc-2026-08-30 (short)</t>
         </is>
       </c>
       <c r="AF30" s="31" t="n"/>
@@ -7899,7 +7905,7 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>55dfd65193ae4c3d</t>
+          <t>62563810a67a4509</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
@@ -7909,12 +7915,12 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T15:00Z</t>
+          <t>2026-08-31T17:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-valvac-alekov-2026-08-30</t>
+          <t>aec-atp-romsaf-caralc-2026-08-30</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -7924,12 +7930,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Aleksandar Kovacevic</t>
+          <t>Carlos Alcaraz</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Valentin Vacherot</t>
+          <t>Roman Safiullin</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -7939,7 +7945,7 @@
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J31" s="25" t="n"/>
@@ -7949,20 +7955,20 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-108</v>
+        <v>-488</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.9259</v>
+        <v>1.2049</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.5192</v>
+        <v>0.8299</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.6385</v>
+        <v>0.9435</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.1185</v>
+        <v>0.1135</v>
       </c>
       <c r="R31" s="26" t="n"/>
       <c r="S31" s="29" t="n">
@@ -7975,33 +7981,27 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
+          <t>open</t>
         </is>
       </c>
       <c r="V31" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>open</t>
         </is>
       </c>
       <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n">
-        <v>1</v>
-      </c>
+      <c r="X31" s="26" t="n"/>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
       <c r="AC31" s="30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD31" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T18:41:38.707356Z</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFNH9JYKDJ on aec-atp-valvac-alekov-2026-08-30 (long)</t>
+          <t>Auto-Buyer order C6VGABM5CKDK on aec-atp-romsaf-caralc-2026-08-30 (short)</t>
         </is>
       </c>
       <c r="AF31" s="31" t="n"/>
@@ -8111,7 +8111,7 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>525d5353a78b4b49</t>
+          <t>a405afb6c6f7469b</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T17:00Z</t>
+          <t>2026-08-31T18:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-matarn-jamduc-2026-08-30</t>
+          <t>aec-atp-dalsvr-valroy-2026-08-30</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>James Duckworth</t>
+          <t>Valentin Royer</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Matteo Arnaldi</t>
+          <t>Dalibor Svrcina</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -8161,24 +8161,24 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.3906</v>
+        <v>0.4902</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.5743</v>
+        <v>0.5763</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.1843</v>
+        <v>0.0863</v>
       </c>
       <c r="R32" s="26" t="n"/>
       <c r="S32" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFCN0FYKDG on aec-atp-matarn-jamduc-2026-08-30 (short)</t>
+          <t>Auto-Buyer order C6VEZ2T7JKDC on aec-atp-dalsvr-valroy-2026-08-30 (long)</t>
         </is>
       </c>
       <c r="AF32" s="31" t="n"/>
@@ -8317,7 +8317,7 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>62563810a67a4509</t>
+          <t>34d64f0e02e04343</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T17:00Z</t>
+          <t>2026-08-31T18:30Z</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-romsaf-caralc-2026-08-30</t>
+          <t>aec-atp-jurrod-gioper-2026-08-30</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Carlos Alcaraz</t>
+          <t>Giovanni Mpetshi Perricard</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Roman Safiullin</t>
+          <t>Jurij Rodionov</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J33" s="25" t="n"/>
@@ -8367,24 +8367,24 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-488</v>
+        <v>104</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.2049</v>
+        <v>2.04</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.8299</v>
+        <v>0.4902</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.9435</v>
+        <v>0.5453</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.1135</v>
+        <v>0.0553</v>
       </c>
       <c r="R33" s="26" t="n"/>
       <c r="S33" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABM5CKDK on aec-atp-romsaf-caralc-2026-08-30 (short)</t>
+          <t>Auto-Buyer order C6VF7S7KGKDM on aec-atp-jurrod-gioper-2026-08-30 (long)</t>
         </is>
       </c>
       <c r="AF33" s="31" t="n"/>
@@ -8523,7 +8523,7 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>a405afb6c6f7469b</t>
+          <t>f138da48996b4c4e</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:00Z</t>
+          <t>2026-08-31T20:30Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-dalsvr-valroy-2026-08-30</t>
+          <t>aec-atp-yanhan-aletab-2026-08-30</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Valentin Royer</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>Dalibor Svrcina</t>
+          <t>Yannick Hanfmann</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -8573,24 +8573,24 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.4902</v>
+        <v>0.4292</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.5763</v>
+        <v>0.5565</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.0863</v>
+        <v>0.1265</v>
       </c>
       <c r="R34" s="26" t="n"/>
       <c r="S34" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VEZ2T7JKDC on aec-atp-dalsvr-valroy-2026-08-30 (long)</t>
+          <t>Auto-Buyer order C6VEZ2V6CKDC on aec-atp-yanhan-aletab-2026-08-30 (long)</t>
         </is>
       </c>
       <c r="AF34" s="31" t="n"/>
@@ -8729,7 +8729,7 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>34d64f0e02e04343</t>
+          <t>87994ded7cbc49d8</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -8739,27 +8739,27 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:30Z</t>
+          <t>2026-08-31T08:00:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-jurrod-gioper-2026-08-30</t>
+          <t>aec-cs2-ssins-havu-2026-08-31</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>TENNIS</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Giovanni Mpetshi Perricard</t>
+          <t>HAVU</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Jurij Rodionov</t>
+          <t>Saint Sinners</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -8779,20 +8779,20 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.4902</v>
+        <v>0.4695</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.5453</v>
+        <v>0.5151</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.0553</v>
+        <v>0.0451</v>
       </c>
       <c r="R35" s="26" t="n"/>
       <c r="S35" s="29" t="n">
@@ -8800,17 +8800,17 @@
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
-          <t>tennis-surface-elo-v1</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U35" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V35" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W35" s="26" t="n"/>
@@ -8820,12 +8820,16 @@
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
       <c r="AC35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="24" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="AD35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:02:25.134027Z</t>
+        </is>
+      </c>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VF7S7KGKDM on aec-atp-jurrod-gioper-2026-08-30 (long)</t>
+          <t>Auto-Buyer order C6VFCN1GAKDG on aec-cs2-ssins-havu-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF35" s="31" t="n"/>
@@ -8935,7 +8939,7 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>f138da48996b4c4e</t>
+          <t>76d3b05a54a14e62</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
@@ -8945,27 +8949,27 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T20:30Z</t>
+          <t>2026-08-31T10:30:00Z</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>aec-atp-yanhan-aletab-2026-08-30</t>
+          <t>aec-cs2-ff-mel-2026-08-31</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>TENNIS</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Yannick Hanfmann</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -8975,7 +8979,7 @@
       </c>
       <c r="I36" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J36" s="25" t="n"/>
@@ -8985,28 +8989,28 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>133</v>
+        <v>-113</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>2.33</v>
+        <v>1.885</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.4292</v>
+        <v>0.5305</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.5565</v>
+        <v>0.5667</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.1265</v>
+        <v>0.0367</v>
       </c>
       <c r="R36" s="26" t="n"/>
       <c r="S36" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
-          <t>tennis-surface-elo-v1</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U36" s="24" t="inlineStr">
@@ -9031,7 +9035,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VEZ2V6CKDC on aec-atp-yanhan-aletab-2026-08-30 (long)</t>
+          <t>Auto-Buyer order C6VGABNFWKDK on aec-cs2-ff-mel-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF36" s="31" t="n"/>
@@ -9141,7 +9145,7 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>87994ded7cbc49d8</t>
+          <t>6d6be9d1964a4439</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
@@ -9151,12 +9155,12 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T08:00:00Z</t>
+          <t>2026-08-31T11:30:00Z</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-ssins-havu-2026-08-31</t>
+          <t>aec-cs2-g2-aur-2026-08-31</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -9166,12 +9170,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>HAVU</t>
+          <t>Aurora Gaming</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>Saint Sinners</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -9191,20 +9195,20 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>113</v>
+        <v>-122</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>2.13</v>
+        <v>1.8197</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.4695</v>
+        <v>0.5495</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.5151</v>
+        <v>0.6077</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.0451</v>
+        <v>0.0577</v>
       </c>
       <c r="R37" s="26" t="n"/>
       <c r="S37" s="29" t="n">
@@ -9232,7 +9236,7 @@
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
       <c r="AC37" s="30" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
         <is>
@@ -9241,7 +9245,7 @@
       </c>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFCN1GAKDG on aec-cs2-ssins-havu-2026-08-31 (long)</t>
+          <t>Auto-Buyer order C6VGABNP6KDK on aec-cs2-g2-aur-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF37" s="31" t="n"/>
@@ -9351,7 +9355,7 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>76d3b05a54a14e62</t>
+          <t>69301f19746a4d8d</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
@@ -9361,12 +9365,12 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T10:30:00Z</t>
+          <t>2026-08-31T12:00:00Z</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-ff-mel-2026-08-31</t>
+          <t>aec-cs2-nem-ntr-2026-08-31</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -9376,12 +9380,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Nuclear TigeRES</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>Team Nemesis</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -9401,24 +9405,24 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-113</v>
+        <v>-100</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.885</v>
+        <v>2</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.5305</v>
+        <v>0.5</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.5667</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.0367</v>
+        <v>0.1265</v>
       </c>
       <c r="R38" s="26" t="n"/>
       <c r="S38" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -9447,7 +9451,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABNFWKDK on aec-cs2-ff-mel-2026-08-31 (short)</t>
+          <t>Auto-Buyer order C6VFCN23GKDG on aec-cs2-nem-ntr-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF38" s="31" t="n"/>
@@ -9557,7 +9561,7 @@
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>6d6be9d1964a4439</t>
+          <t>08a9248313f04395</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
@@ -9567,12 +9571,12 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T11:30:00Z</t>
+          <t>2026-08-31T12:30:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-g2-aur-2026-08-31</t>
+          <t>aec-cs2-cw-5s-2026-08-31</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -9582,12 +9586,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Aurora Gaming</t>
+          <t>5star</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>Chinggis Warriors</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -9613,18 +9617,18 @@
         <v>1.8197</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.5495</v>
+        <v>0.5305</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.6077</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.0577</v>
+        <v>0.0624</v>
       </c>
       <c r="R39" s="26" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -9638,7 +9642,7 @@
       </c>
       <c r="V39" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W39" s="26" t="n"/>
@@ -9648,7 +9652,7 @@
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
       <c r="AC39" s="30" t="n">
-        <v>0.82</v>
+        <v>-1.25</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
         <is>
@@ -9657,7 +9661,7 @@
       </c>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABNP6KDK on aec-cs2-g2-aur-2026-08-31 (long)</t>
+          <t>Auto-Buyer order C6VFNHBQEKDJ on aec-cs2-cw-5s-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF39" s="31" t="n"/>
@@ -9767,7 +9771,7 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>69301f19746a4d8d</t>
+          <t>10fe43507a894dff</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
@@ -9777,12 +9781,12 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T12:00:00Z</t>
+          <t>2026-08-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-nem-ntr-2026-08-31</t>
+          <t>aec-cs2-mouz-fal-2026-08-31</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -9792,12 +9796,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Nuclear TigeRES</t>
+          <t>Team Falcons</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Team Nemesis</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -9817,24 +9821,24 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-100</v>
+        <v>-122</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>2</v>
+        <v>1.8197</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.5</v>
+        <v>0.5495</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.5978</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.1265</v>
+        <v>0.0478</v>
       </c>
       <c r="R40" s="26" t="n"/>
       <c r="S40" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -9863,7 +9867,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFCN23GKDG on aec-cs2-nem-ntr-2026-08-31 (short)</t>
+          <t>Auto-Buyer order C6VFCN32YKDG on aec-cs2-mouz-fal-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF40" s="31" t="n"/>
@@ -9973,7 +9977,7 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>08a9248313f04395</t>
+          <t>2888a62dd3ba4d78</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
@@ -9983,12 +9987,12 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T12:30:00Z</t>
+          <t>2026-08-31T16:30:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-cw-5s-2026-08-31</t>
+          <t>aec-cs2-fut-vit-2026-08-31</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -9998,12 +10002,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>5star</t>
+          <t>Vitality</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>Chinggis Warriors</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -10013,7 +10017,7 @@
       </c>
       <c r="I41" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J41" s="25" t="n"/>
@@ -10023,24 +10027,24 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>-122</v>
+        <v>-213</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>1.8197</v>
+        <v>1.4695</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.5305</v>
+        <v>0.6805</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.9538</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.0624</v>
+        <v>0.2738</v>
       </c>
       <c r="R41" s="26" t="n"/>
       <c r="S41" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -10049,12 +10053,12 @@
       </c>
       <c r="U41" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
+          <t>open</t>
         </is>
       </c>
       <c r="V41" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>open</t>
         </is>
       </c>
       <c r="W41" s="26" t="n"/>
@@ -10064,16 +10068,12 @@
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
       <c r="AC41" s="30" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AD41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T16:02:25.134027Z</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFNHBQEKDJ on aec-cs2-cw-5s-2026-08-31 (long)</t>
+          <t>Auto-Buyer order C6VGABPXTKDK on aec-cs2-fut-vit-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF41" s="31" t="n"/>
@@ -10183,7 +10183,7 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>10fe43507a894dff</t>
+          <t>7a9087c46a114e9c</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T14:00:00Z</t>
+          <t>2026-08-31T17:00:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-mouz-fal-2026-08-31</t>
+          <t>aec-cs2-hon-sawy-2026-08-31</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>SAW Youngsters</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I42" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J42" s="25" t="n"/>
@@ -10233,24 +10233,24 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-122</v>
+        <v>-100</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.8197</v>
+        <v>2</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.5495</v>
+        <v>0.5</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.5978</v>
+        <v>0.5755</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.0478</v>
+        <v>0.0755</v>
       </c>
       <c r="R42" s="26" t="n"/>
       <c r="S42" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VFCN32YKDG on aec-cs2-mouz-fal-2026-08-31 (short)</t>
+          <t>Auto-Buyer order C6VGABQ8AKDK on aec-cs2-hon-sawy-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF42" s="31" t="n"/>
@@ -10389,37 +10389,37 @@
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>2888a62dd3ba4d78</t>
+          <t>48cccc66566349ce</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:52:35.718859Z</t>
+          <t>2026-08-31T05:28:12.217545Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:30:00Z</t>
+          <t>2026-08-31T18:05:00-0400</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-fut-vit-2026-08-31</t>
+          <t>aec-mlb-sf-atl-2026-08-31</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Vitality</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>FUT Esports</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="I43" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J43" s="25" t="n"/>
@@ -10439,28 +10439,28 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-213</v>
+        <v>-150</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.4695</v>
+        <v>1.6667</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.6805</v>
+        <v>0.6</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.9538</v>
+        <v>0.6571</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.2738</v>
+        <v>0.0521</v>
       </c>
       <c r="R43" s="26" t="n"/>
       <c r="S43" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U43" s="24" t="inlineStr">
@@ -10485,7 +10485,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABPXTKDK on aec-cs2-fut-vit-2026-08-31 (short)</t>
+          <t>Auto-Buyer order C6VZ1TQF4KDJ on aec-mlb-sf-atl-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF43" s="31" t="n"/>
@@ -10595,37 +10595,37 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>7a9087c46a114e9c</t>
+          <t>d972531055904f04</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:52:35.718859Z</t>
+          <t>2026-08-31T05:28:12.217545Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T17:00:00Z</t>
+          <t>2026-08-31T19:40:00-0400</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-hon-sawy-2026-08-31</t>
+          <t>aec-mlb-det-min-2026-08-31</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>SAW Youngsters</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J44" s="25" t="n"/>
@@ -10645,28 +10645,28 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-100</v>
+        <v>117</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.5</v>
+        <v>0.4545</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.5755</v>
+        <v>0.5224</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.0755</v>
+        <v>0.0674</v>
       </c>
       <c r="R44" s="26" t="n"/>
       <c r="S44" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U44" s="24" t="inlineStr">
@@ -10691,7 +10691,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VGABQ8AKDK on aec-cs2-hon-sawy-2026-08-31 (long)</t>
+          <t>Auto-Buyer order C6W0RWB0MKDH on aec-mlb-det-min-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF44" s="31" t="n"/>
@@ -10801,22 +10801,22 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>48cccc66566349ce</t>
+          <t>26a05e27c35344e1</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T05:28:12.217545Z</t>
+          <t>2026-08-31T16:12:42.599391Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:05:00-0400</t>
+          <t>2026-08-31T20:40:00-0400</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>aec-mlb-sf-atl-2026-08-31</t>
+          <t>aec-mlb-bal-col-2026-08-31</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J45" s="25" t="n"/>
@@ -10851,20 +10851,20 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-150</v>
+        <v>-127</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.6667</v>
+        <v>1.7874</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5595</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.6571</v>
+        <v>0.5982</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>0.0521</v>
+        <v>0.0382</v>
       </c>
       <c r="R45" s="26" t="n"/>
       <c r="S45" s="29" t="n">
@@ -10897,7 +10897,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6VZ1TQF4KDJ on aec-mlb-sf-atl-2026-08-31 (short)</t>
+          <t>Auto-Buyer order C75CWYPPPKDC on aec-mlb-bal-col-2026-08-31 (long)</t>
         </is>
       </c>
       <c r="AF45" s="31" t="n"/>
@@ -11007,22 +11007,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>d972531055904f04</t>
+          <t>7ee8b96d25fc46af</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T05:28:12.217545Z</t>
+          <t>2026-08-31T19:34:36.451981Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:40:00-0400</t>
+          <t>2026-08-31T22:05Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>aec-mlb-det-min-2026-08-31</t>
+          <t>401878657</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -11032,53 +11032,59 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>8.5</v>
+      </c>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.4545</v>
+        <v>0.4505</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.5224</v>
-      </c>
-      <c r="P46" s="28" t="n"/>
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="P46" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" s="28" t="n">
-        <v>0.0674</v>
-      </c>
-      <c r="R46" s="26" t="n"/>
+        <v>0.1135</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="S46" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>mlb-structural-v10-frozen</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
@@ -11086,27 +11092,29 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V46" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+      <c r="V46" s="24" t="n"/>
       <c r="W46" s="26" t="n"/>
       <c r="X46" s="26" t="n"/>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="AC46" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C6W0RWB0MKDH on aec-mlb-det-min-2026-08-31 (long)</t>
-        </is>
-      </c>
-      <c r="AF46" s="31" t="n"/>
+          <t>Auto-Buyer order V10D71C79953 (1.0 sh @ $0.45) on tsc-mlb-sf-atl-2026-08-31-8pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Auto-executed Polymarket US order</t>
+        </is>
+      </c>
       <c r="AG46" s="24" t="n"/>
       <c r="AH46" s="24" t="n"/>
       <c r="AI46" s="31" t="n"/>
@@ -11213,22 +11221,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>26a05e27c35344e1</t>
+          <t>37aaf37c09f84e3f</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
+          <t>2026-08-31T19:34:36.590960Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T20:40:00-0400</t>
+          <t>2026-08-31T23:40Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>aec-mlb-bal-col-2026-08-31</t>
+          <t>401816754</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -11238,53 +11246,59 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n">
+        <v>9.5</v>
+      </c>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-127</v>
+        <v>-102</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.7874</v>
+        <v>1.9804</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.5595</v>
+        <v>0.505</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.5982</v>
-      </c>
-      <c r="P47" s="28" t="n"/>
+        <v>0.5755</v>
+      </c>
+      <c r="P47" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" s="28" t="n">
-        <v>0.0382</v>
-      </c>
-      <c r="R47" s="26" t="n"/>
+        <v>0.0706</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>mlb-structural-v10-frozen</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
@@ -11292,27 +11306,29 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V47" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+      <c r="V47" s="24" t="n"/>
       <c r="W47" s="26" t="n"/>
       <c r="X47" s="26" t="n"/>
       <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="AC47" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75CWYPPPKDC on aec-mlb-bal-col-2026-08-31 (long)</t>
-        </is>
-      </c>
-      <c r="AF47" s="31" t="n"/>
+          <t>Auto-Buyer order V101066144C4 (1.0 sh @ $0.50) on tsc-mlb-mil-chc-2026-08-31-9pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Auto-executed Polymarket US order</t>
+        </is>
+      </c>
       <c r="AG47" s="24" t="n"/>
       <c r="AH47" s="24" t="n"/>
       <c r="AI47" s="31" t="n"/>
@@ -11419,7 +11435,7 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>7ee8b96d25fc46af</t>
+          <t>816e58389cba4c61</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
@@ -11429,37 +11445,37 @@
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T22:05Z</t>
+          <t>2026-08-31T19:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-sf-atl-2026-08-31-8pt5</t>
+          <t>aec-wta-vikgol-diapar-2026-08-30</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>TENNIS</t>
         </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Diane Parry</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J48" s="25" t="n"/>
@@ -11469,20 +11485,20 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>2.22</v>
+        <v>1.9259</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.4505</v>
+        <v>0.5192</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5579</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.0576</v>
+        <v>0.0379</v>
       </c>
       <c r="R48" s="26" t="n"/>
       <c r="S48" s="29" t="n">
@@ -11490,7 +11506,7 @@
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>tennis-surface-elo-v1</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -11515,7 +11531,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75E2V3VPKDH on tsc-mlb-sf-atl-2026-08-31-8pt5 (short)</t>
+          <t>Auto-Buyer order C75DSQ4KAKDM on aec-wta-vikgol-diapar-2026-08-30 (short)</t>
         </is>
       </c>
       <c r="AF48" s="31" t="n"/>
@@ -11625,7 +11641,7 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>8e234c9a1aa54341</t>
+          <t>b214bda284bc4f41</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
@@ -11635,37 +11651,37 @@
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T22:40Z</t>
+          <t>2026-08-31T19:00:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-nym-tb-2026-08-31-8pt5</t>
+          <t>aec-cs2-dam-zge-2026-08-31</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Zetta Games</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J49" s="25" t="n"/>
@@ -11675,28 +11691,28 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>2.13</v>
+        <v>3.12</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.4695</v>
+        <v>0.3205</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.5185</v>
+        <v>0.5642</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.0485</v>
+        <v>0.2442</v>
       </c>
       <c r="R49" s="26" t="n"/>
       <c r="S49" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
@@ -11721,7 +11737,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75E2V4FEKDH on tsc-mlb-nym-tb-2026-08-31-8pt5 (long)</t>
+          <t>Auto-Buyer order C75ED9T52KDF on aec-cs2-dam-zge-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF49" s="31" t="n"/>
@@ -11831,7 +11847,7 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>37aaf37c09f84e3f</t>
+          <t>fd008ef45af2480d</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
@@ -11841,37 +11857,37 @@
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T23:40Z</t>
+          <t>2026-08-31T22:00:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-mil-chc-2026-08-31-9pt5</t>
+          <t>aec-cs2-mm-sdm-2026-08-31</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Semente do Mal</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Mansão Maromba</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J50" s="25" t="n"/>
@@ -11881,28 +11897,28 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-104</v>
+        <v>212</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.9615</v>
+        <v>3.12</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.505</v>
+        <v>0.3205</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.5448</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.0398</v>
+        <v>0.1866</v>
       </c>
       <c r="R50" s="26" t="n"/>
       <c r="S50" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -11927,7 +11943,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75E1JWMRKDG on tsc-mlb-mil-chc-2026-08-31-9pt5 (short)</t>
+          <t>Auto-Buyer order C75CWYWSTKDC on aec-cs2-mm-sdm-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF50" s="31" t="n"/>
@@ -12037,22 +12053,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8651501eb94f43b2</t>
+          <t>970da3eec9e24614</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
+          <t>2026-08-31T19:34:36.729957Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T01:38Z</t>
+          <t>2026-09-01T00:40Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>tsc-mlb-nyy-laa-2026-08-31-8pt5</t>
+          <t>401816755</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -12062,12 +12078,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -12077,10 +12093,12 @@
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n">
+        <v>10.5</v>
+      </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12096,19 +12114,23 @@
         <v>0.4695</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="P51" s="28" t="n"/>
+        <v>0.5296</v>
+      </c>
+      <c r="P51" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" s="28" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="R51" s="26" t="n"/>
+        <v>0.0601</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="S51" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>mlb-structural-v10-frozen</t>
         </is>
       </c>
       <c r="U51" s="24" t="inlineStr">
@@ -12116,27 +12138,29 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+      <c r="V51" s="24" t="n"/>
       <c r="W51" s="26" t="n"/>
       <c r="X51" s="26" t="n"/>
       <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="AC51" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75D7932RKDD on tsc-mlb-nyy-laa-2026-08-31-8pt5 (long)</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="n"/>
+          <t>Auto-Buyer order V105A22EB006 (1.0 sh @ $0.47) on tsc-mlb-bal-col-2026-08-31-10pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Auto-executed Polymarket US order</t>
+        </is>
+      </c>
       <c r="AG51" s="24" t="n"/>
       <c r="AH51" s="24" t="n"/>
       <c r="AI51" s="31" t="n"/>
@@ -12240,624 +12264,6 @@
       <c r="DO51" s="24" t="n"/>
       <c r="DP51" s="24" t="n"/>
     </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>816e58389cba4c61</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T19:00Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>aec-wta-vikgol-diapar-2026-08-30</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>TENNIS</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>Diane Parry</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Viktorija Golubic</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>1.9259</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.5579</v>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n">
-        <v>0.0379</v>
-      </c>
-      <c r="R52" s="26" t="n"/>
-      <c r="S52" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>tennis-surface-elo-v1</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Auto-Buyer order C75DSQ4KAKDM on aec-wta-vikgol-diapar-2026-08-30 (short)</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="n"/>
-      <c r="AG52" s="24" t="n"/>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="n"/>
-      <c r="AL52" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>take</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>AUTO_BUYER_EXECUTION</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="n"/>
-      <c r="AQ52" s="24" t="n"/>
-      <c r="AR52" s="24" t="n"/>
-      <c r="AS52" s="24" t="n"/>
-      <c r="AT52" s="24" t="n"/>
-      <c r="AU52" s="24" t="n"/>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="n"/>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="n"/>
-      <c r="BA52" s="24" t="n"/>
-      <c r="BB52" s="24" t="n"/>
-      <c r="BC52" s="24" t="n"/>
-      <c r="BD52" s="24" t="n"/>
-      <c r="BE52" s="24" t="n"/>
-      <c r="BF52" s="24" t="n"/>
-      <c r="BG52" s="24" t="n"/>
-      <c r="BH52" s="24" t="n"/>
-      <c r="BI52" s="24" t="n"/>
-      <c r="BJ52" s="25" t="n"/>
-      <c r="BK52" s="26" t="n"/>
-      <c r="BL52" s="27" t="n"/>
-      <c r="BM52" s="28" t="n"/>
-      <c r="BN52" s="28" t="n"/>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-      <c r="CN52" s="24" t="n"/>
-      <c r="CO52" s="24" t="n"/>
-      <c r="CP52" s="24" t="n"/>
-      <c r="CQ52" s="24" t="n"/>
-      <c r="CR52" s="24" t="n"/>
-      <c r="CS52" s="24" t="n"/>
-      <c r="CT52" s="24" t="n"/>
-      <c r="CU52" s="24" t="n"/>
-      <c r="CV52" s="24" t="n"/>
-      <c r="CW52" s="24" t="n"/>
-      <c r="CX52" s="24" t="n"/>
-      <c r="CY52" s="24" t="n"/>
-      <c r="CZ52" s="24" t="n"/>
-      <c r="DA52" s="24" t="n"/>
-      <c r="DB52" s="24" t="n"/>
-      <c r="DC52" s="24" t="n"/>
-      <c r="DD52" s="24" t="n"/>
-      <c r="DE52" s="24" t="n"/>
-      <c r="DF52" s="24" t="n"/>
-      <c r="DG52" s="24" t="n"/>
-      <c r="DH52" s="24" t="n"/>
-      <c r="DI52" s="24" t="n"/>
-      <c r="DJ52" s="24" t="n"/>
-      <c r="DK52" s="24" t="n"/>
-      <c r="DL52" s="24" t="n"/>
-      <c r="DM52" s="24" t="n"/>
-      <c r="DN52" s="24" t="n"/>
-      <c r="DO52" s="24" t="n"/>
-      <c r="DP52" s="24" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>b214bda284bc4f41</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>aec-cs2-dam-zge-2026-08-31</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>Zetta Games</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>Damajuana</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n"/>
-      <c r="K53" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>212</v>
-      </c>
-      <c r="M53" s="27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.3205</v>
-      </c>
-      <c r="O53" s="28" t="n">
-        <v>0.5642</v>
-      </c>
-      <c r="P53" s="28" t="n"/>
-      <c r="Q53" s="28" t="n">
-        <v>0.2442</v>
-      </c>
-      <c r="R53" s="26" t="n"/>
-      <c r="S53" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="26" t="n"/>
-      <c r="AA53" s="28" t="n"/>
-      <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="24" t="n"/>
-      <c r="AE53" s="31" t="inlineStr">
-        <is>
-          <t>Auto-Buyer order C75ED9T52KDF on aec-cs2-dam-zge-2026-08-31 (short)</t>
-        </is>
-      </c>
-      <c r="AF53" s="31" t="n"/>
-      <c r="AG53" s="24" t="n"/>
-      <c r="AH53" s="24" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="24" t="n"/>
-      <c r="AL53" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM53" s="24" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="AN53" s="24" t="inlineStr">
-        <is>
-          <t>take</t>
-        </is>
-      </c>
-      <c r="AO53" s="24" t="inlineStr">
-        <is>
-          <t>AUTO_BUYER_EXECUTION</t>
-        </is>
-      </c>
-      <c r="AP53" s="24" t="n"/>
-      <c r="AQ53" s="24" t="n"/>
-      <c r="AR53" s="24" t="n"/>
-      <c r="AS53" s="24" t="n"/>
-      <c r="AT53" s="24" t="n"/>
-      <c r="AU53" s="24" t="n"/>
-      <c r="AV53" s="24" t="n"/>
-      <c r="AW53" s="24" t="n"/>
-      <c r="AX53" s="24" t="n"/>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="n"/>
-      <c r="BA53" s="24" t="n"/>
-      <c r="BB53" s="24" t="n"/>
-      <c r="BC53" s="24" t="n"/>
-      <c r="BD53" s="24" t="n"/>
-      <c r="BE53" s="24" t="n"/>
-      <c r="BF53" s="24" t="n"/>
-      <c r="BG53" s="24" t="n"/>
-      <c r="BH53" s="24" t="n"/>
-      <c r="BI53" s="24" t="n"/>
-      <c r="BJ53" s="25" t="n"/>
-      <c r="BK53" s="26" t="n"/>
-      <c r="BL53" s="27" t="n"/>
-      <c r="BM53" s="28" t="n"/>
-      <c r="BN53" s="28" t="n"/>
-      <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
-      <c r="BR53" s="28" t="n"/>
-      <c r="BS53" s="28" t="n"/>
-      <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
-      <c r="BV53" s="29" t="n"/>
-      <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
-      <c r="BZ53" s="24" t="n"/>
-      <c r="CA53" s="31" t="n"/>
-      <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
-      <c r="CG53" s="24" t="n"/>
-      <c r="CH53" s="24" t="n"/>
-      <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
-      <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
-      <c r="CN53" s="24" t="n"/>
-      <c r="CO53" s="24" t="n"/>
-      <c r="CP53" s="24" t="n"/>
-      <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="n"/>
-      <c r="CS53" s="24" t="n"/>
-      <c r="CT53" s="24" t="n"/>
-      <c r="CU53" s="24" t="n"/>
-      <c r="CV53" s="24" t="n"/>
-      <c r="CW53" s="24" t="n"/>
-      <c r="CX53" s="24" t="n"/>
-      <c r="CY53" s="24" t="n"/>
-      <c r="CZ53" s="24" t="n"/>
-      <c r="DA53" s="24" t="n"/>
-      <c r="DB53" s="24" t="n"/>
-      <c r="DC53" s="24" t="n"/>
-      <c r="DD53" s="24" t="n"/>
-      <c r="DE53" s="24" t="n"/>
-      <c r="DF53" s="24" t="n"/>
-      <c r="DG53" s="24" t="n"/>
-      <c r="DH53" s="24" t="n"/>
-      <c r="DI53" s="24" t="n"/>
-      <c r="DJ53" s="24" t="n"/>
-      <c r="DK53" s="24" t="n"/>
-      <c r="DL53" s="24" t="n"/>
-      <c r="DM53" s="24" t="n"/>
-      <c r="DN53" s="24" t="n"/>
-      <c r="DO53" s="24" t="n"/>
-      <c r="DP53" s="24" t="n"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>fd008ef45af2480d</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-31T22:00:00Z</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>aec-cs2-mm-sdm-2026-08-31</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>Semente do Mal</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>Mansão Maromba</t>
-        </is>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>212</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N54" s="28" t="n">
-        <v>0.3205</v>
-      </c>
-      <c r="O54" s="28" t="n">
-        <v>0.5066000000000001</v>
-      </c>
-      <c r="P54" s="28" t="n"/>
-      <c r="Q54" s="28" t="n">
-        <v>0.1866</v>
-      </c>
-      <c r="R54" s="26" t="n"/>
-      <c r="S54" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W54" s="26" t="n"/>
-      <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="25" t="n"/>
-      <c r="Z54" s="26" t="n"/>
-      <c r="AA54" s="28" t="n"/>
-      <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="24" t="n"/>
-      <c r="AE54" s="31" t="inlineStr">
-        <is>
-          <t>Auto-Buyer order C75CWYWSTKDC on aec-cs2-mm-sdm-2026-08-31 (short)</t>
-        </is>
-      </c>
-      <c r="AF54" s="31" t="n"/>
-      <c r="AG54" s="24" t="n"/>
-      <c r="AH54" s="24" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="31" t="n"/>
-      <c r="AK54" s="24" t="n"/>
-      <c r="AL54" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM54" s="24" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="AN54" s="24" t="inlineStr">
-        <is>
-          <t>take</t>
-        </is>
-      </c>
-      <c r="AO54" s="24" t="inlineStr">
-        <is>
-          <t>AUTO_BUYER_EXECUTION</t>
-        </is>
-      </c>
-      <c r="AP54" s="24" t="n"/>
-      <c r="AQ54" s="24" t="n"/>
-      <c r="AR54" s="24" t="n"/>
-      <c r="AS54" s="24" t="n"/>
-      <c r="AT54" s="24" t="n"/>
-      <c r="AU54" s="24" t="n"/>
-      <c r="AV54" s="24" t="n"/>
-      <c r="AW54" s="24" t="n"/>
-      <c r="AX54" s="24" t="n"/>
-      <c r="AY54" s="24" t="n"/>
-      <c r="AZ54" s="24" t="n"/>
-      <c r="BA54" s="24" t="n"/>
-      <c r="BB54" s="24" t="n"/>
-      <c r="BC54" s="24" t="n"/>
-      <c r="BD54" s="24" t="n"/>
-      <c r="BE54" s="24" t="n"/>
-      <c r="BF54" s="24" t="n"/>
-      <c r="BG54" s="24" t="n"/>
-      <c r="BH54" s="24" t="n"/>
-      <c r="BI54" s="24" t="n"/>
-      <c r="BJ54" s="25" t="n"/>
-      <c r="BK54" s="26" t="n"/>
-      <c r="BL54" s="27" t="n"/>
-      <c r="BM54" s="28" t="n"/>
-      <c r="BN54" s="28" t="n"/>
-      <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
-      <c r="BR54" s="28" t="n"/>
-      <c r="BS54" s="28" t="n"/>
-      <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
-      <c r="BV54" s="29" t="n"/>
-      <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
-      <c r="BZ54" s="24" t="n"/>
-      <c r="CA54" s="31" t="n"/>
-      <c r="CB54" s="24" t="n"/>
-      <c r="CC54" s="24" t="n"/>
-      <c r="CD54" s="24" t="n"/>
-      <c r="CE54" s="24" t="n"/>
-      <c r="CF54" s="24" t="n"/>
-      <c r="CG54" s="24" t="n"/>
-      <c r="CH54" s="24" t="n"/>
-      <c r="CI54" s="24" t="n"/>
-      <c r="CJ54" s="24" t="n"/>
-      <c r="CK54" s="24" t="n"/>
-      <c r="CL54" s="24" t="n"/>
-      <c r="CM54" s="24" t="n"/>
-      <c r="CN54" s="24" t="n"/>
-      <c r="CO54" s="24" t="n"/>
-      <c r="CP54" s="24" t="n"/>
-      <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="n"/>
-      <c r="CS54" s="24" t="n"/>
-      <c r="CT54" s="24" t="n"/>
-      <c r="CU54" s="24" t="n"/>
-      <c r="CV54" s="24" t="n"/>
-      <c r="CW54" s="24" t="n"/>
-      <c r="CX54" s="24" t="n"/>
-      <c r="CY54" s="24" t="n"/>
-      <c r="CZ54" s="24" t="n"/>
-      <c r="DA54" s="24" t="n"/>
-      <c r="DB54" s="24" t="n"/>
-      <c r="DC54" s="24" t="n"/>
-      <c r="DD54" s="24" t="n"/>
-      <c r="DE54" s="24" t="n"/>
-      <c r="DF54" s="24" t="n"/>
-      <c r="DG54" s="24" t="n"/>
-      <c r="DH54" s="24" t="n"/>
-      <c r="DI54" s="24" t="n"/>
-      <c r="DJ54" s="24" t="n"/>
-      <c r="DK54" s="24" t="n"/>
-      <c r="DL54" s="24" t="n"/>
-      <c r="DM54" s="24" t="n"/>
-      <c r="DN54" s="24" t="n"/>
-      <c r="DO54" s="24" t="n"/>
-      <c r="DP54" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/auto_buyer_picks.xlsx
+++ b/data/auto_buyer_picks.xlsx
@@ -7357,24 +7357,30 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W28" s="26" t="n"/>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X28" s="26" t="n"/>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
       <c r="AC28" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="24" t="n"/>
+        <v>-2</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:58:20.483072Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C6VFNH8ZYKDJ on aec-wta-tamzid-martim-2026-08-30 (long)</t>
@@ -7981,24 +7987,30 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W31" s="26" t="n"/>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X31" s="26" t="n"/>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
       <c r="AC31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="24" t="n"/>
+        <v>0.31</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:58:20.483072Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C6VGABM5CKDK on aec-atp-romsaf-caralc-2026-08-30 (short)</t>
@@ -8393,24 +8405,30 @@
       </c>
       <c r="U33" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V33" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
       <c r="AC33" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="24" t="n"/>
+        <v>1.04</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:58:20.483072Z</t>
+        </is>
+      </c>
       <c r="AE33" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C6VF7S7KGKDM on aec-atp-jurrod-gioper-2026-08-30 (long)</t>
@@ -11007,84 +11025,78 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>7ee8b96d25fc46af</t>
+          <t>816e58389cba4c61</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:34:36.451981Z</t>
+          <t>2026-08-31T16:12:42.599391Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T22:05Z</t>
+          <t>2026-08-31T19:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>401878657</t>
+          <t>aec-wta-vikgol-diapar-2026-08-30</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>TENNIS</t>
         </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Diane Parry</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Viktorija Golubic</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n">
-        <v>8.5</v>
-      </c>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>2.22</v>
+        <v>1.9259</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.4505</v>
+        <v>0.5192</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="P46" s="28" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5579</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="R46" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0379</v>
+      </c>
+      <c r="R46" s="26" t="n"/>
       <c r="S46" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>mlb-structural-v10-frozen</t>
+          <t>tennis-surface-elo-v1</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
@@ -11092,29 +11104,27 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V46" s="24" t="n"/>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="W46" s="26" t="n"/>
       <c r="X46" s="26" t="n"/>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB46" s="28" t="n"/>
       <c r="AC46" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order V10D71C79953 (1.0 sh @ $0.45) on tsc-mlb-sf-atl-2026-08-31-8pt5 (short)</t>
-        </is>
-      </c>
-      <c r="AF46" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C75DSQ4KAKDM on aec-wta-vikgol-diapar-2026-08-30 (short)</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="n"/>
       <c r="AG46" s="24" t="n"/>
       <c r="AH46" s="24" t="n"/>
       <c r="AI46" s="31" t="n"/>
@@ -11221,84 +11231,78 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>37aaf37c09f84e3f</t>
+          <t>b214bda284bc4f41</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:34:36.590960Z</t>
+          <t>2026-08-31T16:12:42.599391Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T23:40Z</t>
+          <t>2026-08-31T19:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>401816754</t>
+          <t>aec-cs2-dam-zge-2026-08-31</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Zetta Games</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Damajuana</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n">
-        <v>9.5</v>
-      </c>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-102</v>
+        <v>212</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.9804</v>
+        <v>3.12</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.505</v>
+        <v>0.3205</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.5755</v>
-      </c>
-      <c r="P47" s="28" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5642</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>0.0706</v>
-      </c>
-      <c r="R47" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2442</v>
+      </c>
+      <c r="R47" s="26" t="n"/>
       <c r="S47" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>mlb-structural-v10-frozen</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
@@ -11306,29 +11310,27 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V47" s="24" t="n"/>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="W47" s="26" t="n"/>
       <c r="X47" s="26" t="n"/>
       <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB47" s="28" t="n"/>
       <c r="AC47" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order V101066144C4 (1.0 sh @ $0.50) on tsc-mlb-mil-chc-2026-08-31-9pt5 (short)</t>
-        </is>
-      </c>
-      <c r="AF47" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order C75ED9T52KDF on aec-cs2-dam-zge-2026-08-31 (short)</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="n"/>
       <c r="AG47" s="24" t="n"/>
       <c r="AH47" s="24" t="n"/>
       <c r="AI47" s="31" t="n"/>
@@ -11435,7 +11437,7 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>816e58389cba4c61</t>
+          <t>fd008ef45af2480d</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
@@ -11445,27 +11447,27 @@
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:00Z</t>
+          <t>2026-08-31T22:00:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>aec-wta-vikgol-diapar-2026-08-30</t>
+          <t>aec-cs2-mm-sdm-2026-08-31</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>TENNIS</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Diane Parry</t>
+          <t>Semente do Mal</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Viktorija Golubic</t>
+          <t>Mansão Maromba</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -11485,28 +11487,28 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-108</v>
+        <v>212</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.9259</v>
+        <v>3.12</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.5192</v>
+        <v>0.3205</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.5579</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.0379</v>
+        <v>0.1866</v>
       </c>
       <c r="R48" s="26" t="n"/>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>tennis-surface-elo-v1</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -11531,7 +11533,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75DSQ4KAKDM on aec-wta-vikgol-diapar-2026-08-30 (short)</t>
+          <t>Auto-Buyer order C75CWYWSTKDC on aec-cs2-mm-sdm-2026-08-31 (short)</t>
         </is>
       </c>
       <c r="AF48" s="31" t="n"/>
@@ -11641,47 +11643,47 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>b214bda284bc4f41</t>
+          <t>7ee8b96d25fc46af</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
+          <t>2026-08-31T19:34:36.451981Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:00:00Z</t>
+          <t>2026-08-31T22:05Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-dam-zge-2026-08-31</t>
+          <t>tsc-mlb-sf-atl-2026-08-31-8pt5</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Zetta Games</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Damajuana</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J49" s="25" t="n"/>
@@ -11691,28 +11693,28 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>3.12</v>
+        <v>2.22</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.3205</v>
+        <v>0.4505</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.5642</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.2442</v>
+        <v>0.1135</v>
       </c>
       <c r="R49" s="26" t="n"/>
       <c r="S49" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>mlb-structural-v10-frozen</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
@@ -11737,7 +11739,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75ED9T52KDF on aec-cs2-dam-zge-2026-08-31 (short)</t>
+          <t>Auto-Buyer order V10D71C79953 on tsc-mlb-sf-atl-2026-08-31-8pt5 (short)</t>
         </is>
       </c>
       <c r="AF49" s="31" t="n"/>
@@ -11847,47 +11849,47 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>fd008ef45af2480d</t>
+          <t>37aaf37c09f84e3f</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:12:42.599391Z</t>
+          <t>2026-08-31T19:34:36.590960Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T22:00:00Z</t>
+          <t>2026-08-31T23:40Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>aec-cs2-mm-sdm-2026-08-31</t>
+          <t>tsc-mlb-mil-chc-2026-08-31-9pt5</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Semente do Mal</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Mansão Maromba</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J50" s="25" t="n"/>
@@ -11897,28 +11899,28 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>212</v>
+        <v>-102</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>3.12</v>
+        <v>1.9804</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.3205</v>
+        <v>0.505</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5755</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.1866</v>
+        <v>0.0706</v>
       </c>
       <c r="R50" s="26" t="n"/>
       <c r="S50" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v6</t>
+          <t>mlb-structural-v10-frozen</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -11943,7 +11945,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order C75CWYWSTKDC on aec-cs2-mm-sdm-2026-08-31 (short)</t>
+          <t>Auto-Buyer order V101066144C4 on tsc-mlb-mil-chc-2026-08-31-9pt5 (short)</t>
         </is>
       </c>
       <c r="AF50" s="31" t="n"/>
@@ -12068,7 +12070,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>401816755</t>
+          <t>tsc-mlb-bal-col-2026-08-31-10pt5</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -12096,9 +12098,7 @@
           <t>under</t>
         </is>
       </c>
-      <c r="J51" s="25" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J51" s="25" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12116,15 +12116,11 @@
       <c r="O51" s="28" t="n">
         <v>0.5296</v>
       </c>
-      <c r="P51" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
         <v>0.0601</v>
       </c>
-      <c r="R51" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R51" s="26" t="n"/>
       <c r="S51" s="29" t="n">
         <v>1.25</v>
       </c>
@@ -12138,29 +12134,27 @@
           <t>open</t>
         </is>
       </c>
-      <c r="V51" s="24" t="n"/>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="W51" s="26" t="n"/>
       <c r="X51" s="26" t="n"/>
       <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB51" s="28" t="n"/>
       <c r="AC51" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Auto-Buyer order V105A22EB006 (1.0 sh @ $0.47) on tsc-mlb-bal-col-2026-08-31-10pt5 (short)</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Auto-executed Polymarket US order</t>
-        </is>
-      </c>
+          <t>Auto-Buyer order V105A22EB006 on tsc-mlb-bal-col-2026-08-31-10pt5 (short)</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="n"/>
       <c r="AG51" s="24" t="n"/>
       <c r="AH51" s="24" t="n"/>
       <c r="AI51" s="31" t="n"/>

--- a/data/auto_buyer_picks.xlsx
+++ b/data/auto_buyer_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP103" headerRowCount="1">
-  <autoFilter ref="A1:DP103"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP122" headerRowCount="1">
+  <autoFilter ref="A1:DP122"/>
   <tableColumns count="120">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -779,19 +779,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$103)</f>
+        <f>COUNTA('Picks'!$A$2:$A$122)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$103,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$122,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$103,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$122,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"win")+COUNTIFS('Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")+COUNTIFS('Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$103,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$122,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$103,"&gt;0",'Picks'!$V$2:$V$103,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$103,"&gt;0",'Picks'!$V$2:$V$103,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$103,"&gt;0",'Picks'!$V$2:$V$103,"win")/(COUNTIFS('Picks'!$BX$2:$BX$103,"&gt;0",'Picks'!$V$2:$V$103,"win")+COUNTIFS('Picks'!$BX$2:$BX$103,"&gt;0",'Picks'!$V$2:$V$103,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")/(COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")+COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$103)/SUM('Picks'!$BX$2:$BX$103),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$122)/SUM('Picks'!$BX$2:$BX$122),0)</f>
         <v/>
       </c>
     </row>
@@ -859,19 +859,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$103)</f>
+        <f>SUM('Picks'!$BY$2:$BY$122)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$103,"&lt;&gt;",'Picks'!$AB$2:$AB$103),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$122,"&lt;&gt;",'Picks'!$AB$2:$AB$122),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$103,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$103,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$122,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$122,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$103,'Picks'!$AM$2:$AM$103,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$122,'Picks'!$AM$2:$AM$122,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A14,'Picks'!$U$2:$U$103,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A14,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A14,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -942,11 +942,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$103,'Picks'!$H$2:$H$103,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$103,'Picks'!$H$2:$H$103,$A14,'Picks'!$U$2:$U$103,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -957,15 +957,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A15,'Picks'!$U$2:$U$103,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A15,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A15,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -973,11 +973,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$103,'Picks'!$H$2:$H$103,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$103,'Picks'!$H$2:$H$103,$A15,'Picks'!$U$2:$U$103,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -988,15 +988,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A16,'Picks'!$U$2:$U$103,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A16,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$103,$A16,'Picks'!$U$2:$U$103,"settled",'Picks'!$V$2:$V$103,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1004,11 +1004,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$103,'Picks'!$H$2:$H$103,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$103,'Picks'!$H$2:$H$103,$A16,'Picks'!$U$2:$U$103,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DP103"/>
+  <dimension ref="A1:DP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="U95" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V95" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W95" s="26" t="n"/>
@@ -21482,9 +21482,13 @@
       <c r="AA95" s="28" t="n"/>
       <c r="AB95" s="28" t="n"/>
       <c r="AC95" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD95" s="24" t="n"/>
+        <v>1.22</v>
+      </c>
+      <c r="AD95" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
       <c r="AE95" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8EPAWWCYMVK on aec-cs2-is-nemi-2026-09-03 (short)</t>
@@ -23135,12 +23139,12 @@
       </c>
       <c r="U103" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V103" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W103" s="26" t="n"/>
@@ -23150,9 +23154,13 @@
       <c r="AA103" s="28" t="n"/>
       <c r="AB103" s="28" t="n"/>
       <c r="AC103" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="24" t="n"/>
+        <v>-1.02</v>
+      </c>
+      <c r="AD103" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
       <c r="AE103" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8EQT1EM2MVG on aec-cs2-sin-fokus-2026-09-03 (long)</t>
@@ -23262,6 +23270,3944 @@
       <c r="DO103" s="24" t="n"/>
       <c r="DP103" s="24" t="n"/>
     </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>12fa89f6e495470b</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T01:00Z</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>aec-wta-jesman-eleryb-2026-09-02</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>Jessica Bouzas Maneiro</t>
+        </is>
+      </c>
+      <c r="H104" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I104" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J104" s="25" t="n"/>
+      <c r="K104" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L104" s="26" t="n">
+        <v>-525</v>
+      </c>
+      <c r="M104" s="27" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="N104" s="28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O104" s="28" t="n">
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="28" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="R104" s="26" t="n"/>
+      <c r="S104" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T104" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U104" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V104" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W104" s="26" t="n"/>
+      <c r="X104" s="26" t="n"/>
+      <c r="Y104" s="25" t="n"/>
+      <c r="Z104" s="26" t="n"/>
+      <c r="AA104" s="28" t="n"/>
+      <c r="AB104" s="28" t="n"/>
+      <c r="AC104" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="24" t="n"/>
+      <c r="AE104" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAC97KPMW0 on aec-wta-jesman-eleryb-2026-09-02 (short)</t>
+        </is>
+      </c>
+      <c r="AF104" s="31" t="n"/>
+      <c r="AG104" s="24" t="n"/>
+      <c r="AH104" s="24" t="n"/>
+      <c r="AI104" s="31" t="n"/>
+      <c r="AJ104" s="31" t="n"/>
+      <c r="AK104" s="24" t="n"/>
+      <c r="AL104" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM104" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN104" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO104" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP104" s="24" t="n"/>
+      <c r="AQ104" s="24" t="n"/>
+      <c r="AR104" s="24" t="n"/>
+      <c r="AS104" s="24" t="n"/>
+      <c r="AT104" s="24" t="n"/>
+      <c r="AU104" s="24" t="n"/>
+      <c r="AV104" s="24" t="n"/>
+      <c r="AW104" s="24" t="n"/>
+      <c r="AX104" s="24" t="n"/>
+      <c r="AY104" s="24" t="n"/>
+      <c r="AZ104" s="24" t="n"/>
+      <c r="BA104" s="24" t="n"/>
+      <c r="BB104" s="24" t="n"/>
+      <c r="BC104" s="24" t="n"/>
+      <c r="BD104" s="24" t="n"/>
+      <c r="BE104" s="24" t="n"/>
+      <c r="BF104" s="24" t="n"/>
+      <c r="BG104" s="24" t="n"/>
+      <c r="BH104" s="24" t="n"/>
+      <c r="BI104" s="24" t="n"/>
+      <c r="BJ104" s="25" t="n"/>
+      <c r="BK104" s="26" t="n"/>
+      <c r="BL104" s="27" t="n"/>
+      <c r="BM104" s="28" t="n"/>
+      <c r="BN104" s="28" t="n"/>
+      <c r="BO104" s="28" t="n"/>
+      <c r="BP104" s="25" t="n"/>
+      <c r="BQ104" s="27" t="n"/>
+      <c r="BR104" s="28" t="n"/>
+      <c r="BS104" s="28" t="n"/>
+      <c r="BT104" s="28" t="n"/>
+      <c r="BU104" s="25" t="n"/>
+      <c r="BV104" s="29" t="n"/>
+      <c r="BW104" s="24" t="n"/>
+      <c r="BX104" s="30" t="n"/>
+      <c r="BY104" s="27" t="n"/>
+      <c r="BZ104" s="24" t="n"/>
+      <c r="CA104" s="31" t="n"/>
+      <c r="CB104" s="24" t="n"/>
+      <c r="CC104" s="24" t="n"/>
+      <c r="CD104" s="24" t="n"/>
+      <c r="CE104" s="24" t="n"/>
+      <c r="CF104" s="24" t="n"/>
+      <c r="CG104" s="24" t="n"/>
+      <c r="CH104" s="24" t="n"/>
+      <c r="CI104" s="24" t="n"/>
+      <c r="CJ104" s="24" t="n"/>
+      <c r="CK104" s="24" t="n"/>
+      <c r="CL104" s="24" t="n"/>
+      <c r="CM104" s="24" t="n"/>
+      <c r="CN104" s="24" t="n"/>
+      <c r="CO104" s="24" t="n"/>
+      <c r="CP104" s="24" t="n"/>
+      <c r="CQ104" s="24" t="n"/>
+      <c r="CR104" s="24" t="n"/>
+      <c r="CS104" s="24" t="n"/>
+      <c r="CT104" s="24" t="n"/>
+      <c r="CU104" s="24" t="n"/>
+      <c r="CV104" s="24" t="n"/>
+      <c r="CW104" s="24" t="n"/>
+      <c r="CX104" s="24" t="n"/>
+      <c r="CY104" s="24" t="n"/>
+      <c r="CZ104" s="24" t="n"/>
+      <c r="DA104" s="24" t="n"/>
+      <c r="DB104" s="24" t="n"/>
+      <c r="DC104" s="24" t="n"/>
+      <c r="DD104" s="24" t="n"/>
+      <c r="DE104" s="24" t="n"/>
+      <c r="DF104" s="24" t="n"/>
+      <c r="DG104" s="24" t="n"/>
+      <c r="DH104" s="24" t="n"/>
+      <c r="DI104" s="24" t="n"/>
+      <c r="DJ104" s="24" t="n"/>
+      <c r="DK104" s="24" t="n"/>
+      <c r="DL104" s="24" t="n"/>
+      <c r="DM104" s="24" t="n"/>
+      <c r="DN104" s="24" t="n"/>
+      <c r="DO104" s="24" t="n"/>
+      <c r="DP104" s="24" t="n"/>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>e9bef91be0644ef4</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00Z</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-felaug-karkha-2026-09-02</t>
+        </is>
+      </c>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>Karen Khachanov</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>Felix Auger-Aliassime</t>
+        </is>
+      </c>
+      <c r="H105" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I105" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J105" s="25" t="n"/>
+      <c r="K105" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L105" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="M105" s="27" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="N105" s="28" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="O105" s="28" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="28" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="R105" s="26" t="n"/>
+      <c r="S105" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U105" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V105" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W105" s="26" t="n"/>
+      <c r="X105" s="26" t="n"/>
+      <c r="Y105" s="25" t="n"/>
+      <c r="Z105" s="26" t="n"/>
+      <c r="AA105" s="28" t="n"/>
+      <c r="AB105" s="28" t="n"/>
+      <c r="AC105" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="24" t="n"/>
+      <c r="AE105" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9JGNDPMVY on aec-atp-felaug-karkha-2026-09-02 (long)</t>
+        </is>
+      </c>
+      <c r="AF105" s="31" t="n"/>
+      <c r="AG105" s="24" t="n"/>
+      <c r="AH105" s="24" t="n"/>
+      <c r="AI105" s="31" t="n"/>
+      <c r="AJ105" s="31" t="n"/>
+      <c r="AK105" s="24" t="n"/>
+      <c r="AL105" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM105" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN105" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO105" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP105" s="24" t="n"/>
+      <c r="AQ105" s="24" t="n"/>
+      <c r="AR105" s="24" t="n"/>
+      <c r="AS105" s="24" t="n"/>
+      <c r="AT105" s="24" t="n"/>
+      <c r="AU105" s="24" t="n"/>
+      <c r="AV105" s="24" t="n"/>
+      <c r="AW105" s="24" t="n"/>
+      <c r="AX105" s="24" t="n"/>
+      <c r="AY105" s="24" t="n"/>
+      <c r="AZ105" s="24" t="n"/>
+      <c r="BA105" s="24" t="n"/>
+      <c r="BB105" s="24" t="n"/>
+      <c r="BC105" s="24" t="n"/>
+      <c r="BD105" s="24" t="n"/>
+      <c r="BE105" s="24" t="n"/>
+      <c r="BF105" s="24" t="n"/>
+      <c r="BG105" s="24" t="n"/>
+      <c r="BH105" s="24" t="n"/>
+      <c r="BI105" s="24" t="n"/>
+      <c r="BJ105" s="25" t="n"/>
+      <c r="BK105" s="26" t="n"/>
+      <c r="BL105" s="27" t="n"/>
+      <c r="BM105" s="28" t="n"/>
+      <c r="BN105" s="28" t="n"/>
+      <c r="BO105" s="28" t="n"/>
+      <c r="BP105" s="25" t="n"/>
+      <c r="BQ105" s="27" t="n"/>
+      <c r="BR105" s="28" t="n"/>
+      <c r="BS105" s="28" t="n"/>
+      <c r="BT105" s="28" t="n"/>
+      <c r="BU105" s="25" t="n"/>
+      <c r="BV105" s="29" t="n"/>
+      <c r="BW105" s="24" t="n"/>
+      <c r="BX105" s="30" t="n"/>
+      <c r="BY105" s="27" t="n"/>
+      <c r="BZ105" s="24" t="n"/>
+      <c r="CA105" s="31" t="n"/>
+      <c r="CB105" s="24" t="n"/>
+      <c r="CC105" s="24" t="n"/>
+      <c r="CD105" s="24" t="n"/>
+      <c r="CE105" s="24" t="n"/>
+      <c r="CF105" s="24" t="n"/>
+      <c r="CG105" s="24" t="n"/>
+      <c r="CH105" s="24" t="n"/>
+      <c r="CI105" s="24" t="n"/>
+      <c r="CJ105" s="24" t="n"/>
+      <c r="CK105" s="24" t="n"/>
+      <c r="CL105" s="24" t="n"/>
+      <c r="CM105" s="24" t="n"/>
+      <c r="CN105" s="24" t="n"/>
+      <c r="CO105" s="24" t="n"/>
+      <c r="CP105" s="24" t="n"/>
+      <c r="CQ105" s="24" t="n"/>
+      <c r="CR105" s="24" t="n"/>
+      <c r="CS105" s="24" t="n"/>
+      <c r="CT105" s="24" t="n"/>
+      <c r="CU105" s="24" t="n"/>
+      <c r="CV105" s="24" t="n"/>
+      <c r="CW105" s="24" t="n"/>
+      <c r="CX105" s="24" t="n"/>
+      <c r="CY105" s="24" t="n"/>
+      <c r="CZ105" s="24" t="n"/>
+      <c r="DA105" s="24" t="n"/>
+      <c r="DB105" s="24" t="n"/>
+      <c r="DC105" s="24" t="n"/>
+      <c r="DD105" s="24" t="n"/>
+      <c r="DE105" s="24" t="n"/>
+      <c r="DF105" s="24" t="n"/>
+      <c r="DG105" s="24" t="n"/>
+      <c r="DH105" s="24" t="n"/>
+      <c r="DI105" s="24" t="n"/>
+      <c r="DJ105" s="24" t="n"/>
+      <c r="DK105" s="24" t="n"/>
+      <c r="DL105" s="24" t="n"/>
+      <c r="DM105" s="24" t="n"/>
+      <c r="DN105" s="24" t="n"/>
+      <c r="DO105" s="24" t="n"/>
+      <c r="DP105" s="24" t="n"/>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>ec2906bb14b24356</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00Z</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-lucdar-dalsvr-2026-09-02</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F106" s="24" t="inlineStr">
+        <is>
+          <t>Dalibor Svrcina</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="H106" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I106" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J106" s="25" t="n"/>
+      <c r="K106" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L106" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M106" s="27" t="n">
+        <v>1.7519</v>
+      </c>
+      <c r="N106" s="28" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="O106" s="28" t="n">
+        <v>0.6375999999999999</v>
+      </c>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="28" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="R106" s="26" t="n"/>
+      <c r="S106" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U106" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V106" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W106" s="26" t="n"/>
+      <c r="X106" s="26" t="n"/>
+      <c r="Y106" s="25" t="n"/>
+      <c r="Z106" s="26" t="n"/>
+      <c r="AA106" s="28" t="n"/>
+      <c r="AB106" s="28" t="n"/>
+      <c r="AC106" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="24" t="n"/>
+      <c r="AE106" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAJ717GMVR on aec-atp-lucdar-dalsvr-2026-09-02 (long)</t>
+        </is>
+      </c>
+      <c r="AF106" s="31" t="n"/>
+      <c r="AG106" s="24" t="n"/>
+      <c r="AH106" s="24" t="n"/>
+      <c r="AI106" s="31" t="n"/>
+      <c r="AJ106" s="31" t="n"/>
+      <c r="AK106" s="24" t="n"/>
+      <c r="AL106" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM106" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN106" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO106" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP106" s="24" t="n"/>
+      <c r="AQ106" s="24" t="n"/>
+      <c r="AR106" s="24" t="n"/>
+      <c r="AS106" s="24" t="n"/>
+      <c r="AT106" s="24" t="n"/>
+      <c r="AU106" s="24" t="n"/>
+      <c r="AV106" s="24" t="n"/>
+      <c r="AW106" s="24" t="n"/>
+      <c r="AX106" s="24" t="n"/>
+      <c r="AY106" s="24" t="n"/>
+      <c r="AZ106" s="24" t="n"/>
+      <c r="BA106" s="24" t="n"/>
+      <c r="BB106" s="24" t="n"/>
+      <c r="BC106" s="24" t="n"/>
+      <c r="BD106" s="24" t="n"/>
+      <c r="BE106" s="24" t="n"/>
+      <c r="BF106" s="24" t="n"/>
+      <c r="BG106" s="24" t="n"/>
+      <c r="BH106" s="24" t="n"/>
+      <c r="BI106" s="24" t="n"/>
+      <c r="BJ106" s="25" t="n"/>
+      <c r="BK106" s="26" t="n"/>
+      <c r="BL106" s="27" t="n"/>
+      <c r="BM106" s="28" t="n"/>
+      <c r="BN106" s="28" t="n"/>
+      <c r="BO106" s="28" t="n"/>
+      <c r="BP106" s="25" t="n"/>
+      <c r="BQ106" s="27" t="n"/>
+      <c r="BR106" s="28" t="n"/>
+      <c r="BS106" s="28" t="n"/>
+      <c r="BT106" s="28" t="n"/>
+      <c r="BU106" s="25" t="n"/>
+      <c r="BV106" s="29" t="n"/>
+      <c r="BW106" s="24" t="n"/>
+      <c r="BX106" s="30" t="n"/>
+      <c r="BY106" s="27" t="n"/>
+      <c r="BZ106" s="24" t="n"/>
+      <c r="CA106" s="31" t="n"/>
+      <c r="CB106" s="24" t="n"/>
+      <c r="CC106" s="24" t="n"/>
+      <c r="CD106" s="24" t="n"/>
+      <c r="CE106" s="24" t="n"/>
+      <c r="CF106" s="24" t="n"/>
+      <c r="CG106" s="24" t="n"/>
+      <c r="CH106" s="24" t="n"/>
+      <c r="CI106" s="24" t="n"/>
+      <c r="CJ106" s="24" t="n"/>
+      <c r="CK106" s="24" t="n"/>
+      <c r="CL106" s="24" t="n"/>
+      <c r="CM106" s="24" t="n"/>
+      <c r="CN106" s="24" t="n"/>
+      <c r="CO106" s="24" t="n"/>
+      <c r="CP106" s="24" t="n"/>
+      <c r="CQ106" s="24" t="n"/>
+      <c r="CR106" s="24" t="n"/>
+      <c r="CS106" s="24" t="n"/>
+      <c r="CT106" s="24" t="n"/>
+      <c r="CU106" s="24" t="n"/>
+      <c r="CV106" s="24" t="n"/>
+      <c r="CW106" s="24" t="n"/>
+      <c r="CX106" s="24" t="n"/>
+      <c r="CY106" s="24" t="n"/>
+      <c r="CZ106" s="24" t="n"/>
+      <c r="DA106" s="24" t="n"/>
+      <c r="DB106" s="24" t="n"/>
+      <c r="DC106" s="24" t="n"/>
+      <c r="DD106" s="24" t="n"/>
+      <c r="DE106" s="24" t="n"/>
+      <c r="DF106" s="24" t="n"/>
+      <c r="DG106" s="24" t="n"/>
+      <c r="DH106" s="24" t="n"/>
+      <c r="DI106" s="24" t="n"/>
+      <c r="DJ106" s="24" t="n"/>
+      <c r="DK106" s="24" t="n"/>
+      <c r="DL106" s="24" t="n"/>
+      <c r="DM106" s="24" t="n"/>
+      <c r="DN106" s="24" t="n"/>
+      <c r="DO106" s="24" t="n"/>
+      <c r="DP106" s="24" t="n"/>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t>ad4dfd69909b43b5</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00Z</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-janstr-fracer-2026-09-02</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="inlineStr">
+        <is>
+          <t>Jan-Lennard Struff</t>
+        </is>
+      </c>
+      <c r="H107" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I107" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J107" s="25" t="n"/>
+      <c r="K107" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L107" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M107" s="27" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="N107" s="28" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="O107" s="28" t="n">
+        <v>0.7209</v>
+      </c>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="28" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="R107" s="26" t="n"/>
+      <c r="S107" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T107" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U107" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V107" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W107" s="26" t="n"/>
+      <c r="X107" s="26" t="n"/>
+      <c r="Y107" s="25" t="n"/>
+      <c r="Z107" s="26" t="n"/>
+      <c r="AA107" s="28" t="n"/>
+      <c r="AB107" s="28" t="n"/>
+      <c r="AC107" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="24" t="n"/>
+      <c r="AE107" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SA9KYNEMVF on aec-atp-janstr-fracer-2026-09-02 (short)</t>
+        </is>
+      </c>
+      <c r="AF107" s="31" t="n"/>
+      <c r="AG107" s="24" t="n"/>
+      <c r="AH107" s="24" t="n"/>
+      <c r="AI107" s="31" t="n"/>
+      <c r="AJ107" s="31" t="n"/>
+      <c r="AK107" s="24" t="n"/>
+      <c r="AL107" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM107" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN107" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO107" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP107" s="24" t="n"/>
+      <c r="AQ107" s="24" t="n"/>
+      <c r="AR107" s="24" t="n"/>
+      <c r="AS107" s="24" t="n"/>
+      <c r="AT107" s="24" t="n"/>
+      <c r="AU107" s="24" t="n"/>
+      <c r="AV107" s="24" t="n"/>
+      <c r="AW107" s="24" t="n"/>
+      <c r="AX107" s="24" t="n"/>
+      <c r="AY107" s="24" t="n"/>
+      <c r="AZ107" s="24" t="n"/>
+      <c r="BA107" s="24" t="n"/>
+      <c r="BB107" s="24" t="n"/>
+      <c r="BC107" s="24" t="n"/>
+      <c r="BD107" s="24" t="n"/>
+      <c r="BE107" s="24" t="n"/>
+      <c r="BF107" s="24" t="n"/>
+      <c r="BG107" s="24" t="n"/>
+      <c r="BH107" s="24" t="n"/>
+      <c r="BI107" s="24" t="n"/>
+      <c r="BJ107" s="25" t="n"/>
+      <c r="BK107" s="26" t="n"/>
+      <c r="BL107" s="27" t="n"/>
+      <c r="BM107" s="28" t="n"/>
+      <c r="BN107" s="28" t="n"/>
+      <c r="BO107" s="28" t="n"/>
+      <c r="BP107" s="25" t="n"/>
+      <c r="BQ107" s="27" t="n"/>
+      <c r="BR107" s="28" t="n"/>
+      <c r="BS107" s="28" t="n"/>
+      <c r="BT107" s="28" t="n"/>
+      <c r="BU107" s="25" t="n"/>
+      <c r="BV107" s="29" t="n"/>
+      <c r="BW107" s="24" t="n"/>
+      <c r="BX107" s="30" t="n"/>
+      <c r="BY107" s="27" t="n"/>
+      <c r="BZ107" s="24" t="n"/>
+      <c r="CA107" s="31" t="n"/>
+      <c r="CB107" s="24" t="n"/>
+      <c r="CC107" s="24" t="n"/>
+      <c r="CD107" s="24" t="n"/>
+      <c r="CE107" s="24" t="n"/>
+      <c r="CF107" s="24" t="n"/>
+      <c r="CG107" s="24" t="n"/>
+      <c r="CH107" s="24" t="n"/>
+      <c r="CI107" s="24" t="n"/>
+      <c r="CJ107" s="24" t="n"/>
+      <c r="CK107" s="24" t="n"/>
+      <c r="CL107" s="24" t="n"/>
+      <c r="CM107" s="24" t="n"/>
+      <c r="CN107" s="24" t="n"/>
+      <c r="CO107" s="24" t="n"/>
+      <c r="CP107" s="24" t="n"/>
+      <c r="CQ107" s="24" t="n"/>
+      <c r="CR107" s="24" t="n"/>
+      <c r="CS107" s="24" t="n"/>
+      <c r="CT107" s="24" t="n"/>
+      <c r="CU107" s="24" t="n"/>
+      <c r="CV107" s="24" t="n"/>
+      <c r="CW107" s="24" t="n"/>
+      <c r="CX107" s="24" t="n"/>
+      <c r="CY107" s="24" t="n"/>
+      <c r="CZ107" s="24" t="n"/>
+      <c r="DA107" s="24" t="n"/>
+      <c r="DB107" s="24" t="n"/>
+      <c r="DC107" s="24" t="n"/>
+      <c r="DD107" s="24" t="n"/>
+      <c r="DE107" s="24" t="n"/>
+      <c r="DF107" s="24" t="n"/>
+      <c r="DG107" s="24" t="n"/>
+      <c r="DH107" s="24" t="n"/>
+      <c r="DI107" s="24" t="n"/>
+      <c r="DJ107" s="24" t="n"/>
+      <c r="DK107" s="24" t="n"/>
+      <c r="DL107" s="24" t="n"/>
+      <c r="DM107" s="24" t="n"/>
+      <c r="DN107" s="24" t="n"/>
+      <c r="DO107" s="24" t="n"/>
+      <c r="DP107" s="24" t="n"/>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t>5eb9281023994c1d</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:00Z</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-benbon-ignbus-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>Ignacio Buse</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="H108" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I108" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J108" s="25" t="n"/>
+      <c r="K108" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L108" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M108" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N108" s="28" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="O108" s="28" t="n">
+        <v>0.5246</v>
+      </c>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="28" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="R108" s="26" t="n"/>
+      <c r="S108" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T108" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U108" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V108" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W108" s="26" t="n"/>
+      <c r="X108" s="26" t="n"/>
+      <c r="Y108" s="25" t="n"/>
+      <c r="Z108" s="26" t="n"/>
+      <c r="AA108" s="28" t="n"/>
+      <c r="AB108" s="28" t="n"/>
+      <c r="AC108" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="24" t="n"/>
+      <c r="AE108" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9RQ5K2MVZ on aec-atp-benbon-ignbus-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF108" s="31" t="n"/>
+      <c r="AG108" s="24" t="n"/>
+      <c r="AH108" s="24" t="n"/>
+      <c r="AI108" s="31" t="n"/>
+      <c r="AJ108" s="31" t="n"/>
+      <c r="AK108" s="24" t="n"/>
+      <c r="AL108" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM108" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN108" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO108" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP108" s="24" t="n"/>
+      <c r="AQ108" s="24" t="n"/>
+      <c r="AR108" s="24" t="n"/>
+      <c r="AS108" s="24" t="n"/>
+      <c r="AT108" s="24" t="n"/>
+      <c r="AU108" s="24" t="n"/>
+      <c r="AV108" s="24" t="n"/>
+      <c r="AW108" s="24" t="n"/>
+      <c r="AX108" s="24" t="n"/>
+      <c r="AY108" s="24" t="n"/>
+      <c r="AZ108" s="24" t="n"/>
+      <c r="BA108" s="24" t="n"/>
+      <c r="BB108" s="24" t="n"/>
+      <c r="BC108" s="24" t="n"/>
+      <c r="BD108" s="24" t="n"/>
+      <c r="BE108" s="24" t="n"/>
+      <c r="BF108" s="24" t="n"/>
+      <c r="BG108" s="24" t="n"/>
+      <c r="BH108" s="24" t="n"/>
+      <c r="BI108" s="24" t="n"/>
+      <c r="BJ108" s="25" t="n"/>
+      <c r="BK108" s="26" t="n"/>
+      <c r="BL108" s="27" t="n"/>
+      <c r="BM108" s="28" t="n"/>
+      <c r="BN108" s="28" t="n"/>
+      <c r="BO108" s="28" t="n"/>
+      <c r="BP108" s="25" t="n"/>
+      <c r="BQ108" s="27" t="n"/>
+      <c r="BR108" s="28" t="n"/>
+      <c r="BS108" s="28" t="n"/>
+      <c r="BT108" s="28" t="n"/>
+      <c r="BU108" s="25" t="n"/>
+      <c r="BV108" s="29" t="n"/>
+      <c r="BW108" s="24" t="n"/>
+      <c r="BX108" s="30" t="n"/>
+      <c r="BY108" s="27" t="n"/>
+      <c r="BZ108" s="24" t="n"/>
+      <c r="CA108" s="31" t="n"/>
+      <c r="CB108" s="24" t="n"/>
+      <c r="CC108" s="24" t="n"/>
+      <c r="CD108" s="24" t="n"/>
+      <c r="CE108" s="24" t="n"/>
+      <c r="CF108" s="24" t="n"/>
+      <c r="CG108" s="24" t="n"/>
+      <c r="CH108" s="24" t="n"/>
+      <c r="CI108" s="24" t="n"/>
+      <c r="CJ108" s="24" t="n"/>
+      <c r="CK108" s="24" t="n"/>
+      <c r="CL108" s="24" t="n"/>
+      <c r="CM108" s="24" t="n"/>
+      <c r="CN108" s="24" t="n"/>
+      <c r="CO108" s="24" t="n"/>
+      <c r="CP108" s="24" t="n"/>
+      <c r="CQ108" s="24" t="n"/>
+      <c r="CR108" s="24" t="n"/>
+      <c r="CS108" s="24" t="n"/>
+      <c r="CT108" s="24" t="n"/>
+      <c r="CU108" s="24" t="n"/>
+      <c r="CV108" s="24" t="n"/>
+      <c r="CW108" s="24" t="n"/>
+      <c r="CX108" s="24" t="n"/>
+      <c r="CY108" s="24" t="n"/>
+      <c r="CZ108" s="24" t="n"/>
+      <c r="DA108" s="24" t="n"/>
+      <c r="DB108" s="24" t="n"/>
+      <c r="DC108" s="24" t="n"/>
+      <c r="DD108" s="24" t="n"/>
+      <c r="DE108" s="24" t="n"/>
+      <c r="DF108" s="24" t="n"/>
+      <c r="DG108" s="24" t="n"/>
+      <c r="DH108" s="24" t="n"/>
+      <c r="DI108" s="24" t="n"/>
+      <c r="DJ108" s="24" t="n"/>
+      <c r="DK108" s="24" t="n"/>
+      <c r="DL108" s="24" t="n"/>
+      <c r="DM108" s="24" t="n"/>
+      <c r="DN108" s="24" t="n"/>
+      <c r="DO108" s="24" t="n"/>
+      <c r="DP108" s="24" t="n"/>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="24" t="inlineStr">
+        <is>
+          <t>499f668b627b4948</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-doc-bce-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F109" s="24" t="inlineStr">
+        <is>
+          <t>Barcząca Esports</t>
+        </is>
+      </c>
+      <c r="G109" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="H109" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I109" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J109" s="25" t="n"/>
+      <c r="K109" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L109" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M109" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N109" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O109" s="28" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="28" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="R109" s="26" t="n"/>
+      <c r="S109" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T109" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U109" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V109" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W109" s="26" t="n"/>
+      <c r="X109" s="26" t="n"/>
+      <c r="Y109" s="25" t="n"/>
+      <c r="Z109" s="26" t="n"/>
+      <c r="AA109" s="28" t="n"/>
+      <c r="AB109" s="28" t="n"/>
+      <c r="AC109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" s="24" t="n"/>
+      <c r="AE109" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SA9KZAEMVF on aec-lol-doc-bce-2026-09-03 (short)</t>
+        </is>
+      </c>
+      <c r="AF109" s="31" t="n"/>
+      <c r="AG109" s="24" t="n"/>
+      <c r="AH109" s="24" t="n"/>
+      <c r="AI109" s="31" t="n"/>
+      <c r="AJ109" s="31" t="n"/>
+      <c r="AK109" s="24" t="n"/>
+      <c r="AL109" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM109" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN109" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO109" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP109" s="24" t="n"/>
+      <c r="AQ109" s="24" t="n"/>
+      <c r="AR109" s="24" t="n"/>
+      <c r="AS109" s="24" t="n"/>
+      <c r="AT109" s="24" t="n"/>
+      <c r="AU109" s="24" t="n"/>
+      <c r="AV109" s="24" t="n"/>
+      <c r="AW109" s="24" t="n"/>
+      <c r="AX109" s="24" t="n"/>
+      <c r="AY109" s="24" t="n"/>
+      <c r="AZ109" s="24" t="n"/>
+      <c r="BA109" s="24" t="n"/>
+      <c r="BB109" s="24" t="n"/>
+      <c r="BC109" s="24" t="n"/>
+      <c r="BD109" s="24" t="n"/>
+      <c r="BE109" s="24" t="n"/>
+      <c r="BF109" s="24" t="n"/>
+      <c r="BG109" s="24" t="n"/>
+      <c r="BH109" s="24" t="n"/>
+      <c r="BI109" s="24" t="n"/>
+      <c r="BJ109" s="25" t="n"/>
+      <c r="BK109" s="26" t="n"/>
+      <c r="BL109" s="27" t="n"/>
+      <c r="BM109" s="28" t="n"/>
+      <c r="BN109" s="28" t="n"/>
+      <c r="BO109" s="28" t="n"/>
+      <c r="BP109" s="25" t="n"/>
+      <c r="BQ109" s="27" t="n"/>
+      <c r="BR109" s="28" t="n"/>
+      <c r="BS109" s="28" t="n"/>
+      <c r="BT109" s="28" t="n"/>
+      <c r="BU109" s="25" t="n"/>
+      <c r="BV109" s="29" t="n"/>
+      <c r="BW109" s="24" t="n"/>
+      <c r="BX109" s="30" t="n"/>
+      <c r="BY109" s="27" t="n"/>
+      <c r="BZ109" s="24" t="n"/>
+      <c r="CA109" s="31" t="n"/>
+      <c r="CB109" s="24" t="n"/>
+      <c r="CC109" s="24" t="n"/>
+      <c r="CD109" s="24" t="n"/>
+      <c r="CE109" s="24" t="n"/>
+      <c r="CF109" s="24" t="n"/>
+      <c r="CG109" s="24" t="n"/>
+      <c r="CH109" s="24" t="n"/>
+      <c r="CI109" s="24" t="n"/>
+      <c r="CJ109" s="24" t="n"/>
+      <c r="CK109" s="24" t="n"/>
+      <c r="CL109" s="24" t="n"/>
+      <c r="CM109" s="24" t="n"/>
+      <c r="CN109" s="24" t="n"/>
+      <c r="CO109" s="24" t="n"/>
+      <c r="CP109" s="24" t="n"/>
+      <c r="CQ109" s="24" t="n"/>
+      <c r="CR109" s="24" t="n"/>
+      <c r="CS109" s="24" t="n"/>
+      <c r="CT109" s="24" t="n"/>
+      <c r="CU109" s="24" t="n"/>
+      <c r="CV109" s="24" t="n"/>
+      <c r="CW109" s="24" t="n"/>
+      <c r="CX109" s="24" t="n"/>
+      <c r="CY109" s="24" t="n"/>
+      <c r="CZ109" s="24" t="n"/>
+      <c r="DA109" s="24" t="n"/>
+      <c r="DB109" s="24" t="n"/>
+      <c r="DC109" s="24" t="n"/>
+      <c r="DD109" s="24" t="n"/>
+      <c r="DE109" s="24" t="n"/>
+      <c r="DF109" s="24" t="n"/>
+      <c r="DG109" s="24" t="n"/>
+      <c r="DH109" s="24" t="n"/>
+      <c r="DI109" s="24" t="n"/>
+      <c r="DJ109" s="24" t="n"/>
+      <c r="DK109" s="24" t="n"/>
+      <c r="DL109" s="24" t="n"/>
+      <c r="DM109" s="24" t="n"/>
+      <c r="DN109" s="24" t="n"/>
+      <c r="DO109" s="24" t="n"/>
+      <c r="DP109" s="24" t="n"/>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="24" t="inlineStr">
+        <is>
+          <t>1afb1ec1d9d340e5</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-pcific-su-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>SU Esports</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCIFIC </t>
+        </is>
+      </c>
+      <c r="H110" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I110" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J110" s="25" t="n"/>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L110" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M110" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N110" s="28" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="O110" s="28" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="28" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="R110" s="26" t="n"/>
+      <c r="S110" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T110" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U110" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V110" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W110" s="26" t="n"/>
+      <c r="X110" s="26" t="n"/>
+      <c r="Y110" s="25" t="n"/>
+      <c r="Z110" s="26" t="n"/>
+      <c r="AA110" s="28" t="n"/>
+      <c r="AB110" s="28" t="n"/>
+      <c r="AC110" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" s="24" t="n"/>
+      <c r="AE110" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAKWMYRMVG on aec-lol-pcific-su-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF110" s="31" t="n"/>
+      <c r="AG110" s="24" t="n"/>
+      <c r="AH110" s="24" t="n"/>
+      <c r="AI110" s="31" t="n"/>
+      <c r="AJ110" s="31" t="n"/>
+      <c r="AK110" s="24" t="n"/>
+      <c r="AL110" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM110" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN110" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO110" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP110" s="24" t="n"/>
+      <c r="AQ110" s="24" t="n"/>
+      <c r="AR110" s="24" t="n"/>
+      <c r="AS110" s="24" t="n"/>
+      <c r="AT110" s="24" t="n"/>
+      <c r="AU110" s="24" t="n"/>
+      <c r="AV110" s="24" t="n"/>
+      <c r="AW110" s="24" t="n"/>
+      <c r="AX110" s="24" t="n"/>
+      <c r="AY110" s="24" t="n"/>
+      <c r="AZ110" s="24" t="n"/>
+      <c r="BA110" s="24" t="n"/>
+      <c r="BB110" s="24" t="n"/>
+      <c r="BC110" s="24" t="n"/>
+      <c r="BD110" s="24" t="n"/>
+      <c r="BE110" s="24" t="n"/>
+      <c r="BF110" s="24" t="n"/>
+      <c r="BG110" s="24" t="n"/>
+      <c r="BH110" s="24" t="n"/>
+      <c r="BI110" s="24" t="n"/>
+      <c r="BJ110" s="25" t="n"/>
+      <c r="BK110" s="26" t="n"/>
+      <c r="BL110" s="27" t="n"/>
+      <c r="BM110" s="28" t="n"/>
+      <c r="BN110" s="28" t="n"/>
+      <c r="BO110" s="28" t="n"/>
+      <c r="BP110" s="25" t="n"/>
+      <c r="BQ110" s="27" t="n"/>
+      <c r="BR110" s="28" t="n"/>
+      <c r="BS110" s="28" t="n"/>
+      <c r="BT110" s="28" t="n"/>
+      <c r="BU110" s="25" t="n"/>
+      <c r="BV110" s="29" t="n"/>
+      <c r="BW110" s="24" t="n"/>
+      <c r="BX110" s="30" t="n"/>
+      <c r="BY110" s="27" t="n"/>
+      <c r="BZ110" s="24" t="n"/>
+      <c r="CA110" s="31" t="n"/>
+      <c r="CB110" s="24" t="n"/>
+      <c r="CC110" s="24" t="n"/>
+      <c r="CD110" s="24" t="n"/>
+      <c r="CE110" s="24" t="n"/>
+      <c r="CF110" s="24" t="n"/>
+      <c r="CG110" s="24" t="n"/>
+      <c r="CH110" s="24" t="n"/>
+      <c r="CI110" s="24" t="n"/>
+      <c r="CJ110" s="24" t="n"/>
+      <c r="CK110" s="24" t="n"/>
+      <c r="CL110" s="24" t="n"/>
+      <c r="CM110" s="24" t="n"/>
+      <c r="CN110" s="24" t="n"/>
+      <c r="CO110" s="24" t="n"/>
+      <c r="CP110" s="24" t="n"/>
+      <c r="CQ110" s="24" t="n"/>
+      <c r="CR110" s="24" t="n"/>
+      <c r="CS110" s="24" t="n"/>
+      <c r="CT110" s="24" t="n"/>
+      <c r="CU110" s="24" t="n"/>
+      <c r="CV110" s="24" t="n"/>
+      <c r="CW110" s="24" t="n"/>
+      <c r="CX110" s="24" t="n"/>
+      <c r="CY110" s="24" t="n"/>
+      <c r="CZ110" s="24" t="n"/>
+      <c r="DA110" s="24" t="n"/>
+      <c r="DB110" s="24" t="n"/>
+      <c r="DC110" s="24" t="n"/>
+      <c r="DD110" s="24" t="n"/>
+      <c r="DE110" s="24" t="n"/>
+      <c r="DF110" s="24" t="n"/>
+      <c r="DG110" s="24" t="n"/>
+      <c r="DH110" s="24" t="n"/>
+      <c r="DI110" s="24" t="n"/>
+      <c r="DJ110" s="24" t="n"/>
+      <c r="DK110" s="24" t="n"/>
+      <c r="DL110" s="24" t="n"/>
+      <c r="DM110" s="24" t="n"/>
+      <c r="DN110" s="24" t="n"/>
+      <c r="DO110" s="24" t="n"/>
+      <c r="DP110" s="24" t="n"/>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t>5ea53b60e25a46ef</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-sec-myth-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>Senshi Esports</t>
+        </is>
+      </c>
+      <c r="H111" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J111" s="25" t="n"/>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M111" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N111" s="28" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="O111" s="28" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="28" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="R111" s="26" t="n"/>
+      <c r="S111" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T111" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U111" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W111" s="26" t="n"/>
+      <c r="X111" s="26" t="n"/>
+      <c r="Y111" s="25" t="n"/>
+      <c r="Z111" s="26" t="n"/>
+      <c r="AA111" s="28" t="n"/>
+      <c r="AB111" s="28" t="n"/>
+      <c r="AC111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="24" t="n"/>
+      <c r="AE111" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SADETDWMVK on aec-lol-sec-myth-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF111" s="31" t="n"/>
+      <c r="AG111" s="24" t="n"/>
+      <c r="AH111" s="24" t="n"/>
+      <c r="AI111" s="31" t="n"/>
+      <c r="AJ111" s="31" t="n"/>
+      <c r="AK111" s="24" t="n"/>
+      <c r="AL111" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM111" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN111" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO111" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP111" s="24" t="n"/>
+      <c r="AQ111" s="24" t="n"/>
+      <c r="AR111" s="24" t="n"/>
+      <c r="AS111" s="24" t="n"/>
+      <c r="AT111" s="24" t="n"/>
+      <c r="AU111" s="24" t="n"/>
+      <c r="AV111" s="24" t="n"/>
+      <c r="AW111" s="24" t="n"/>
+      <c r="AX111" s="24" t="n"/>
+      <c r="AY111" s="24" t="n"/>
+      <c r="AZ111" s="24" t="n"/>
+      <c r="BA111" s="24" t="n"/>
+      <c r="BB111" s="24" t="n"/>
+      <c r="BC111" s="24" t="n"/>
+      <c r="BD111" s="24" t="n"/>
+      <c r="BE111" s="24" t="n"/>
+      <c r="BF111" s="24" t="n"/>
+      <c r="BG111" s="24" t="n"/>
+      <c r="BH111" s="24" t="n"/>
+      <c r="BI111" s="24" t="n"/>
+      <c r="BJ111" s="25" t="n"/>
+      <c r="BK111" s="26" t="n"/>
+      <c r="BL111" s="27" t="n"/>
+      <c r="BM111" s="28" t="n"/>
+      <c r="BN111" s="28" t="n"/>
+      <c r="BO111" s="28" t="n"/>
+      <c r="BP111" s="25" t="n"/>
+      <c r="BQ111" s="27" t="n"/>
+      <c r="BR111" s="28" t="n"/>
+      <c r="BS111" s="28" t="n"/>
+      <c r="BT111" s="28" t="n"/>
+      <c r="BU111" s="25" t="n"/>
+      <c r="BV111" s="29" t="n"/>
+      <c r="BW111" s="24" t="n"/>
+      <c r="BX111" s="30" t="n"/>
+      <c r="BY111" s="27" t="n"/>
+      <c r="BZ111" s="24" t="n"/>
+      <c r="CA111" s="31" t="n"/>
+      <c r="CB111" s="24" t="n"/>
+      <c r="CC111" s="24" t="n"/>
+      <c r="CD111" s="24" t="n"/>
+      <c r="CE111" s="24" t="n"/>
+      <c r="CF111" s="24" t="n"/>
+      <c r="CG111" s="24" t="n"/>
+      <c r="CH111" s="24" t="n"/>
+      <c r="CI111" s="24" t="n"/>
+      <c r="CJ111" s="24" t="n"/>
+      <c r="CK111" s="24" t="n"/>
+      <c r="CL111" s="24" t="n"/>
+      <c r="CM111" s="24" t="n"/>
+      <c r="CN111" s="24" t="n"/>
+      <c r="CO111" s="24" t="n"/>
+      <c r="CP111" s="24" t="n"/>
+      <c r="CQ111" s="24" t="n"/>
+      <c r="CR111" s="24" t="n"/>
+      <c r="CS111" s="24" t="n"/>
+      <c r="CT111" s="24" t="n"/>
+      <c r="CU111" s="24" t="n"/>
+      <c r="CV111" s="24" t="n"/>
+      <c r="CW111" s="24" t="n"/>
+      <c r="CX111" s="24" t="n"/>
+      <c r="CY111" s="24" t="n"/>
+      <c r="CZ111" s="24" t="n"/>
+      <c r="DA111" s="24" t="n"/>
+      <c r="DB111" s="24" t="n"/>
+      <c r="DC111" s="24" t="n"/>
+      <c r="DD111" s="24" t="n"/>
+      <c r="DE111" s="24" t="n"/>
+      <c r="DF111" s="24" t="n"/>
+      <c r="DG111" s="24" t="n"/>
+      <c r="DH111" s="24" t="n"/>
+      <c r="DI111" s="24" t="n"/>
+      <c r="DJ111" s="24" t="n"/>
+      <c r="DK111" s="24" t="n"/>
+      <c r="DL111" s="24" t="n"/>
+      <c r="DM111" s="24" t="n"/>
+      <c r="DN111" s="24" t="n"/>
+      <c r="DO111" s="24" t="n"/>
+      <c r="DP111" s="24" t="n"/>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>b8c313dca7364d0e</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-lds-dv1-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>devils.one inStreamly</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J112" s="25" t="n"/>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M112" s="27" t="n">
+        <v>1.9615</v>
+      </c>
+      <c r="N112" s="28" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="O112" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="28" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R112" s="26" t="n"/>
+      <c r="S112" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T112" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U112" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V112" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W112" s="26" t="n"/>
+      <c r="X112" s="26" t="n"/>
+      <c r="Y112" s="25" t="n"/>
+      <c r="Z112" s="26" t="n"/>
+      <c r="AA112" s="28" t="n"/>
+      <c r="AB112" s="28" t="n"/>
+      <c r="AC112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="24" t="n"/>
+      <c r="AE112" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAMAA24MVP on aec-lol-lds-dv1-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF112" s="31" t="n"/>
+      <c r="AG112" s="24" t="n"/>
+      <c r="AH112" s="24" t="n"/>
+      <c r="AI112" s="31" t="n"/>
+      <c r="AJ112" s="31" t="n"/>
+      <c r="AK112" s="24" t="n"/>
+      <c r="AL112" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM112" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN112" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO112" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP112" s="24" t="n"/>
+      <c r="AQ112" s="24" t="n"/>
+      <c r="AR112" s="24" t="n"/>
+      <c r="AS112" s="24" t="n"/>
+      <c r="AT112" s="24" t="n"/>
+      <c r="AU112" s="24" t="n"/>
+      <c r="AV112" s="24" t="n"/>
+      <c r="AW112" s="24" t="n"/>
+      <c r="AX112" s="24" t="n"/>
+      <c r="AY112" s="24" t="n"/>
+      <c r="AZ112" s="24" t="n"/>
+      <c r="BA112" s="24" t="n"/>
+      <c r="BB112" s="24" t="n"/>
+      <c r="BC112" s="24" t="n"/>
+      <c r="BD112" s="24" t="n"/>
+      <c r="BE112" s="24" t="n"/>
+      <c r="BF112" s="24" t="n"/>
+      <c r="BG112" s="24" t="n"/>
+      <c r="BH112" s="24" t="n"/>
+      <c r="BI112" s="24" t="n"/>
+      <c r="BJ112" s="25" t="n"/>
+      <c r="BK112" s="26" t="n"/>
+      <c r="BL112" s="27" t="n"/>
+      <c r="BM112" s="28" t="n"/>
+      <c r="BN112" s="28" t="n"/>
+      <c r="BO112" s="28" t="n"/>
+      <c r="BP112" s="25" t="n"/>
+      <c r="BQ112" s="27" t="n"/>
+      <c r="BR112" s="28" t="n"/>
+      <c r="BS112" s="28" t="n"/>
+      <c r="BT112" s="28" t="n"/>
+      <c r="BU112" s="25" t="n"/>
+      <c r="BV112" s="29" t="n"/>
+      <c r="BW112" s="24" t="n"/>
+      <c r="BX112" s="30" t="n"/>
+      <c r="BY112" s="27" t="n"/>
+      <c r="BZ112" s="24" t="n"/>
+      <c r="CA112" s="31" t="n"/>
+      <c r="CB112" s="24" t="n"/>
+      <c r="CC112" s="24" t="n"/>
+      <c r="CD112" s="24" t="n"/>
+      <c r="CE112" s="24" t="n"/>
+      <c r="CF112" s="24" t="n"/>
+      <c r="CG112" s="24" t="n"/>
+      <c r="CH112" s="24" t="n"/>
+      <c r="CI112" s="24" t="n"/>
+      <c r="CJ112" s="24" t="n"/>
+      <c r="CK112" s="24" t="n"/>
+      <c r="CL112" s="24" t="n"/>
+      <c r="CM112" s="24" t="n"/>
+      <c r="CN112" s="24" t="n"/>
+      <c r="CO112" s="24" t="n"/>
+      <c r="CP112" s="24" t="n"/>
+      <c r="CQ112" s="24" t="n"/>
+      <c r="CR112" s="24" t="n"/>
+      <c r="CS112" s="24" t="n"/>
+      <c r="CT112" s="24" t="n"/>
+      <c r="CU112" s="24" t="n"/>
+      <c r="CV112" s="24" t="n"/>
+      <c r="CW112" s="24" t="n"/>
+      <c r="CX112" s="24" t="n"/>
+      <c r="CY112" s="24" t="n"/>
+      <c r="CZ112" s="24" t="n"/>
+      <c r="DA112" s="24" t="n"/>
+      <c r="DB112" s="24" t="n"/>
+      <c r="DC112" s="24" t="n"/>
+      <c r="DD112" s="24" t="n"/>
+      <c r="DE112" s="24" t="n"/>
+      <c r="DF112" s="24" t="n"/>
+      <c r="DG112" s="24" t="n"/>
+      <c r="DH112" s="24" t="n"/>
+      <c r="DI112" s="24" t="n"/>
+      <c r="DJ112" s="24" t="n"/>
+      <c r="DK112" s="24" t="n"/>
+      <c r="DL112" s="24" t="n"/>
+      <c r="DM112" s="24" t="n"/>
+      <c r="DN112" s="24" t="n"/>
+      <c r="DO112" s="24" t="n"/>
+      <c r="DP112" s="24" t="n"/>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>b7e3c094952e47cb</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-domi-drm-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>Dream Esports</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>Dominion Goblins</t>
+        </is>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J113" s="25" t="n"/>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M113" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N113" s="28" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="O113" s="28" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="28" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="R113" s="26" t="n"/>
+      <c r="S113" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T113" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U113" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V113" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W113" s="26" t="n"/>
+      <c r="X113" s="26" t="n"/>
+      <c r="Y113" s="25" t="n"/>
+      <c r="Z113" s="26" t="n"/>
+      <c r="AA113" s="28" t="n"/>
+      <c r="AB113" s="28" t="n"/>
+      <c r="AC113" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="24" t="n"/>
+      <c r="AE113" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAC9AMPMW0 on aec-lol-domi-drm-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF113" s="31" t="n"/>
+      <c r="AG113" s="24" t="n"/>
+      <c r="AH113" s="24" t="n"/>
+      <c r="AI113" s="31" t="n"/>
+      <c r="AJ113" s="31" t="n"/>
+      <c r="AK113" s="24" t="n"/>
+      <c r="AL113" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM113" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN113" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO113" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP113" s="24" t="n"/>
+      <c r="AQ113" s="24" t="n"/>
+      <c r="AR113" s="24" t="n"/>
+      <c r="AS113" s="24" t="n"/>
+      <c r="AT113" s="24" t="n"/>
+      <c r="AU113" s="24" t="n"/>
+      <c r="AV113" s="24" t="n"/>
+      <c r="AW113" s="24" t="n"/>
+      <c r="AX113" s="24" t="n"/>
+      <c r="AY113" s="24" t="n"/>
+      <c r="AZ113" s="24" t="n"/>
+      <c r="BA113" s="24" t="n"/>
+      <c r="BB113" s="24" t="n"/>
+      <c r="BC113" s="24" t="n"/>
+      <c r="BD113" s="24" t="n"/>
+      <c r="BE113" s="24" t="n"/>
+      <c r="BF113" s="24" t="n"/>
+      <c r="BG113" s="24" t="n"/>
+      <c r="BH113" s="24" t="n"/>
+      <c r="BI113" s="24" t="n"/>
+      <c r="BJ113" s="25" t="n"/>
+      <c r="BK113" s="26" t="n"/>
+      <c r="BL113" s="27" t="n"/>
+      <c r="BM113" s="28" t="n"/>
+      <c r="BN113" s="28" t="n"/>
+      <c r="BO113" s="28" t="n"/>
+      <c r="BP113" s="25" t="n"/>
+      <c r="BQ113" s="27" t="n"/>
+      <c r="BR113" s="28" t="n"/>
+      <c r="BS113" s="28" t="n"/>
+      <c r="BT113" s="28" t="n"/>
+      <c r="BU113" s="25" t="n"/>
+      <c r="BV113" s="29" t="n"/>
+      <c r="BW113" s="24" t="n"/>
+      <c r="BX113" s="30" t="n"/>
+      <c r="BY113" s="27" t="n"/>
+      <c r="BZ113" s="24" t="n"/>
+      <c r="CA113" s="31" t="n"/>
+      <c r="CB113" s="24" t="n"/>
+      <c r="CC113" s="24" t="n"/>
+      <c r="CD113" s="24" t="n"/>
+      <c r="CE113" s="24" t="n"/>
+      <c r="CF113" s="24" t="n"/>
+      <c r="CG113" s="24" t="n"/>
+      <c r="CH113" s="24" t="n"/>
+      <c r="CI113" s="24" t="n"/>
+      <c r="CJ113" s="24" t="n"/>
+      <c r="CK113" s="24" t="n"/>
+      <c r="CL113" s="24" t="n"/>
+      <c r="CM113" s="24" t="n"/>
+      <c r="CN113" s="24" t="n"/>
+      <c r="CO113" s="24" t="n"/>
+      <c r="CP113" s="24" t="n"/>
+      <c r="CQ113" s="24" t="n"/>
+      <c r="CR113" s="24" t="n"/>
+      <c r="CS113" s="24" t="n"/>
+      <c r="CT113" s="24" t="n"/>
+      <c r="CU113" s="24" t="n"/>
+      <c r="CV113" s="24" t="n"/>
+      <c r="CW113" s="24" t="n"/>
+      <c r="CX113" s="24" t="n"/>
+      <c r="CY113" s="24" t="n"/>
+      <c r="CZ113" s="24" t="n"/>
+      <c r="DA113" s="24" t="n"/>
+      <c r="DB113" s="24" t="n"/>
+      <c r="DC113" s="24" t="n"/>
+      <c r="DD113" s="24" t="n"/>
+      <c r="DE113" s="24" t="n"/>
+      <c r="DF113" s="24" t="n"/>
+      <c r="DG113" s="24" t="n"/>
+      <c r="DH113" s="24" t="n"/>
+      <c r="DI113" s="24" t="n"/>
+      <c r="DJ113" s="24" t="n"/>
+      <c r="DK113" s="24" t="n"/>
+      <c r="DL113" s="24" t="n"/>
+      <c r="DM113" s="24" t="n"/>
+      <c r="DN113" s="24" t="n"/>
+      <c r="DO113" s="24" t="n"/>
+      <c r="DP113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>8ae128177f5b440c</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-g2a-pf-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>PsychoFace</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J114" s="25" t="n"/>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L114" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M114" s="27" t="n">
+        <v>1.9259</v>
+      </c>
+      <c r="N114" s="28" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="O114" s="28" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="28" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="R114" s="26" t="n"/>
+      <c r="S114" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T114" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U114" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V114" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W114" s="26" t="n"/>
+      <c r="X114" s="26" t="n"/>
+      <c r="Y114" s="25" t="n"/>
+      <c r="Z114" s="26" t="n"/>
+      <c r="AA114" s="28" t="n"/>
+      <c r="AB114" s="28" t="n"/>
+      <c r="AC114" s="30" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="AD114" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE114" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9RQ7WYMVZ on aec-cs2-g2a-pf-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF114" s="31" t="n"/>
+      <c r="AG114" s="24" t="n"/>
+      <c r="AH114" s="24" t="n"/>
+      <c r="AI114" s="31" t="n"/>
+      <c r="AJ114" s="31" t="n"/>
+      <c r="AK114" s="24" t="n"/>
+      <c r="AL114" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM114" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN114" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO114" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP114" s="24" t="n"/>
+      <c r="AQ114" s="24" t="n"/>
+      <c r="AR114" s="24" t="n"/>
+      <c r="AS114" s="24" t="n"/>
+      <c r="AT114" s="24" t="n"/>
+      <c r="AU114" s="24" t="n"/>
+      <c r="AV114" s="24" t="n"/>
+      <c r="AW114" s="24" t="n"/>
+      <c r="AX114" s="24" t="n"/>
+      <c r="AY114" s="24" t="n"/>
+      <c r="AZ114" s="24" t="n"/>
+      <c r="BA114" s="24" t="n"/>
+      <c r="BB114" s="24" t="n"/>
+      <c r="BC114" s="24" t="n"/>
+      <c r="BD114" s="24" t="n"/>
+      <c r="BE114" s="24" t="n"/>
+      <c r="BF114" s="24" t="n"/>
+      <c r="BG114" s="24" t="n"/>
+      <c r="BH114" s="24" t="n"/>
+      <c r="BI114" s="24" t="n"/>
+      <c r="BJ114" s="25" t="n"/>
+      <c r="BK114" s="26" t="n"/>
+      <c r="BL114" s="27" t="n"/>
+      <c r="BM114" s="28" t="n"/>
+      <c r="BN114" s="28" t="n"/>
+      <c r="BO114" s="28" t="n"/>
+      <c r="BP114" s="25" t="n"/>
+      <c r="BQ114" s="27" t="n"/>
+      <c r="BR114" s="28" t="n"/>
+      <c r="BS114" s="28" t="n"/>
+      <c r="BT114" s="28" t="n"/>
+      <c r="BU114" s="25" t="n"/>
+      <c r="BV114" s="29" t="n"/>
+      <c r="BW114" s="24" t="n"/>
+      <c r="BX114" s="30" t="n"/>
+      <c r="BY114" s="27" t="n"/>
+      <c r="BZ114" s="24" t="n"/>
+      <c r="CA114" s="31" t="n"/>
+      <c r="CB114" s="24" t="n"/>
+      <c r="CC114" s="24" t="n"/>
+      <c r="CD114" s="24" t="n"/>
+      <c r="CE114" s="24" t="n"/>
+      <c r="CF114" s="24" t="n"/>
+      <c r="CG114" s="24" t="n"/>
+      <c r="CH114" s="24" t="n"/>
+      <c r="CI114" s="24" t="n"/>
+      <c r="CJ114" s="24" t="n"/>
+      <c r="CK114" s="24" t="n"/>
+      <c r="CL114" s="24" t="n"/>
+      <c r="CM114" s="24" t="n"/>
+      <c r="CN114" s="24" t="n"/>
+      <c r="CO114" s="24" t="n"/>
+      <c r="CP114" s="24" t="n"/>
+      <c r="CQ114" s="24" t="n"/>
+      <c r="CR114" s="24" t="n"/>
+      <c r="CS114" s="24" t="n"/>
+      <c r="CT114" s="24" t="n"/>
+      <c r="CU114" s="24" t="n"/>
+      <c r="CV114" s="24" t="n"/>
+      <c r="CW114" s="24" t="n"/>
+      <c r="CX114" s="24" t="n"/>
+      <c r="CY114" s="24" t="n"/>
+      <c r="CZ114" s="24" t="n"/>
+      <c r="DA114" s="24" t="n"/>
+      <c r="DB114" s="24" t="n"/>
+      <c r="DC114" s="24" t="n"/>
+      <c r="DD114" s="24" t="n"/>
+      <c r="DE114" s="24" t="n"/>
+      <c r="DF114" s="24" t="n"/>
+      <c r="DG114" s="24" t="n"/>
+      <c r="DH114" s="24" t="n"/>
+      <c r="DI114" s="24" t="n"/>
+      <c r="DJ114" s="24" t="n"/>
+      <c r="DK114" s="24" t="n"/>
+      <c r="DL114" s="24" t="n"/>
+      <c r="DM114" s="24" t="n"/>
+      <c r="DN114" s="24" t="n"/>
+      <c r="DO114" s="24" t="n"/>
+      <c r="DP114" s="24" t="n"/>
+    </row>
+    <row r="115" ht="36" customHeight="1">
+      <c r="A115" s="24" t="inlineStr">
+        <is>
+          <t>98602be4e1d84939</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C115" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-vexar-bge-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>Vexar</t>
+        </is>
+      </c>
+      <c r="H115" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I115" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J115" s="25" t="n"/>
+      <c r="K115" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M115" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N115" s="28" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="O115" s="28" t="n">
+        <v>0.5564</v>
+      </c>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="28" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="R115" s="26" t="n"/>
+      <c r="S115" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T115" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U115" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V115" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W115" s="26" t="n"/>
+      <c r="X115" s="26" t="n"/>
+      <c r="Y115" s="25" t="n"/>
+      <c r="Z115" s="26" t="n"/>
+      <c r="AA115" s="28" t="n"/>
+      <c r="AB115" s="28" t="n"/>
+      <c r="AC115" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="24" t="n"/>
+      <c r="AE115" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9GE15EMVV on aec-cs2-vexar-bge-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF115" s="31" t="n"/>
+      <c r="AG115" s="24" t="n"/>
+      <c r="AH115" s="24" t="n"/>
+      <c r="AI115" s="31" t="n"/>
+      <c r="AJ115" s="31" t="n"/>
+      <c r="AK115" s="24" t="n"/>
+      <c r="AL115" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM115" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN115" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO115" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP115" s="24" t="n"/>
+      <c r="AQ115" s="24" t="n"/>
+      <c r="AR115" s="24" t="n"/>
+      <c r="AS115" s="24" t="n"/>
+      <c r="AT115" s="24" t="n"/>
+      <c r="AU115" s="24" t="n"/>
+      <c r="AV115" s="24" t="n"/>
+      <c r="AW115" s="24" t="n"/>
+      <c r="AX115" s="24" t="n"/>
+      <c r="AY115" s="24" t="n"/>
+      <c r="AZ115" s="24" t="n"/>
+      <c r="BA115" s="24" t="n"/>
+      <c r="BB115" s="24" t="n"/>
+      <c r="BC115" s="24" t="n"/>
+      <c r="BD115" s="24" t="n"/>
+      <c r="BE115" s="24" t="n"/>
+      <c r="BF115" s="24" t="n"/>
+      <c r="BG115" s="24" t="n"/>
+      <c r="BH115" s="24" t="n"/>
+      <c r="BI115" s="24" t="n"/>
+      <c r="BJ115" s="25" t="n"/>
+      <c r="BK115" s="26" t="n"/>
+      <c r="BL115" s="27" t="n"/>
+      <c r="BM115" s="28" t="n"/>
+      <c r="BN115" s="28" t="n"/>
+      <c r="BO115" s="28" t="n"/>
+      <c r="BP115" s="25" t="n"/>
+      <c r="BQ115" s="27" t="n"/>
+      <c r="BR115" s="28" t="n"/>
+      <c r="BS115" s="28" t="n"/>
+      <c r="BT115" s="28" t="n"/>
+      <c r="BU115" s="25" t="n"/>
+      <c r="BV115" s="29" t="n"/>
+      <c r="BW115" s="24" t="n"/>
+      <c r="BX115" s="30" t="n"/>
+      <c r="BY115" s="27" t="n"/>
+      <c r="BZ115" s="24" t="n"/>
+      <c r="CA115" s="31" t="n"/>
+      <c r="CB115" s="24" t="n"/>
+      <c r="CC115" s="24" t="n"/>
+      <c r="CD115" s="24" t="n"/>
+      <c r="CE115" s="24" t="n"/>
+      <c r="CF115" s="24" t="n"/>
+      <c r="CG115" s="24" t="n"/>
+      <c r="CH115" s="24" t="n"/>
+      <c r="CI115" s="24" t="n"/>
+      <c r="CJ115" s="24" t="n"/>
+      <c r="CK115" s="24" t="n"/>
+      <c r="CL115" s="24" t="n"/>
+      <c r="CM115" s="24" t="n"/>
+      <c r="CN115" s="24" t="n"/>
+      <c r="CO115" s="24" t="n"/>
+      <c r="CP115" s="24" t="n"/>
+      <c r="CQ115" s="24" t="n"/>
+      <c r="CR115" s="24" t="n"/>
+      <c r="CS115" s="24" t="n"/>
+      <c r="CT115" s="24" t="n"/>
+      <c r="CU115" s="24" t="n"/>
+      <c r="CV115" s="24" t="n"/>
+      <c r="CW115" s="24" t="n"/>
+      <c r="CX115" s="24" t="n"/>
+      <c r="CY115" s="24" t="n"/>
+      <c r="CZ115" s="24" t="n"/>
+      <c r="DA115" s="24" t="n"/>
+      <c r="DB115" s="24" t="n"/>
+      <c r="DC115" s="24" t="n"/>
+      <c r="DD115" s="24" t="n"/>
+      <c r="DE115" s="24" t="n"/>
+      <c r="DF115" s="24" t="n"/>
+      <c r="DG115" s="24" t="n"/>
+      <c r="DH115" s="24" t="n"/>
+      <c r="DI115" s="24" t="n"/>
+      <c r="DJ115" s="24" t="n"/>
+      <c r="DK115" s="24" t="n"/>
+      <c r="DL115" s="24" t="n"/>
+      <c r="DM115" s="24" t="n"/>
+      <c r="DN115" s="24" t="n"/>
+      <c r="DO115" s="24" t="n"/>
+      <c r="DP115" s="24" t="n"/>
+    </row>
+    <row r="116" ht="36" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>59d5f8dca13249d0</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-is-nemi-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga</t>
+        </is>
+      </c>
+      <c r="G116" s="24" t="inlineStr">
+        <is>
+          <t>Iberian Soul</t>
+        </is>
+      </c>
+      <c r="H116" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I116" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J116" s="25" t="n"/>
+      <c r="K116" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L116" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M116" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N116" s="28" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="O116" s="28" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="28" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="R116" s="26" t="n"/>
+      <c r="S116" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T116" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U116" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V116" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W116" s="26" t="n"/>
+      <c r="X116" s="26" t="n"/>
+      <c r="Y116" s="25" t="n"/>
+      <c r="Z116" s="26" t="n"/>
+      <c r="AA116" s="28" t="n"/>
+      <c r="AB116" s="28" t="n"/>
+      <c r="AC116" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD116" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE116" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAPZXQGMW0 on aec-cs2-is-nemi-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF116" s="31" t="n"/>
+      <c r="AG116" s="24" t="n"/>
+      <c r="AH116" s="24" t="n"/>
+      <c r="AI116" s="31" t="n"/>
+      <c r="AJ116" s="31" t="n"/>
+      <c r="AK116" s="24" t="n"/>
+      <c r="AL116" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM116" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN116" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO116" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP116" s="24" t="n"/>
+      <c r="AQ116" s="24" t="n"/>
+      <c r="AR116" s="24" t="n"/>
+      <c r="AS116" s="24" t="n"/>
+      <c r="AT116" s="24" t="n"/>
+      <c r="AU116" s="24" t="n"/>
+      <c r="AV116" s="24" t="n"/>
+      <c r="AW116" s="24" t="n"/>
+      <c r="AX116" s="24" t="n"/>
+      <c r="AY116" s="24" t="n"/>
+      <c r="AZ116" s="24" t="n"/>
+      <c r="BA116" s="24" t="n"/>
+      <c r="BB116" s="24" t="n"/>
+      <c r="BC116" s="24" t="n"/>
+      <c r="BD116" s="24" t="n"/>
+      <c r="BE116" s="24" t="n"/>
+      <c r="BF116" s="24" t="n"/>
+      <c r="BG116" s="24" t="n"/>
+      <c r="BH116" s="24" t="n"/>
+      <c r="BI116" s="24" t="n"/>
+      <c r="BJ116" s="25" t="n"/>
+      <c r="BK116" s="26" t="n"/>
+      <c r="BL116" s="27" t="n"/>
+      <c r="BM116" s="28" t="n"/>
+      <c r="BN116" s="28" t="n"/>
+      <c r="BO116" s="28" t="n"/>
+      <c r="BP116" s="25" t="n"/>
+      <c r="BQ116" s="27" t="n"/>
+      <c r="BR116" s="28" t="n"/>
+      <c r="BS116" s="28" t="n"/>
+      <c r="BT116" s="28" t="n"/>
+      <c r="BU116" s="25" t="n"/>
+      <c r="BV116" s="29" t="n"/>
+      <c r="BW116" s="24" t="n"/>
+      <c r="BX116" s="30" t="n"/>
+      <c r="BY116" s="27" t="n"/>
+      <c r="BZ116" s="24" t="n"/>
+      <c r="CA116" s="31" t="n"/>
+      <c r="CB116" s="24" t="n"/>
+      <c r="CC116" s="24" t="n"/>
+      <c r="CD116" s="24" t="n"/>
+      <c r="CE116" s="24" t="n"/>
+      <c r="CF116" s="24" t="n"/>
+      <c r="CG116" s="24" t="n"/>
+      <c r="CH116" s="24" t="n"/>
+      <c r="CI116" s="24" t="n"/>
+      <c r="CJ116" s="24" t="n"/>
+      <c r="CK116" s="24" t="n"/>
+      <c r="CL116" s="24" t="n"/>
+      <c r="CM116" s="24" t="n"/>
+      <c r="CN116" s="24" t="n"/>
+      <c r="CO116" s="24" t="n"/>
+      <c r="CP116" s="24" t="n"/>
+      <c r="CQ116" s="24" t="n"/>
+      <c r="CR116" s="24" t="n"/>
+      <c r="CS116" s="24" t="n"/>
+      <c r="CT116" s="24" t="n"/>
+      <c r="CU116" s="24" t="n"/>
+      <c r="CV116" s="24" t="n"/>
+      <c r="CW116" s="24" t="n"/>
+      <c r="CX116" s="24" t="n"/>
+      <c r="CY116" s="24" t="n"/>
+      <c r="CZ116" s="24" t="n"/>
+      <c r="DA116" s="24" t="n"/>
+      <c r="DB116" s="24" t="n"/>
+      <c r="DC116" s="24" t="n"/>
+      <c r="DD116" s="24" t="n"/>
+      <c r="DE116" s="24" t="n"/>
+      <c r="DF116" s="24" t="n"/>
+      <c r="DG116" s="24" t="n"/>
+      <c r="DH116" s="24" t="n"/>
+      <c r="DI116" s="24" t="n"/>
+      <c r="DJ116" s="24" t="n"/>
+      <c r="DK116" s="24" t="n"/>
+      <c r="DL116" s="24" t="n"/>
+      <c r="DM116" s="24" t="n"/>
+      <c r="DN116" s="24" t="n"/>
+      <c r="DO116" s="24" t="n"/>
+      <c r="DP116" s="24" t="n"/>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="A117" s="24" t="inlineStr">
+        <is>
+          <t>c3b52dee2e854cfa</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-for-biga-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>BIG Academy</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="H117" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I117" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J117" s="25" t="n"/>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L117" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M117" s="27" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="N117" s="28" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="O117" s="28" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="28" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="R117" s="26" t="n"/>
+      <c r="S117" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T117" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U117" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V117" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W117" s="26" t="n"/>
+      <c r="X117" s="26" t="n"/>
+      <c r="Y117" s="25" t="n"/>
+      <c r="Z117" s="26" t="n"/>
+      <c r="AA117" s="28" t="n"/>
+      <c r="AB117" s="28" t="n"/>
+      <c r="AC117" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="24" t="n"/>
+      <c r="AE117" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9JDN66MW1 on aec-cs2-for-biga-2026-09-03 (short)</t>
+        </is>
+      </c>
+      <c r="AF117" s="31" t="n"/>
+      <c r="AG117" s="24" t="n"/>
+      <c r="AH117" s="24" t="n"/>
+      <c r="AI117" s="31" t="n"/>
+      <c r="AJ117" s="31" t="n"/>
+      <c r="AK117" s="24" t="n"/>
+      <c r="AL117" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM117" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN117" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO117" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP117" s="24" t="n"/>
+      <c r="AQ117" s="24" t="n"/>
+      <c r="AR117" s="24" t="n"/>
+      <c r="AS117" s="24" t="n"/>
+      <c r="AT117" s="24" t="n"/>
+      <c r="AU117" s="24" t="n"/>
+      <c r="AV117" s="24" t="n"/>
+      <c r="AW117" s="24" t="n"/>
+      <c r="AX117" s="24" t="n"/>
+      <c r="AY117" s="24" t="n"/>
+      <c r="AZ117" s="24" t="n"/>
+      <c r="BA117" s="24" t="n"/>
+      <c r="BB117" s="24" t="n"/>
+      <c r="BC117" s="24" t="n"/>
+      <c r="BD117" s="24" t="n"/>
+      <c r="BE117" s="24" t="n"/>
+      <c r="BF117" s="24" t="n"/>
+      <c r="BG117" s="24" t="n"/>
+      <c r="BH117" s="24" t="n"/>
+      <c r="BI117" s="24" t="n"/>
+      <c r="BJ117" s="25" t="n"/>
+      <c r="BK117" s="26" t="n"/>
+      <c r="BL117" s="27" t="n"/>
+      <c r="BM117" s="28" t="n"/>
+      <c r="BN117" s="28" t="n"/>
+      <c r="BO117" s="28" t="n"/>
+      <c r="BP117" s="25" t="n"/>
+      <c r="BQ117" s="27" t="n"/>
+      <c r="BR117" s="28" t="n"/>
+      <c r="BS117" s="28" t="n"/>
+      <c r="BT117" s="28" t="n"/>
+      <c r="BU117" s="25" t="n"/>
+      <c r="BV117" s="29" t="n"/>
+      <c r="BW117" s="24" t="n"/>
+      <c r="BX117" s="30" t="n"/>
+      <c r="BY117" s="27" t="n"/>
+      <c r="BZ117" s="24" t="n"/>
+      <c r="CA117" s="31" t="n"/>
+      <c r="CB117" s="24" t="n"/>
+      <c r="CC117" s="24" t="n"/>
+      <c r="CD117" s="24" t="n"/>
+      <c r="CE117" s="24" t="n"/>
+      <c r="CF117" s="24" t="n"/>
+      <c r="CG117" s="24" t="n"/>
+      <c r="CH117" s="24" t="n"/>
+      <c r="CI117" s="24" t="n"/>
+      <c r="CJ117" s="24" t="n"/>
+      <c r="CK117" s="24" t="n"/>
+      <c r="CL117" s="24" t="n"/>
+      <c r="CM117" s="24" t="n"/>
+      <c r="CN117" s="24" t="n"/>
+      <c r="CO117" s="24" t="n"/>
+      <c r="CP117" s="24" t="n"/>
+      <c r="CQ117" s="24" t="n"/>
+      <c r="CR117" s="24" t="n"/>
+      <c r="CS117" s="24" t="n"/>
+      <c r="CT117" s="24" t="n"/>
+      <c r="CU117" s="24" t="n"/>
+      <c r="CV117" s="24" t="n"/>
+      <c r="CW117" s="24" t="n"/>
+      <c r="CX117" s="24" t="n"/>
+      <c r="CY117" s="24" t="n"/>
+      <c r="CZ117" s="24" t="n"/>
+      <c r="DA117" s="24" t="n"/>
+      <c r="DB117" s="24" t="n"/>
+      <c r="DC117" s="24" t="n"/>
+      <c r="DD117" s="24" t="n"/>
+      <c r="DE117" s="24" t="n"/>
+      <c r="DF117" s="24" t="n"/>
+      <c r="DG117" s="24" t="n"/>
+      <c r="DH117" s="24" t="n"/>
+      <c r="DI117" s="24" t="n"/>
+      <c r="DJ117" s="24" t="n"/>
+      <c r="DK117" s="24" t="n"/>
+      <c r="DL117" s="24" t="n"/>
+      <c r="DM117" s="24" t="n"/>
+      <c r="DN117" s="24" t="n"/>
+      <c r="DO117" s="24" t="n"/>
+      <c r="DP117" s="24" t="n"/>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>fe6312d3e15e40dd</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-leo-tlr-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>The Last Resort</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>Leo Team</t>
+        </is>
+      </c>
+      <c r="H118" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I118" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J118" s="25" t="n"/>
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L118" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M118" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N118" s="28" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="O118" s="28" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="28" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="R118" s="26" t="n"/>
+      <c r="S118" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T118" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U118" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V118" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W118" s="26" t="n"/>
+      <c r="X118" s="26" t="n"/>
+      <c r="Y118" s="25" t="n"/>
+      <c r="Z118" s="26" t="n"/>
+      <c r="AA118" s="28" t="n"/>
+      <c r="AB118" s="28" t="n"/>
+      <c r="AC118" s="30" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="AD118" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE118" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SAJ759CMVR on aec-cs2-leo-tlr-2026-09-03 (short)</t>
+        </is>
+      </c>
+      <c r="AF118" s="31" t="n"/>
+      <c r="AG118" s="24" t="n"/>
+      <c r="AH118" s="24" t="n"/>
+      <c r="AI118" s="31" t="n"/>
+      <c r="AJ118" s="31" t="n"/>
+      <c r="AK118" s="24" t="n"/>
+      <c r="AL118" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM118" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN118" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO118" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP118" s="24" t="n"/>
+      <c r="AQ118" s="24" t="n"/>
+      <c r="AR118" s="24" t="n"/>
+      <c r="AS118" s="24" t="n"/>
+      <c r="AT118" s="24" t="n"/>
+      <c r="AU118" s="24" t="n"/>
+      <c r="AV118" s="24" t="n"/>
+      <c r="AW118" s="24" t="n"/>
+      <c r="AX118" s="24" t="n"/>
+      <c r="AY118" s="24" t="n"/>
+      <c r="AZ118" s="24" t="n"/>
+      <c r="BA118" s="24" t="n"/>
+      <c r="BB118" s="24" t="n"/>
+      <c r="BC118" s="24" t="n"/>
+      <c r="BD118" s="24" t="n"/>
+      <c r="BE118" s="24" t="n"/>
+      <c r="BF118" s="24" t="n"/>
+      <c r="BG118" s="24" t="n"/>
+      <c r="BH118" s="24" t="n"/>
+      <c r="BI118" s="24" t="n"/>
+      <c r="BJ118" s="25" t="n"/>
+      <c r="BK118" s="26" t="n"/>
+      <c r="BL118" s="27" t="n"/>
+      <c r="BM118" s="28" t="n"/>
+      <c r="BN118" s="28" t="n"/>
+      <c r="BO118" s="28" t="n"/>
+      <c r="BP118" s="25" t="n"/>
+      <c r="BQ118" s="27" t="n"/>
+      <c r="BR118" s="28" t="n"/>
+      <c r="BS118" s="28" t="n"/>
+      <c r="BT118" s="28" t="n"/>
+      <c r="BU118" s="25" t="n"/>
+      <c r="BV118" s="29" t="n"/>
+      <c r="BW118" s="24" t="n"/>
+      <c r="BX118" s="30" t="n"/>
+      <c r="BY118" s="27" t="n"/>
+      <c r="BZ118" s="24" t="n"/>
+      <c r="CA118" s="31" t="n"/>
+      <c r="CB118" s="24" t="n"/>
+      <c r="CC118" s="24" t="n"/>
+      <c r="CD118" s="24" t="n"/>
+      <c r="CE118" s="24" t="n"/>
+      <c r="CF118" s="24" t="n"/>
+      <c r="CG118" s="24" t="n"/>
+      <c r="CH118" s="24" t="n"/>
+      <c r="CI118" s="24" t="n"/>
+      <c r="CJ118" s="24" t="n"/>
+      <c r="CK118" s="24" t="n"/>
+      <c r="CL118" s="24" t="n"/>
+      <c r="CM118" s="24" t="n"/>
+      <c r="CN118" s="24" t="n"/>
+      <c r="CO118" s="24" t="n"/>
+      <c r="CP118" s="24" t="n"/>
+      <c r="CQ118" s="24" t="n"/>
+      <c r="CR118" s="24" t="n"/>
+      <c r="CS118" s="24" t="n"/>
+      <c r="CT118" s="24" t="n"/>
+      <c r="CU118" s="24" t="n"/>
+      <c r="CV118" s="24" t="n"/>
+      <c r="CW118" s="24" t="n"/>
+      <c r="CX118" s="24" t="n"/>
+      <c r="CY118" s="24" t="n"/>
+      <c r="CZ118" s="24" t="n"/>
+      <c r="DA118" s="24" t="n"/>
+      <c r="DB118" s="24" t="n"/>
+      <c r="DC118" s="24" t="n"/>
+      <c r="DD118" s="24" t="n"/>
+      <c r="DE118" s="24" t="n"/>
+      <c r="DF118" s="24" t="n"/>
+      <c r="DG118" s="24" t="n"/>
+      <c r="DH118" s="24" t="n"/>
+      <c r="DI118" s="24" t="n"/>
+      <c r="DJ118" s="24" t="n"/>
+      <c r="DK118" s="24" t="n"/>
+      <c r="DL118" s="24" t="n"/>
+      <c r="DM118" s="24" t="n"/>
+      <c r="DN118" s="24" t="n"/>
+      <c r="DO118" s="24" t="n"/>
+      <c r="DP118" s="24" t="n"/>
+    </row>
+    <row r="119" ht="36" customHeight="1">
+      <c r="A119" s="24" t="inlineStr">
+        <is>
+          <t>b0078c89886b41a1</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-hotu-nem-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>Team Nemesis</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="inlineStr">
+        <is>
+          <t>HOTU</t>
+        </is>
+      </c>
+      <c r="H119" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I119" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J119" s="25" t="n"/>
+      <c r="K119" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L119" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M119" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N119" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O119" s="28" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="28" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="R119" s="26" t="n"/>
+      <c r="S119" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U119" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V119" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W119" s="26" t="n"/>
+      <c r="X119" s="26" t="n"/>
+      <c r="Y119" s="25" t="n"/>
+      <c r="Z119" s="26" t="n"/>
+      <c r="AA119" s="28" t="n"/>
+      <c r="AB119" s="28" t="n"/>
+      <c r="AC119" s="30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD119" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE119" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SADEXSEMVK on aec-cs2-hotu-nem-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF119" s="31" t="n"/>
+      <c r="AG119" s="24" t="n"/>
+      <c r="AH119" s="24" t="n"/>
+      <c r="AI119" s="31" t="n"/>
+      <c r="AJ119" s="31" t="n"/>
+      <c r="AK119" s="24" t="n"/>
+      <c r="AL119" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM119" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN119" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO119" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP119" s="24" t="n"/>
+      <c r="AQ119" s="24" t="n"/>
+      <c r="AR119" s="24" t="n"/>
+      <c r="AS119" s="24" t="n"/>
+      <c r="AT119" s="24" t="n"/>
+      <c r="AU119" s="24" t="n"/>
+      <c r="AV119" s="24" t="n"/>
+      <c r="AW119" s="24" t="n"/>
+      <c r="AX119" s="24" t="n"/>
+      <c r="AY119" s="24" t="n"/>
+      <c r="AZ119" s="24" t="n"/>
+      <c r="BA119" s="24" t="n"/>
+      <c r="BB119" s="24" t="n"/>
+      <c r="BC119" s="24" t="n"/>
+      <c r="BD119" s="24" t="n"/>
+      <c r="BE119" s="24" t="n"/>
+      <c r="BF119" s="24" t="n"/>
+      <c r="BG119" s="24" t="n"/>
+      <c r="BH119" s="24" t="n"/>
+      <c r="BI119" s="24" t="n"/>
+      <c r="BJ119" s="25" t="n"/>
+      <c r="BK119" s="26" t="n"/>
+      <c r="BL119" s="27" t="n"/>
+      <c r="BM119" s="28" t="n"/>
+      <c r="BN119" s="28" t="n"/>
+      <c r="BO119" s="28" t="n"/>
+      <c r="BP119" s="25" t="n"/>
+      <c r="BQ119" s="27" t="n"/>
+      <c r="BR119" s="28" t="n"/>
+      <c r="BS119" s="28" t="n"/>
+      <c r="BT119" s="28" t="n"/>
+      <c r="BU119" s="25" t="n"/>
+      <c r="BV119" s="29" t="n"/>
+      <c r="BW119" s="24" t="n"/>
+      <c r="BX119" s="30" t="n"/>
+      <c r="BY119" s="27" t="n"/>
+      <c r="BZ119" s="24" t="n"/>
+      <c r="CA119" s="31" t="n"/>
+      <c r="CB119" s="24" t="n"/>
+      <c r="CC119" s="24" t="n"/>
+      <c r="CD119" s="24" t="n"/>
+      <c r="CE119" s="24" t="n"/>
+      <c r="CF119" s="24" t="n"/>
+      <c r="CG119" s="24" t="n"/>
+      <c r="CH119" s="24" t="n"/>
+      <c r="CI119" s="24" t="n"/>
+      <c r="CJ119" s="24" t="n"/>
+      <c r="CK119" s="24" t="n"/>
+      <c r="CL119" s="24" t="n"/>
+      <c r="CM119" s="24" t="n"/>
+      <c r="CN119" s="24" t="n"/>
+      <c r="CO119" s="24" t="n"/>
+      <c r="CP119" s="24" t="n"/>
+      <c r="CQ119" s="24" t="n"/>
+      <c r="CR119" s="24" t="n"/>
+      <c r="CS119" s="24" t="n"/>
+      <c r="CT119" s="24" t="n"/>
+      <c r="CU119" s="24" t="n"/>
+      <c r="CV119" s="24" t="n"/>
+      <c r="CW119" s="24" t="n"/>
+      <c r="CX119" s="24" t="n"/>
+      <c r="CY119" s="24" t="n"/>
+      <c r="CZ119" s="24" t="n"/>
+      <c r="DA119" s="24" t="n"/>
+      <c r="DB119" s="24" t="n"/>
+      <c r="DC119" s="24" t="n"/>
+      <c r="DD119" s="24" t="n"/>
+      <c r="DE119" s="24" t="n"/>
+      <c r="DF119" s="24" t="n"/>
+      <c r="DG119" s="24" t="n"/>
+      <c r="DH119" s="24" t="n"/>
+      <c r="DI119" s="24" t="n"/>
+      <c r="DJ119" s="24" t="n"/>
+      <c r="DK119" s="24" t="n"/>
+      <c r="DL119" s="24" t="n"/>
+      <c r="DM119" s="24" t="n"/>
+      <c r="DN119" s="24" t="n"/>
+      <c r="DO119" s="24" t="n"/>
+      <c r="DP119" s="24" t="n"/>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="A120" s="24" t="inlineStr">
+        <is>
+          <t>008720233ab74009</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-k27-nemi-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>K27</t>
+        </is>
+      </c>
+      <c r="H120" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I120" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J120" s="25" t="n"/>
+      <c r="K120" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L120" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M120" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O120" s="28" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="28" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="R120" s="26" t="n"/>
+      <c r="S120" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U120" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V120" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W120" s="26" t="n"/>
+      <c r="X120" s="26" t="n"/>
+      <c r="Y120" s="25" t="n"/>
+      <c r="Z120" s="26" t="n"/>
+      <c r="AA120" s="28" t="n"/>
+      <c r="AB120" s="28" t="n"/>
+      <c r="AC120" s="30" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AD120" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE120" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9ZJRFWMVY on aec-cs2-k27-nemi-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF120" s="31" t="n"/>
+      <c r="AG120" s="24" t="n"/>
+      <c r="AH120" s="24" t="n"/>
+      <c r="AI120" s="31" t="n"/>
+      <c r="AJ120" s="31" t="n"/>
+      <c r="AK120" s="24" t="n"/>
+      <c r="AL120" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM120" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN120" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO120" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP120" s="24" t="n"/>
+      <c r="AQ120" s="24" t="n"/>
+      <c r="AR120" s="24" t="n"/>
+      <c r="AS120" s="24" t="n"/>
+      <c r="AT120" s="24" t="n"/>
+      <c r="AU120" s="24" t="n"/>
+      <c r="AV120" s="24" t="n"/>
+      <c r="AW120" s="24" t="n"/>
+      <c r="AX120" s="24" t="n"/>
+      <c r="AY120" s="24" t="n"/>
+      <c r="AZ120" s="24" t="n"/>
+      <c r="BA120" s="24" t="n"/>
+      <c r="BB120" s="24" t="n"/>
+      <c r="BC120" s="24" t="n"/>
+      <c r="BD120" s="24" t="n"/>
+      <c r="BE120" s="24" t="n"/>
+      <c r="BF120" s="24" t="n"/>
+      <c r="BG120" s="24" t="n"/>
+      <c r="BH120" s="24" t="n"/>
+      <c r="BI120" s="24" t="n"/>
+      <c r="BJ120" s="25" t="n"/>
+      <c r="BK120" s="26" t="n"/>
+      <c r="BL120" s="27" t="n"/>
+      <c r="BM120" s="28" t="n"/>
+      <c r="BN120" s="28" t="n"/>
+      <c r="BO120" s="28" t="n"/>
+      <c r="BP120" s="25" t="n"/>
+      <c r="BQ120" s="27" t="n"/>
+      <c r="BR120" s="28" t="n"/>
+      <c r="BS120" s="28" t="n"/>
+      <c r="BT120" s="28" t="n"/>
+      <c r="BU120" s="25" t="n"/>
+      <c r="BV120" s="29" t="n"/>
+      <c r="BW120" s="24" t="n"/>
+      <c r="BX120" s="30" t="n"/>
+      <c r="BY120" s="27" t="n"/>
+      <c r="BZ120" s="24" t="n"/>
+      <c r="CA120" s="31" t="n"/>
+      <c r="CB120" s="24" t="n"/>
+      <c r="CC120" s="24" t="n"/>
+      <c r="CD120" s="24" t="n"/>
+      <c r="CE120" s="24" t="n"/>
+      <c r="CF120" s="24" t="n"/>
+      <c r="CG120" s="24" t="n"/>
+      <c r="CH120" s="24" t="n"/>
+      <c r="CI120" s="24" t="n"/>
+      <c r="CJ120" s="24" t="n"/>
+      <c r="CK120" s="24" t="n"/>
+      <c r="CL120" s="24" t="n"/>
+      <c r="CM120" s="24" t="n"/>
+      <c r="CN120" s="24" t="n"/>
+      <c r="CO120" s="24" t="n"/>
+      <c r="CP120" s="24" t="n"/>
+      <c r="CQ120" s="24" t="n"/>
+      <c r="CR120" s="24" t="n"/>
+      <c r="CS120" s="24" t="n"/>
+      <c r="CT120" s="24" t="n"/>
+      <c r="CU120" s="24" t="n"/>
+      <c r="CV120" s="24" t="n"/>
+      <c r="CW120" s="24" t="n"/>
+      <c r="CX120" s="24" t="n"/>
+      <c r="CY120" s="24" t="n"/>
+      <c r="CZ120" s="24" t="n"/>
+      <c r="DA120" s="24" t="n"/>
+      <c r="DB120" s="24" t="n"/>
+      <c r="DC120" s="24" t="n"/>
+      <c r="DD120" s="24" t="n"/>
+      <c r="DE120" s="24" t="n"/>
+      <c r="DF120" s="24" t="n"/>
+      <c r="DG120" s="24" t="n"/>
+      <c r="DH120" s="24" t="n"/>
+      <c r="DI120" s="24" t="n"/>
+      <c r="DJ120" s="24" t="n"/>
+      <c r="DK120" s="24" t="n"/>
+      <c r="DL120" s="24" t="n"/>
+      <c r="DM120" s="24" t="n"/>
+      <c r="DN120" s="24" t="n"/>
+      <c r="DO120" s="24" t="n"/>
+      <c r="DP120" s="24" t="n"/>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="24" t="inlineStr">
+        <is>
+          <t>13e14aa86506432f</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C121" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-mgc-big-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>BIG</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="inlineStr">
+        <is>
+          <t>magic</t>
+        </is>
+      </c>
+      <c r="H121" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I121" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J121" s="25" t="n"/>
+      <c r="K121" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L121" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M121" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N121" s="28" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="O121" s="28" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="28" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="R121" s="26" t="n"/>
+      <c r="S121" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T121" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U121" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V121" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W121" s="26" t="n"/>
+      <c r="X121" s="26" t="n"/>
+      <c r="Y121" s="25" t="n"/>
+      <c r="Z121" s="26" t="n"/>
+      <c r="AA121" s="28" t="n"/>
+      <c r="AB121" s="28" t="n"/>
+      <c r="AC121" s="30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD121" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:41:14.239238Z</t>
+        </is>
+      </c>
+      <c r="AE121" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8S9JDPXWMW1 on aec-cs2-mgc-big-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF121" s="31" t="n"/>
+      <c r="AG121" s="24" t="n"/>
+      <c r="AH121" s="24" t="n"/>
+      <c r="AI121" s="31" t="n"/>
+      <c r="AJ121" s="31" t="n"/>
+      <c r="AK121" s="24" t="n"/>
+      <c r="AL121" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM121" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN121" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO121" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP121" s="24" t="n"/>
+      <c r="AQ121" s="24" t="n"/>
+      <c r="AR121" s="24" t="n"/>
+      <c r="AS121" s="24" t="n"/>
+      <c r="AT121" s="24" t="n"/>
+      <c r="AU121" s="24" t="n"/>
+      <c r="AV121" s="24" t="n"/>
+      <c r="AW121" s="24" t="n"/>
+      <c r="AX121" s="24" t="n"/>
+      <c r="AY121" s="24" t="n"/>
+      <c r="AZ121" s="24" t="n"/>
+      <c r="BA121" s="24" t="n"/>
+      <c r="BB121" s="24" t="n"/>
+      <c r="BC121" s="24" t="n"/>
+      <c r="BD121" s="24" t="n"/>
+      <c r="BE121" s="24" t="n"/>
+      <c r="BF121" s="24" t="n"/>
+      <c r="BG121" s="24" t="n"/>
+      <c r="BH121" s="24" t="n"/>
+      <c r="BI121" s="24" t="n"/>
+      <c r="BJ121" s="25" t="n"/>
+      <c r="BK121" s="26" t="n"/>
+      <c r="BL121" s="27" t="n"/>
+      <c r="BM121" s="28" t="n"/>
+      <c r="BN121" s="28" t="n"/>
+      <c r="BO121" s="28" t="n"/>
+      <c r="BP121" s="25" t="n"/>
+      <c r="BQ121" s="27" t="n"/>
+      <c r="BR121" s="28" t="n"/>
+      <c r="BS121" s="28" t="n"/>
+      <c r="BT121" s="28" t="n"/>
+      <c r="BU121" s="25" t="n"/>
+      <c r="BV121" s="29" t="n"/>
+      <c r="BW121" s="24" t="n"/>
+      <c r="BX121" s="30" t="n"/>
+      <c r="BY121" s="27" t="n"/>
+      <c r="BZ121" s="24" t="n"/>
+      <c r="CA121" s="31" t="n"/>
+      <c r="CB121" s="24" t="n"/>
+      <c r="CC121" s="24" t="n"/>
+      <c r="CD121" s="24" t="n"/>
+      <c r="CE121" s="24" t="n"/>
+      <c r="CF121" s="24" t="n"/>
+      <c r="CG121" s="24" t="n"/>
+      <c r="CH121" s="24" t="n"/>
+      <c r="CI121" s="24" t="n"/>
+      <c r="CJ121" s="24" t="n"/>
+      <c r="CK121" s="24" t="n"/>
+      <c r="CL121" s="24" t="n"/>
+      <c r="CM121" s="24" t="n"/>
+      <c r="CN121" s="24" t="n"/>
+      <c r="CO121" s="24" t="n"/>
+      <c r="CP121" s="24" t="n"/>
+      <c r="CQ121" s="24" t="n"/>
+      <c r="CR121" s="24" t="n"/>
+      <c r="CS121" s="24" t="n"/>
+      <c r="CT121" s="24" t="n"/>
+      <c r="CU121" s="24" t="n"/>
+      <c r="CV121" s="24" t="n"/>
+      <c r="CW121" s="24" t="n"/>
+      <c r="CX121" s="24" t="n"/>
+      <c r="CY121" s="24" t="n"/>
+      <c r="CZ121" s="24" t="n"/>
+      <c r="DA121" s="24" t="n"/>
+      <c r="DB121" s="24" t="n"/>
+      <c r="DC121" s="24" t="n"/>
+      <c r="DD121" s="24" t="n"/>
+      <c r="DE121" s="24" t="n"/>
+      <c r="DF121" s="24" t="n"/>
+      <c r="DG121" s="24" t="n"/>
+      <c r="DH121" s="24" t="n"/>
+      <c r="DI121" s="24" t="n"/>
+      <c r="DJ121" s="24" t="n"/>
+      <c r="DK121" s="24" t="n"/>
+      <c r="DL121" s="24" t="n"/>
+      <c r="DM121" s="24" t="n"/>
+      <c r="DN121" s="24" t="n"/>
+      <c r="DO121" s="24" t="n"/>
+      <c r="DP121" s="24" t="n"/>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="24" t="inlineStr">
+        <is>
+          <t>4d37bfccafc046d9</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:38:33.638803Z</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-ntr-ef-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="H122" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I122" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J122" s="25" t="n"/>
+      <c r="K122" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L122" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M122" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N122" s="28" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O122" s="28" t="n">
+        <v>0.6431</v>
+      </c>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="28" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="R122" s="26" t="n"/>
+      <c r="S122" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T122" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U122" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V122" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W122" s="26" t="n"/>
+      <c r="X122" s="26" t="n"/>
+      <c r="Y122" s="25" t="n"/>
+      <c r="Z122" s="26" t="n"/>
+      <c r="AA122" s="28" t="n"/>
+      <c r="AB122" s="28" t="n"/>
+      <c r="AC122" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="24" t="n"/>
+      <c r="AE122" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8SADEYG6MVK on aec-cs2-ntr-ef-2026-09-03 (long)</t>
+        </is>
+      </c>
+      <c r="AF122" s="31" t="n"/>
+      <c r="AG122" s="24" t="n"/>
+      <c r="AH122" s="24" t="n"/>
+      <c r="AI122" s="31" t="n"/>
+      <c r="AJ122" s="31" t="n"/>
+      <c r="AK122" s="24" t="n"/>
+      <c r="AL122" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM122" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN122" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO122" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP122" s="24" t="n"/>
+      <c r="AQ122" s="24" t="n"/>
+      <c r="AR122" s="24" t="n"/>
+      <c r="AS122" s="24" t="n"/>
+      <c r="AT122" s="24" t="n"/>
+      <c r="AU122" s="24" t="n"/>
+      <c r="AV122" s="24" t="n"/>
+      <c r="AW122" s="24" t="n"/>
+      <c r="AX122" s="24" t="n"/>
+      <c r="AY122" s="24" t="n"/>
+      <c r="AZ122" s="24" t="n"/>
+      <c r="BA122" s="24" t="n"/>
+      <c r="BB122" s="24" t="n"/>
+      <c r="BC122" s="24" t="n"/>
+      <c r="BD122" s="24" t="n"/>
+      <c r="BE122" s="24" t="n"/>
+      <c r="BF122" s="24" t="n"/>
+      <c r="BG122" s="24" t="n"/>
+      <c r="BH122" s="24" t="n"/>
+      <c r="BI122" s="24" t="n"/>
+      <c r="BJ122" s="25" t="n"/>
+      <c r="BK122" s="26" t="n"/>
+      <c r="BL122" s="27" t="n"/>
+      <c r="BM122" s="28" t="n"/>
+      <c r="BN122" s="28" t="n"/>
+      <c r="BO122" s="28" t="n"/>
+      <c r="BP122" s="25" t="n"/>
+      <c r="BQ122" s="27" t="n"/>
+      <c r="BR122" s="28" t="n"/>
+      <c r="BS122" s="28" t="n"/>
+      <c r="BT122" s="28" t="n"/>
+      <c r="BU122" s="25" t="n"/>
+      <c r="BV122" s="29" t="n"/>
+      <c r="BW122" s="24" t="n"/>
+      <c r="BX122" s="30" t="n"/>
+      <c r="BY122" s="27" t="n"/>
+      <c r="BZ122" s="24" t="n"/>
+      <c r="CA122" s="31" t="n"/>
+      <c r="CB122" s="24" t="n"/>
+      <c r="CC122" s="24" t="n"/>
+      <c r="CD122" s="24" t="n"/>
+      <c r="CE122" s="24" t="n"/>
+      <c r="CF122" s="24" t="n"/>
+      <c r="CG122" s="24" t="n"/>
+      <c r="CH122" s="24" t="n"/>
+      <c r="CI122" s="24" t="n"/>
+      <c r="CJ122" s="24" t="n"/>
+      <c r="CK122" s="24" t="n"/>
+      <c r="CL122" s="24" t="n"/>
+      <c r="CM122" s="24" t="n"/>
+      <c r="CN122" s="24" t="n"/>
+      <c r="CO122" s="24" t="n"/>
+      <c r="CP122" s="24" t="n"/>
+      <c r="CQ122" s="24" t="n"/>
+      <c r="CR122" s="24" t="n"/>
+      <c r="CS122" s="24" t="n"/>
+      <c r="CT122" s="24" t="n"/>
+      <c r="CU122" s="24" t="n"/>
+      <c r="CV122" s="24" t="n"/>
+      <c r="CW122" s="24" t="n"/>
+      <c r="CX122" s="24" t="n"/>
+      <c r="CY122" s="24" t="n"/>
+      <c r="CZ122" s="24" t="n"/>
+      <c r="DA122" s="24" t="n"/>
+      <c r="DB122" s="24" t="n"/>
+      <c r="DC122" s="24" t="n"/>
+      <c r="DD122" s="24" t="n"/>
+      <c r="DE122" s="24" t="n"/>
+      <c r="DF122" s="24" t="n"/>
+      <c r="DG122" s="24" t="n"/>
+      <c r="DH122" s="24" t="n"/>
+      <c r="DI122" s="24" t="n"/>
+      <c r="DJ122" s="24" t="n"/>
+      <c r="DK122" s="24" t="n"/>
+      <c r="DL122" s="24" t="n"/>
+      <c r="DM122" s="24" t="n"/>
+      <c r="DN122" s="24" t="n"/>
+      <c r="DO122" s="24" t="n"/>
+      <c r="DP122" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/auto_buyer_picks.xlsx
+++ b/data/auto_buyer_picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP122" headerRowCount="1">
-  <autoFilter ref="A1:DP122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DP139" headerRowCount="1">
+  <autoFilter ref="A1:DP139"/>
   <tableColumns count="120">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -779,19 +779,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$122)</f>
+        <f>COUNTA('Picks'!$A$2:$A$139)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$122,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$139,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$122,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")+COUNTIFS('Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")+COUNTIFS('Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -819,19 +819,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$122,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$139,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")/(COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"win")+COUNTIFS('Picks'!$BX$2:$BX$122,"&gt;0",'Picks'!$V$2:$V$122,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")/(COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"win")+COUNTIFS('Picks'!$BX$2:$BX$139,"&gt;0",'Picks'!$V$2:$V$139,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$122)/SUM('Picks'!$BX$2:$BX$122),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$139)/SUM('Picks'!$BX$2:$BX$139),0)</f>
         <v/>
       </c>
     </row>
@@ -859,19 +859,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$122)</f>
+        <f>SUM('Picks'!$BY$2:$BY$139)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$122,"&lt;&gt;",'Picks'!$AB$2:$AB$122),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$139,"&lt;&gt;",'Picks'!$AB$2:$AB$139),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$122,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$122,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$139,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$122,'Picks'!$AM$2:$AM$122,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$139,'Picks'!$AM$2:$AM$139,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -926,15 +926,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -942,11 +942,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A14,'Picks'!$U$2:$U$122,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A14,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -957,15 +957,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -973,11 +973,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A15,'Picks'!$U$2:$U$122,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A15,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -988,15 +988,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled",'Picks'!$V$2:$V$122,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled",'Picks'!$V$2:$V$139,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1004,11 +1004,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$122,'Picks'!$H$2:$H$122,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$139,'Picks'!$H$2:$H$139,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$122,'Picks'!$H$2:$H$122,$A16,'Picks'!$U$2:$U$122,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$139,'Picks'!$H$2:$H$139,$A16,'Picks'!$U$2:$U$139,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DP122"/>
+  <dimension ref="A1:DP139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2080,11 +2080,11 @@
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
       <c r="AC3" s="30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:02:17.739705Z</t>
+          <t>2026-08-30T21:00:59.237064596Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
@@ -2296,11 +2296,11 @@
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
       <c r="AC4" s="30" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:29:23.578191Z</t>
+          <t>2026-08-30T21:12:34.084264238Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
@@ -2508,11 +2508,11 @@
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:02:17.739705Z</t>
+          <t>2026-08-30T18:53:59.356255520Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
@@ -2720,11 +2720,11 @@
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
       <c r="AC6" s="30" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:02:17.739705Z</t>
+          <t>2026-08-30T20:55:03.737915379Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
@@ -2932,11 +2932,11 @@
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
       <c r="AC7" s="30" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-30T23:59:38.006704226Z</t>
         </is>
       </c>
       <c r="AE7" s="31" t="inlineStr">
@@ -3144,11 +3144,11 @@
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
       <c r="AC8" s="30" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:30:23.932460Z</t>
+          <t>2026-08-30T21:44:48.583035980Z</t>
         </is>
       </c>
       <c r="AE8" s="31" t="inlineStr">
@@ -3356,11 +3356,11 @@
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
       <c r="AC9" s="30" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T18:13:23.815760Z</t>
+          <t>2026-08-30T17:03:18.404033999Z</t>
         </is>
       </c>
       <c r="AE9" s="31" t="inlineStr">
@@ -3568,11 +3568,11 @@
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
       <c r="AC10" s="30" t="n">
-        <v>-1.34</v>
+        <v>-1.36</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:02:17.739705Z</t>
+          <t>2026-08-30T21:08:57.550864338Z</t>
         </is>
       </c>
       <c r="AE10" s="31" t="inlineStr">
@@ -3780,11 +3780,11 @@
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
       <c r="AC11" s="30" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:02:17.739705Z</t>
+          <t>2026-08-30T21:07:47.852390448Z</t>
         </is>
       </c>
       <c r="AE11" s="31" t="inlineStr">
@@ -3992,11 +3992,11 @@
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
       <c r="AC12" s="30" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-30T22:23:48.254732909Z</t>
         </is>
       </c>
       <c r="AE12" s="31" t="inlineStr">
@@ -4204,11 +4204,11 @@
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
       <c r="AC13" s="30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-30T23:00:18.347523723Z</t>
         </is>
       </c>
       <c r="AE13" s="31" t="inlineStr">
@@ -4418,11 +4418,11 @@
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
       <c r="AC14" s="30" t="n">
-        <v>-1.14</v>
+        <v>-1.16</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-30T21:29:23.578191Z</t>
+          <t>2026-08-30T21:06:03.341016599Z</t>
         </is>
       </c>
       <c r="AE14" s="31" t="inlineStr">
@@ -4634,11 +4634,11 @@
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
       <c r="AC15" s="30" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-30T23:02:59.181343795Z</t>
         </is>
       </c>
       <c r="AE15" s="31" t="inlineStr">
@@ -4846,11 +4846,11 @@
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
       <c r="AC16" s="30" t="n">
-        <v>-1.02</v>
+        <v>-1.04</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-30T23:06:15.866769516Z</t>
         </is>
       </c>
       <c r="AE16" s="31" t="inlineStr">
@@ -5058,11 +5058,11 @@
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
       <c r="AC17" s="30" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:41:38.707356Z</t>
+          <t>2026-08-31T18:27:28.086989559Z</t>
         </is>
       </c>
       <c r="AE17" s="31" t="inlineStr">
@@ -5272,11 +5272,11 @@
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
       <c r="AC18" s="30" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:47:49.455874Z</t>
+          <t>2026-08-31T00:52:49.510904509Z</t>
         </is>
       </c>
       <c r="AE18" s="31" t="inlineStr">
@@ -5484,11 +5484,11 @@
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
       <c r="AC19" s="30" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T01:59:03.295568Z</t>
+          <t>2026-08-31T03:58:48.536124373Z</t>
         </is>
       </c>
       <c r="AE19" s="31" t="inlineStr">
@@ -5694,11 +5694,11 @@
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
       <c r="AC20" s="30" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:02:25.134027Z</t>
+          <t>2026-08-31T11:00:03.697515228Z</t>
         </is>
       </c>
       <c r="AE20" s="31" t="inlineStr">
@@ -5904,11 +5904,11 @@
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
       <c r="AC21" s="30" t="n">
-        <v>-0.92</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:02:34.026411Z</t>
+          <t>2026-08-30T20:24:20.395157730Z</t>
         </is>
       </c>
       <c r="AE21" s="31" t="inlineStr">
@@ -6114,11 +6114,11 @@
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
       <c r="AC22" s="30" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:01:24.010499Z</t>
+          <t>2026-08-30T21:22:08.748834907Z</t>
         </is>
       </c>
       <c r="AE22" s="31" t="inlineStr">
@@ -6324,11 +6324,11 @@
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
       <c r="AC23" s="30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:01:24.010499Z</t>
+          <t>2026-08-30T23:52:48.541092830Z</t>
         </is>
       </c>
       <c r="AE23" s="31" t="inlineStr">
@@ -6744,11 +6744,11 @@
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
       <c r="AC25" s="30" t="n">
-        <v>-0.92</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T04:01:24.010499Z</t>
+          <t>2026-08-30T21:32:25.656048661Z</t>
         </is>
       </c>
       <c r="AE25" s="31" t="inlineStr">
@@ -7172,11 +7172,11 @@
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
       <c r="AC27" s="30" t="n">
-        <v>-0.78</v>
+        <v>-0.8</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:41:38.707356Z</t>
+          <t>2026-08-31T16:58:29.020261016Z</t>
         </is>
       </c>
       <c r="AE27" s="31" t="inlineStr">
@@ -7384,11 +7384,11 @@
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
       <c r="AC28" s="30" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:58:20.483072Z</t>
+          <t>2026-08-31T19:09:23.048313655Z</t>
         </is>
       </c>
       <c r="AE28" s="31" t="inlineStr">
@@ -7596,11 +7596,11 @@
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
       <c r="AC29" s="30" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T18:41:38.707356Z</t>
+          <t>2026-08-31T17:16:03.313048988Z</t>
         </is>
       </c>
       <c r="AE29" s="31" t="inlineStr">
@@ -7808,11 +7808,11 @@
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
       <c r="AC30" s="30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T20:52:02.503057Z</t>
+          <t>2026-08-31T20:53:58.036522501Z</t>
         </is>
       </c>
       <c r="AE30" s="31" t="inlineStr">
@@ -8020,11 +8020,11 @@
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
       <c r="AC31" s="30" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:58:20.483072Z</t>
+          <t>2026-08-31T20:11:28.041703979Z</t>
         </is>
       </c>
       <c r="AE31" s="31" t="inlineStr">
@@ -8232,11 +8232,11 @@
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
       <c r="AC32" s="30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T01:06:31.555224Z</t>
+          <t>2026-08-31T22:44:38.648681532Z</t>
         </is>
       </c>
       <c r="AE32" s="31" t="inlineStr">
@@ -8444,11 +8444,11 @@
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
       <c r="AC33" s="30" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T19:58:20.483072Z</t>
+          <t>2026-08-31T19:52:23.076721877Z</t>
         </is>
       </c>
       <c r="AE33" s="31" t="inlineStr">
@@ -8656,11 +8656,11 @@
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
       <c r="AC34" s="30" t="n">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="AD34" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T01:06:31.555224Z</t>
+          <t>2026-08-31T22:45:58.023703924Z</t>
         </is>
       </c>
       <c r="AE34" s="31" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="V35" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W35" s="26" t="n"/>
@@ -8866,11 +8866,11 @@
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
       <c r="AC35" s="30" t="n">
-        <v>1.06</v>
+        <v>-0.96</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:02:25.134027Z</t>
+          <t>2026-08-31T09:37:32.992024705Z</t>
         </is>
       </c>
       <c r="AE35" s="31" t="inlineStr">
@@ -9286,11 +9286,11 @@
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
       <c r="AC37" s="30" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AD37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:02:25.134027Z</t>
+          <t>2026-08-31T15:00:58.786217103Z</t>
         </is>
       </c>
       <c r="AE37" s="31" t="inlineStr">
@@ -9496,11 +9496,11 @@
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
       <c r="AC38" s="30" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AD38" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T16:15:43.108683054Z</t>
         </is>
       </c>
       <c r="AE38" s="31" t="inlineStr">
@@ -9706,11 +9706,11 @@
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
       <c r="AC39" s="30" t="n">
-        <v>-1.1</v>
+        <v>-1.12</v>
       </c>
       <c r="AD39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T16:02:25.134027Z</t>
+          <t>2026-08-31T15:37:57.988972966Z</t>
         </is>
       </c>
       <c r="AE39" s="31" t="inlineStr">
@@ -9916,11 +9916,11 @@
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
       <c r="AC40" s="30" t="n">
-        <v>-1.1</v>
+        <v>-1.12</v>
       </c>
       <c r="AD40" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T17:59:23.147516089Z</t>
         </is>
       </c>
       <c r="AE40" s="31" t="inlineStr">
@@ -10126,11 +10126,11 @@
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
       <c r="AC41" s="30" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="AD41" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T20:24:53.926365895Z</t>
         </is>
       </c>
       <c r="AE41" s="31" t="inlineStr">
@@ -10336,11 +10336,11 @@
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
       <c r="AC42" s="30" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AD42" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T20:20:34.042912899Z</t>
         </is>
       </c>
       <c r="AE42" s="31" t="inlineStr">
@@ -10764,11 +10764,11 @@
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
       <c r="AC44" s="30" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="AD44" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T02:26:20.477542Z</t>
+          <t>2026-09-01T02:10:43.568442228Z</t>
         </is>
       </c>
       <c r="AE44" s="31" t="inlineStr">
@@ -11186,11 +11186,11 @@
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
       <c r="AC46" s="30" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-31T21:15:44.676592Z</t>
+          <t>2026-08-31T21:17:23.007193367Z</t>
         </is>
       </c>
       <c r="AE46" s="31" t="inlineStr">
@@ -11396,11 +11396,11 @@
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
       <c r="AC47" s="30" t="n">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
       <c r="AD47" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T20:27:58.618077525Z</t>
         </is>
       </c>
       <c r="AE47" s="31" t="inlineStr">
@@ -11606,11 +11606,11 @@
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
       <c r="AC48" s="30" t="n">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
       <c r="AD48" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T03:08:18.589524Z</t>
+          <t>2026-08-31T23:34:08.396620140Z</t>
         </is>
       </c>
       <c r="AE48" s="31" t="inlineStr">
@@ -11822,11 +11822,11 @@
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
       <c r="AC49" s="30" t="n">
-        <v>-0.9</v>
+        <v>-0.92</v>
       </c>
       <c r="AD49" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T01:06:31.555224Z</t>
+          <t>2026-09-01T00:32:49.129618616Z</t>
         </is>
       </c>
       <c r="AE49" s="31" t="inlineStr">
@@ -12038,11 +12038,11 @@
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
       <c r="AC50" s="30" t="n">
-        <v>-1</v>
+        <v>-1.03</v>
       </c>
       <c r="AD50" s="24" t="inlineStr">
         <is>
-          <t>2026-09-01T02:26:20.477542Z</t>
+          <t>2026-09-01T02:25:14.474989956Z</t>
         </is>
       </c>
       <c r="AE50" s="31" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="R76" s="26" t="n"/>
       <c r="S76" s="29" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T76" s="24" t="inlineStr">
         <is>
@@ -17489,12 +17489,12 @@
       </c>
       <c r="U76" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V76" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>push</t>
         </is>
       </c>
       <c r="W76" s="26" t="n"/>
@@ -17506,7 +17506,11 @@
       <c r="AC76" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AD76" s="24" t="n"/>
+      <c r="AD76" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996535+00:00</t>
+        </is>
+      </c>
       <c r="AE76" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C83KK4ZN6M9F on aec-cs2-ntr-gl-2026-09-02 (long)</t>
@@ -20005,12 +20009,12 @@
       </c>
       <c r="U88" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V88" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>push</t>
         </is>
       </c>
       <c r="W88" s="26" t="n"/>
@@ -20022,7 +20026,11 @@
       <c r="AC88" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AD88" s="24" t="n"/>
+      <c r="AD88" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996557+00:00</t>
+        </is>
+      </c>
       <c r="AE88" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C84KN9MBEMAC on aec-cs2-sparta-jpu-2026-09-02 (long)</t>
@@ -20832,7 +20840,7 @@
       </c>
       <c r="R92" s="26" t="n"/>
       <c r="S92" s="29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T92" s="24" t="inlineStr">
         <is>
@@ -20841,12 +20849,12 @@
       </c>
       <c r="U92" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V92" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>push</t>
         </is>
       </c>
       <c r="W92" s="26" t="n"/>
@@ -20858,7 +20866,11 @@
       <c r="AC92" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AD92" s="24" t="n"/>
+      <c r="AD92" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996569+00:00</t>
+        </is>
+      </c>
       <c r="AE92" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C84N4FF4GMCS on aec-cs2-hotu-ntr-2026-09-02 (short)</t>
@@ -22097,12 +22109,12 @@
       </c>
       <c r="U98" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V98" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W98" s="26" t="n"/>
@@ -22112,9 +22124,13 @@
       <c r="AA98" s="28" t="n"/>
       <c r="AB98" s="28" t="n"/>
       <c r="AC98" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD98" s="24" t="n"/>
+        <v>0.97</v>
+      </c>
+      <c r="AD98" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:21:35.150063Z</t>
+        </is>
+      </c>
       <c r="AE98" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8EQVPVMMMVK on aec-cs2-navij-sdf-2026-09-02 (long)</t>
@@ -23349,12 +23365,12 @@
       </c>
       <c r="U104" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V104" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W104" s="26" t="n"/>
@@ -23364,9 +23380,13 @@
       <c r="AA104" s="28" t="n"/>
       <c r="AB104" s="28" t="n"/>
       <c r="AC104" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" s="24" t="n"/>
+        <v>0.23</v>
+      </c>
+      <c r="AD104" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:21:35.150063Z</t>
+        </is>
+      </c>
       <c r="AE104" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SAC97KPMW0 on aec-wta-jesman-eleryb-2026-09-02 (short)</t>
@@ -23555,12 +23575,12 @@
       </c>
       <c r="U105" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V105" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W105" s="26" t="n"/>
@@ -23570,9 +23590,13 @@
       <c r="AA105" s="28" t="n"/>
       <c r="AB105" s="28" t="n"/>
       <c r="AC105" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="24" t="n"/>
+        <v>-1.02</v>
+      </c>
+      <c r="AD105" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE105" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8S9JGNDPMVY on aec-atp-felaug-karkha-2026-09-02 (long)</t>
@@ -23761,24 +23785,30 @@
       </c>
       <c r="U106" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V106" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W106" s="26" t="n"/>
-      <c r="X106" s="26" t="n"/>
+      <c r="X106" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y106" s="25" t="n"/>
       <c r="Z106" s="26" t="n"/>
       <c r="AA106" s="28" t="n"/>
       <c r="AB106" s="28" t="n"/>
       <c r="AC106" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" s="24" t="n"/>
+        <v>0.73</v>
+      </c>
+      <c r="AD106" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T19:10:41.048939747Z</t>
+        </is>
+      </c>
       <c r="AE106" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SAJ717GMVR on aec-atp-lucdar-dalsvr-2026-09-02 (long)</t>
@@ -23967,24 +23997,30 @@
       </c>
       <c r="U107" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V107" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="W107" s="26" t="n"/>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W107" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="X107" s="26" t="n"/>
       <c r="Y107" s="25" t="n"/>
       <c r="Z107" s="26" t="n"/>
       <c r="AA107" s="28" t="n"/>
       <c r="AB107" s="28" t="n"/>
       <c r="AC107" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" s="24" t="n"/>
+        <v>0.92</v>
+      </c>
+      <c r="AD107" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T19:37:56.025811831Z</t>
+        </is>
+      </c>
       <c r="AE107" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SA9KYNEMVF on aec-atp-janstr-fracer-2026-09-02 (short)</t>
@@ -24164,7 +24200,7 @@
       </c>
       <c r="R108" s="26" t="n"/>
       <c r="S108" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T108" s="24" t="inlineStr">
         <is>
@@ -24173,16 +24209,18 @@
       </c>
       <c r="U108" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V108" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>void</t>
         </is>
       </c>
       <c r="W108" s="26" t="n"/>
-      <c r="X108" s="26" t="n"/>
+      <c r="X108" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y108" s="25" t="n"/>
       <c r="Z108" s="26" t="n"/>
       <c r="AA108" s="28" t="n"/>
@@ -24190,7 +24228,11 @@
       <c r="AC108" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AD108" s="24" t="n"/>
+      <c r="AD108" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:56:21.677022+00:00</t>
+        </is>
+      </c>
       <c r="AE108" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8S9RQ5K2MVZ on aec-atp-benbon-ignbus-2026-09-03 (long)</t>
@@ -24379,12 +24421,12 @@
       </c>
       <c r="U109" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V109" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W109" s="26" t="n"/>
@@ -24394,9 +24436,13 @@
       <c r="AA109" s="28" t="n"/>
       <c r="AB109" s="28" t="n"/>
       <c r="AC109" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD109" s="24" t="n"/>
+        <v>-1.55</v>
+      </c>
+      <c r="AD109" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE109" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SA9KZAEMVF on aec-lol-doc-bce-2026-09-03 (short)</t>
@@ -24585,12 +24631,12 @@
       </c>
       <c r="U110" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V110" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W110" s="26" t="n"/>
@@ -24600,9 +24646,13 @@
       <c r="AA110" s="28" t="n"/>
       <c r="AB110" s="28" t="n"/>
       <c r="AC110" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD110" s="24" t="n"/>
+        <v>2.06</v>
+      </c>
+      <c r="AD110" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE110" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SAKWMYRMVG on aec-lol-pcific-su-2026-09-03 (long)</t>
@@ -24791,12 +24841,12 @@
       </c>
       <c r="U111" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V111" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W111" s="26" t="n"/>
@@ -24806,9 +24856,13 @@
       <c r="AA111" s="28" t="n"/>
       <c r="AB111" s="28" t="n"/>
       <c r="AC111" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" s="24" t="n"/>
+        <v>1.32</v>
+      </c>
+      <c r="AD111" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE111" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SADETDWMVK on aec-lol-sec-myth-2026-09-03 (long)</t>
@@ -24988,7 +25042,7 @@
       </c>
       <c r="R112" s="26" t="n"/>
       <c r="S112" s="29" t="n">
-        <v>1.25</v>
+        <v>0.09</v>
       </c>
       <c r="T112" s="24" t="inlineStr">
         <is>
@@ -24997,12 +25051,12 @@
       </c>
       <c r="U112" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V112" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W112" s="26" t="n"/>
@@ -25012,9 +25066,13 @@
       <c r="AA112" s="28" t="n"/>
       <c r="AB112" s="28" t="n"/>
       <c r="AC112" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" s="24" t="n"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AD112" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T19:00:05.981241216Z</t>
+        </is>
+      </c>
       <c r="AE112" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SAMAA24MVP on aec-lol-lds-dv1-2026-09-03 (long)</t>
@@ -25203,12 +25261,12 @@
       </c>
       <c r="U113" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V113" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W113" s="26" t="n"/>
@@ -25218,9 +25276,13 @@
       <c r="AA113" s="28" t="n"/>
       <c r="AB113" s="28" t="n"/>
       <c r="AC113" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" s="24" t="n"/>
+        <v>1.75</v>
+      </c>
+      <c r="AD113" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:21:35.150063Z</t>
+        </is>
+      </c>
       <c r="AE113" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SAC9AMPMW0 on aec-lol-domi-drm-2026-09-03 (long)</t>
@@ -25610,7 +25672,7 @@
       </c>
       <c r="R115" s="26" t="n"/>
       <c r="S115" s="29" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="T115" s="24" t="inlineStr">
         <is>
@@ -25619,12 +25681,12 @@
       </c>
       <c r="U115" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V115" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W115" s="26" t="n"/>
@@ -25634,9 +25696,13 @@
       <c r="AA115" s="28" t="n"/>
       <c r="AB115" s="28" t="n"/>
       <c r="AC115" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" s="24" t="n"/>
+        <v>0.76</v>
+      </c>
+      <c r="AD115" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T06:27:21.111521Z</t>
+        </is>
+      </c>
       <c r="AE115" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8S9GE15EMVV on aec-cs2-vexar-bge-2026-09-03 (long)</t>
@@ -26035,12 +26101,12 @@
       </c>
       <c r="U117" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V117" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W117" s="26" t="n"/>
@@ -26050,9 +26116,13 @@
       <c r="AA117" s="28" t="n"/>
       <c r="AB117" s="28" t="n"/>
       <c r="AC117" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" s="24" t="n"/>
+        <v>1.65</v>
+      </c>
+      <c r="AD117" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE117" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8S9JDN66MW1 on aec-cs2-for-biga-2026-09-03 (short)</t>
@@ -27081,12 +27151,12 @@
       </c>
       <c r="U122" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="V122" s="24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W122" s="26" t="n"/>
@@ -27096,9 +27166,13 @@
       <c r="AA122" s="28" t="n"/>
       <c r="AB122" s="28" t="n"/>
       <c r="AC122" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="24" t="n"/>
+        <v>1.97</v>
+      </c>
+      <c r="AD122" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:46:54.513627Z</t>
+        </is>
+      </c>
       <c r="AE122" s="31" t="inlineStr">
         <is>
           <t>Auto-Buyer order C8SADEYG6MVK on aec-cs2-ntr-ef-2026-09-03 (long)</t>
@@ -27208,6 +27282,3504 @@
       <c r="DO122" s="24" t="n"/>
       <c r="DP122" s="24" t="n"/>
     </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="24" t="inlineStr">
+        <is>
+          <t>64564d7fda6d4e87</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:26:18.232551Z</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T11:30:00Z</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-hotu-ef-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="G123" s="24" t="inlineStr">
+        <is>
+          <t>HOTU</t>
+        </is>
+      </c>
+      <c r="H123" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I123" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J123" s="25" t="n"/>
+      <c r="K123" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L123" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M123" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" s="28" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="O123" s="28" t="n">
+        <v>0.6056</v>
+      </c>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="28" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="R123" s="26" t="n"/>
+      <c r="S123" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U123" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V123" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W123" s="26" t="n"/>
+      <c r="X123" s="26" t="n"/>
+      <c r="Y123" s="25" t="n"/>
+      <c r="Z123" s="26" t="n"/>
+      <c r="AA123" s="28" t="n"/>
+      <c r="AB123" s="28" t="n"/>
+      <c r="AC123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" s="24" t="n"/>
+      <c r="AE123" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DRPGMDGMW1 on aec-cs2-hotu-ef-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF123" s="31" t="n"/>
+      <c r="AG123" s="24" t="n"/>
+      <c r="AH123" s="24" t="n"/>
+      <c r="AI123" s="31" t="n"/>
+      <c r="AJ123" s="31" t="n"/>
+      <c r="AK123" s="24" t="n"/>
+      <c r="AL123" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM123" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN123" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO123" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP123" s="24" t="n"/>
+      <c r="AQ123" s="24" t="n"/>
+      <c r="AR123" s="24" t="n"/>
+      <c r="AS123" s="24" t="n"/>
+      <c r="AT123" s="24" t="n"/>
+      <c r="AU123" s="24" t="n"/>
+      <c r="AV123" s="24" t="n"/>
+      <c r="AW123" s="24" t="n"/>
+      <c r="AX123" s="24" t="n"/>
+      <c r="AY123" s="24" t="n"/>
+      <c r="AZ123" s="24" t="n"/>
+      <c r="BA123" s="24" t="n"/>
+      <c r="BB123" s="24" t="n"/>
+      <c r="BC123" s="24" t="n"/>
+      <c r="BD123" s="24" t="n"/>
+      <c r="BE123" s="24" t="n"/>
+      <c r="BF123" s="24" t="n"/>
+      <c r="BG123" s="24" t="n"/>
+      <c r="BH123" s="24" t="n"/>
+      <c r="BI123" s="24" t="n"/>
+      <c r="BJ123" s="25" t="n"/>
+      <c r="BK123" s="26" t="n"/>
+      <c r="BL123" s="27" t="n"/>
+      <c r="BM123" s="28" t="n"/>
+      <c r="BN123" s="28" t="n"/>
+      <c r="BO123" s="28" t="n"/>
+      <c r="BP123" s="25" t="n"/>
+      <c r="BQ123" s="27" t="n"/>
+      <c r="BR123" s="28" t="n"/>
+      <c r="BS123" s="28" t="n"/>
+      <c r="BT123" s="28" t="n"/>
+      <c r="BU123" s="25" t="n"/>
+      <c r="BV123" s="29" t="n"/>
+      <c r="BW123" s="24" t="n"/>
+      <c r="BX123" s="30" t="n"/>
+      <c r="BY123" s="27" t="n"/>
+      <c r="BZ123" s="24" t="n"/>
+      <c r="CA123" s="31" t="n"/>
+      <c r="CB123" s="24" t="n"/>
+      <c r="CC123" s="24" t="n"/>
+      <c r="CD123" s="24" t="n"/>
+      <c r="CE123" s="24" t="n"/>
+      <c r="CF123" s="24" t="n"/>
+      <c r="CG123" s="24" t="n"/>
+      <c r="CH123" s="24" t="n"/>
+      <c r="CI123" s="24" t="n"/>
+      <c r="CJ123" s="24" t="n"/>
+      <c r="CK123" s="24" t="n"/>
+      <c r="CL123" s="24" t="n"/>
+      <c r="CM123" s="24" t="n"/>
+      <c r="CN123" s="24" t="n"/>
+      <c r="CO123" s="24" t="n"/>
+      <c r="CP123" s="24" t="n"/>
+      <c r="CQ123" s="24" t="n"/>
+      <c r="CR123" s="24" t="n"/>
+      <c r="CS123" s="24" t="n"/>
+      <c r="CT123" s="24" t="n"/>
+      <c r="CU123" s="24" t="n"/>
+      <c r="CV123" s="24" t="n"/>
+      <c r="CW123" s="24" t="n"/>
+      <c r="CX123" s="24" t="n"/>
+      <c r="CY123" s="24" t="n"/>
+      <c r="CZ123" s="24" t="n"/>
+      <c r="DA123" s="24" t="n"/>
+      <c r="DB123" s="24" t="n"/>
+      <c r="DC123" s="24" t="n"/>
+      <c r="DD123" s="24" t="n"/>
+      <c r="DE123" s="24" t="n"/>
+      <c r="DF123" s="24" t="n"/>
+      <c r="DG123" s="24" t="n"/>
+      <c r="DH123" s="24" t="n"/>
+      <c r="DI123" s="24" t="n"/>
+      <c r="DJ123" s="24" t="n"/>
+      <c r="DK123" s="24" t="n"/>
+      <c r="DL123" s="24" t="n"/>
+      <c r="DM123" s="24" t="n"/>
+      <c r="DN123" s="24" t="n"/>
+      <c r="DO123" s="24" t="n"/>
+      <c r="DP123" s="24" t="n"/>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="A124" s="24" t="inlineStr">
+        <is>
+          <t>46391c8767ba45aa</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:26:18.232551Z</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D124" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-uno-alka-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="G124" s="24" t="inlineStr">
+        <is>
+          <t>UNO MILLE</t>
+        </is>
+      </c>
+      <c r="H124" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I124" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J124" s="25" t="n"/>
+      <c r="K124" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L124" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M124" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N124" s="28" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="O124" s="28" t="n">
+        <v>0.6655</v>
+      </c>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="28" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="R124" s="26" t="n"/>
+      <c r="S124" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T124" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U124" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V124" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W124" s="26" t="n"/>
+      <c r="X124" s="26" t="n"/>
+      <c r="Y124" s="25" t="n"/>
+      <c r="Z124" s="26" t="n"/>
+      <c r="AA124" s="28" t="n"/>
+      <c r="AB124" s="28" t="n"/>
+      <c r="AC124" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" s="24" t="n"/>
+      <c r="AE124" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DSQW05EMVK on aec-cs2-uno-alka-2026-09-04 (short)</t>
+        </is>
+      </c>
+      <c r="AF124" s="31" t="n"/>
+      <c r="AG124" s="24" t="n"/>
+      <c r="AH124" s="24" t="n"/>
+      <c r="AI124" s="31" t="n"/>
+      <c r="AJ124" s="31" t="n"/>
+      <c r="AK124" s="24" t="n"/>
+      <c r="AL124" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM124" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN124" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO124" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP124" s="24" t="n"/>
+      <c r="AQ124" s="24" t="n"/>
+      <c r="AR124" s="24" t="n"/>
+      <c r="AS124" s="24" t="n"/>
+      <c r="AT124" s="24" t="n"/>
+      <c r="AU124" s="24" t="n"/>
+      <c r="AV124" s="24" t="n"/>
+      <c r="AW124" s="24" t="n"/>
+      <c r="AX124" s="24" t="n"/>
+      <c r="AY124" s="24" t="n"/>
+      <c r="AZ124" s="24" t="n"/>
+      <c r="BA124" s="24" t="n"/>
+      <c r="BB124" s="24" t="n"/>
+      <c r="BC124" s="24" t="n"/>
+      <c r="BD124" s="24" t="n"/>
+      <c r="BE124" s="24" t="n"/>
+      <c r="BF124" s="24" t="n"/>
+      <c r="BG124" s="24" t="n"/>
+      <c r="BH124" s="24" t="n"/>
+      <c r="BI124" s="24" t="n"/>
+      <c r="BJ124" s="25" t="n"/>
+      <c r="BK124" s="26" t="n"/>
+      <c r="BL124" s="27" t="n"/>
+      <c r="BM124" s="28" t="n"/>
+      <c r="BN124" s="28" t="n"/>
+      <c r="BO124" s="28" t="n"/>
+      <c r="BP124" s="25" t="n"/>
+      <c r="BQ124" s="27" t="n"/>
+      <c r="BR124" s="28" t="n"/>
+      <c r="BS124" s="28" t="n"/>
+      <c r="BT124" s="28" t="n"/>
+      <c r="BU124" s="25" t="n"/>
+      <c r="BV124" s="29" t="n"/>
+      <c r="BW124" s="24" t="n"/>
+      <c r="BX124" s="30" t="n"/>
+      <c r="BY124" s="27" t="n"/>
+      <c r="BZ124" s="24" t="n"/>
+      <c r="CA124" s="31" t="n"/>
+      <c r="CB124" s="24" t="n"/>
+      <c r="CC124" s="24" t="n"/>
+      <c r="CD124" s="24" t="n"/>
+      <c r="CE124" s="24" t="n"/>
+      <c r="CF124" s="24" t="n"/>
+      <c r="CG124" s="24" t="n"/>
+      <c r="CH124" s="24" t="n"/>
+      <c r="CI124" s="24" t="n"/>
+      <c r="CJ124" s="24" t="n"/>
+      <c r="CK124" s="24" t="n"/>
+      <c r="CL124" s="24" t="n"/>
+      <c r="CM124" s="24" t="n"/>
+      <c r="CN124" s="24" t="n"/>
+      <c r="CO124" s="24" t="n"/>
+      <c r="CP124" s="24" t="n"/>
+      <c r="CQ124" s="24" t="n"/>
+      <c r="CR124" s="24" t="n"/>
+      <c r="CS124" s="24" t="n"/>
+      <c r="CT124" s="24" t="n"/>
+      <c r="CU124" s="24" t="n"/>
+      <c r="CV124" s="24" t="n"/>
+      <c r="CW124" s="24" t="n"/>
+      <c r="CX124" s="24" t="n"/>
+      <c r="CY124" s="24" t="n"/>
+      <c r="CZ124" s="24" t="n"/>
+      <c r="DA124" s="24" t="n"/>
+      <c r="DB124" s="24" t="n"/>
+      <c r="DC124" s="24" t="n"/>
+      <c r="DD124" s="24" t="n"/>
+      <c r="DE124" s="24" t="n"/>
+      <c r="DF124" s="24" t="n"/>
+      <c r="DG124" s="24" t="n"/>
+      <c r="DH124" s="24" t="n"/>
+      <c r="DI124" s="24" t="n"/>
+      <c r="DJ124" s="24" t="n"/>
+      <c r="DK124" s="24" t="n"/>
+      <c r="DL124" s="24" t="n"/>
+      <c r="DM124" s="24" t="n"/>
+      <c r="DN124" s="24" t="n"/>
+      <c r="DO124" s="24" t="n"/>
+      <c r="DP124" s="24" t="n"/>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="24" t="inlineStr">
+        <is>
+          <t>b4340b03780a4930</t>
+        </is>
+      </c>
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996635+00:00</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D125" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-bbc-wal-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E125" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F125" s="24" t="n"/>
+      <c r="G125" s="24" t="inlineStr">
+        <is>
+          <t>Walczaki</t>
+        </is>
+      </c>
+      <c r="H125" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I125" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J125" s="25" t="n"/>
+      <c r="K125" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L125" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M125" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N125" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O125" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="26" t="n"/>
+      <c r="S125" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T125" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U125" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V125" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W125" s="26" t="n"/>
+      <c r="X125" s="26" t="n"/>
+      <c r="Y125" s="25" t="n"/>
+      <c r="Z125" s="26" t="n"/>
+      <c r="AA125" s="28" t="n"/>
+      <c r="AB125" s="28" t="n"/>
+      <c r="AC125" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" s="24" t="n"/>
+      <c r="AE125" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C93CSEF08MVG on aec-cs2-bbc-wal-2026-09-04 (short)</t>
+        </is>
+      </c>
+      <c r="AF125" s="31" t="n"/>
+      <c r="AG125" s="24" t="n"/>
+      <c r="AH125" s="24" t="n"/>
+      <c r="AI125" s="31" t="n"/>
+      <c r="AJ125" s="31" t="n"/>
+      <c r="AK125" s="24" t="n"/>
+      <c r="AL125" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM125" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN125" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO125" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP125" s="24" t="n"/>
+      <c r="AQ125" s="24" t="n"/>
+      <c r="AR125" s="24" t="n"/>
+      <c r="AS125" s="24" t="n"/>
+      <c r="AT125" s="24" t="n"/>
+      <c r="AU125" s="24" t="n"/>
+      <c r="AV125" s="24" t="n"/>
+      <c r="AW125" s="24" t="n"/>
+      <c r="AX125" s="24" t="n"/>
+      <c r="AY125" s="24" t="n"/>
+      <c r="AZ125" s="24" t="n"/>
+      <c r="BA125" s="24" t="n"/>
+      <c r="BB125" s="24" t="n"/>
+      <c r="BC125" s="24" t="n"/>
+      <c r="BD125" s="24" t="n"/>
+      <c r="BE125" s="24" t="n"/>
+      <c r="BF125" s="24" t="n"/>
+      <c r="BG125" s="24" t="n"/>
+      <c r="BH125" s="24" t="n"/>
+      <c r="BI125" s="24" t="n"/>
+      <c r="BJ125" s="25" t="n"/>
+      <c r="BK125" s="26" t="n"/>
+      <c r="BL125" s="27" t="n"/>
+      <c r="BM125" s="28" t="n"/>
+      <c r="BN125" s="28" t="n"/>
+      <c r="BO125" s="28" t="n"/>
+      <c r="BP125" s="25" t="n"/>
+      <c r="BQ125" s="27" t="n"/>
+      <c r="BR125" s="28" t="n"/>
+      <c r="BS125" s="28" t="n"/>
+      <c r="BT125" s="28" t="n"/>
+      <c r="BU125" s="25" t="n"/>
+      <c r="BV125" s="29" t="n"/>
+      <c r="BW125" s="24" t="n"/>
+      <c r="BX125" s="30" t="n"/>
+      <c r="BY125" s="27" t="n"/>
+      <c r="BZ125" s="24" t="n"/>
+      <c r="CA125" s="31" t="n"/>
+      <c r="CB125" s="24" t="n"/>
+      <c r="CC125" s="24" t="n"/>
+      <c r="CD125" s="24" t="n"/>
+      <c r="CE125" s="24" t="n"/>
+      <c r="CF125" s="24" t="n"/>
+      <c r="CG125" s="24" t="n"/>
+      <c r="CH125" s="24" t="n"/>
+      <c r="CI125" s="24" t="n"/>
+      <c r="CJ125" s="24" t="n"/>
+      <c r="CK125" s="24" t="n"/>
+      <c r="CL125" s="24" t="n"/>
+      <c r="CM125" s="24" t="n"/>
+      <c r="CN125" s="24" t="n"/>
+      <c r="CO125" s="24" t="n"/>
+      <c r="CP125" s="24" t="n"/>
+      <c r="CQ125" s="24" t="n"/>
+      <c r="CR125" s="24" t="n"/>
+      <c r="CS125" s="24" t="n"/>
+      <c r="CT125" s="24" t="n"/>
+      <c r="CU125" s="24" t="n"/>
+      <c r="CV125" s="24" t="n"/>
+      <c r="CW125" s="24" t="n"/>
+      <c r="CX125" s="24" t="n"/>
+      <c r="CY125" s="24" t="n"/>
+      <c r="CZ125" s="24" t="n"/>
+      <c r="DA125" s="24" t="n"/>
+      <c r="DB125" s="24" t="n"/>
+      <c r="DC125" s="24" t="n"/>
+      <c r="DD125" s="24" t="n"/>
+      <c r="DE125" s="24" t="n"/>
+      <c r="DF125" s="24" t="n"/>
+      <c r="DG125" s="24" t="n"/>
+      <c r="DH125" s="24" t="n"/>
+      <c r="DI125" s="24" t="n"/>
+      <c r="DJ125" s="24" t="n"/>
+      <c r="DK125" s="24" t="n"/>
+      <c r="DL125" s="24" t="n"/>
+      <c r="DM125" s="24" t="n"/>
+      <c r="DN125" s="24" t="n"/>
+      <c r="DO125" s="24" t="n"/>
+      <c r="DP125" s="24" t="n"/>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="24" t="inlineStr">
+        <is>
+          <t>f21a2eac0ae3472a</t>
+        </is>
+      </c>
+      <c r="B126" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996652+00:00</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D126" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-inf-ntr-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E126" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F126" s="24" t="n"/>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>Nuclear TigeRES</t>
+        </is>
+      </c>
+      <c r="H126" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I126" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J126" s="25" t="n"/>
+      <c r="K126" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L126" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M126" s="27" t="n">
+        <v>1.4484</v>
+      </c>
+      <c r="N126" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O126" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="26" t="n"/>
+      <c r="S126" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U126" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V126" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W126" s="26" t="n"/>
+      <c r="X126" s="26" t="n"/>
+      <c r="Y126" s="25" t="n"/>
+      <c r="Z126" s="26" t="n"/>
+      <c r="AA126" s="28" t="n"/>
+      <c r="AB126" s="28" t="n"/>
+      <c r="AC126" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="24" t="n"/>
+      <c r="AE126" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C93D5H6T6MVR on aec-cs2-inf-ntr-2026-09-04 (short)</t>
+        </is>
+      </c>
+      <c r="AF126" s="31" t="n"/>
+      <c r="AG126" s="24" t="n"/>
+      <c r="AH126" s="24" t="n"/>
+      <c r="AI126" s="31" t="n"/>
+      <c r="AJ126" s="31" t="n"/>
+      <c r="AK126" s="24" t="n"/>
+      <c r="AL126" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM126" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN126" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO126" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP126" s="24" t="n"/>
+      <c r="AQ126" s="24" t="n"/>
+      <c r="AR126" s="24" t="n"/>
+      <c r="AS126" s="24" t="n"/>
+      <c r="AT126" s="24" t="n"/>
+      <c r="AU126" s="24" t="n"/>
+      <c r="AV126" s="24" t="n"/>
+      <c r="AW126" s="24" t="n"/>
+      <c r="AX126" s="24" t="n"/>
+      <c r="AY126" s="24" t="n"/>
+      <c r="AZ126" s="24" t="n"/>
+      <c r="BA126" s="24" t="n"/>
+      <c r="BB126" s="24" t="n"/>
+      <c r="BC126" s="24" t="n"/>
+      <c r="BD126" s="24" t="n"/>
+      <c r="BE126" s="24" t="n"/>
+      <c r="BF126" s="24" t="n"/>
+      <c r="BG126" s="24" t="n"/>
+      <c r="BH126" s="24" t="n"/>
+      <c r="BI126" s="24" t="n"/>
+      <c r="BJ126" s="25" t="n"/>
+      <c r="BK126" s="26" t="n"/>
+      <c r="BL126" s="27" t="n"/>
+      <c r="BM126" s="28" t="n"/>
+      <c r="BN126" s="28" t="n"/>
+      <c r="BO126" s="28" t="n"/>
+      <c r="BP126" s="25" t="n"/>
+      <c r="BQ126" s="27" t="n"/>
+      <c r="BR126" s="28" t="n"/>
+      <c r="BS126" s="28" t="n"/>
+      <c r="BT126" s="28" t="n"/>
+      <c r="BU126" s="25" t="n"/>
+      <c r="BV126" s="29" t="n"/>
+      <c r="BW126" s="24" t="n"/>
+      <c r="BX126" s="30" t="n"/>
+      <c r="BY126" s="27" t="n"/>
+      <c r="BZ126" s="24" t="n"/>
+      <c r="CA126" s="31" t="n"/>
+      <c r="CB126" s="24" t="n"/>
+      <c r="CC126" s="24" t="n"/>
+      <c r="CD126" s="24" t="n"/>
+      <c r="CE126" s="24" t="n"/>
+      <c r="CF126" s="24" t="n"/>
+      <c r="CG126" s="24" t="n"/>
+      <c r="CH126" s="24" t="n"/>
+      <c r="CI126" s="24" t="n"/>
+      <c r="CJ126" s="24" t="n"/>
+      <c r="CK126" s="24" t="n"/>
+      <c r="CL126" s="24" t="n"/>
+      <c r="CM126" s="24" t="n"/>
+      <c r="CN126" s="24" t="n"/>
+      <c r="CO126" s="24" t="n"/>
+      <c r="CP126" s="24" t="n"/>
+      <c r="CQ126" s="24" t="n"/>
+      <c r="CR126" s="24" t="n"/>
+      <c r="CS126" s="24" t="n"/>
+      <c r="CT126" s="24" t="n"/>
+      <c r="CU126" s="24" t="n"/>
+      <c r="CV126" s="24" t="n"/>
+      <c r="CW126" s="24" t="n"/>
+      <c r="CX126" s="24" t="n"/>
+      <c r="CY126" s="24" t="n"/>
+      <c r="CZ126" s="24" t="n"/>
+      <c r="DA126" s="24" t="n"/>
+      <c r="DB126" s="24" t="n"/>
+      <c r="DC126" s="24" t="n"/>
+      <c r="DD126" s="24" t="n"/>
+      <c r="DE126" s="24" t="n"/>
+      <c r="DF126" s="24" t="n"/>
+      <c r="DG126" s="24" t="n"/>
+      <c r="DH126" s="24" t="n"/>
+      <c r="DI126" s="24" t="n"/>
+      <c r="DJ126" s="24" t="n"/>
+      <c r="DK126" s="24" t="n"/>
+      <c r="DL126" s="24" t="n"/>
+      <c r="DM126" s="24" t="n"/>
+      <c r="DN126" s="24" t="n"/>
+      <c r="DO126" s="24" t="n"/>
+      <c r="DP126" s="24" t="n"/>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="24" t="inlineStr">
+        <is>
+          <t>1ab96547628b445d</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:31:41.996664+00:00</t>
+        </is>
+      </c>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D127" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-isg-pld-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="n"/>
+      <c r="G127" s="24" t="inlineStr">
+        <is>
+          <t>Isurus</t>
+        </is>
+      </c>
+      <c r="H127" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I127" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J127" s="25" t="n"/>
+      <c r="K127" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L127" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M127" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N127" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O127" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P127" s="28" t="n"/>
+      <c r="Q127" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="26" t="n"/>
+      <c r="S127" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T127" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U127" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V127" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W127" s="26" t="n"/>
+      <c r="X127" s="26" t="n"/>
+      <c r="Y127" s="25" t="n"/>
+      <c r="Z127" s="26" t="n"/>
+      <c r="AA127" s="28" t="n"/>
+      <c r="AB127" s="28" t="n"/>
+      <c r="AC127" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" s="24" t="n"/>
+      <c r="AE127" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C93D489P0MVF on aec-cs2-isg-pld-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF127" s="31" t="n"/>
+      <c r="AG127" s="24" t="n"/>
+      <c r="AH127" s="24" t="n"/>
+      <c r="AI127" s="31" t="n"/>
+      <c r="AJ127" s="31" t="n"/>
+      <c r="AK127" s="24" t="n"/>
+      <c r="AL127" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM127" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN127" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO127" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP127" s="24" t="n"/>
+      <c r="AQ127" s="24" t="n"/>
+      <c r="AR127" s="24" t="n"/>
+      <c r="AS127" s="24" t="n"/>
+      <c r="AT127" s="24" t="n"/>
+      <c r="AU127" s="24" t="n"/>
+      <c r="AV127" s="24" t="n"/>
+      <c r="AW127" s="24" t="n"/>
+      <c r="AX127" s="24" t="n"/>
+      <c r="AY127" s="24" t="n"/>
+      <c r="AZ127" s="24" t="n"/>
+      <c r="BA127" s="24" t="n"/>
+      <c r="BB127" s="24" t="n"/>
+      <c r="BC127" s="24" t="n"/>
+      <c r="BD127" s="24" t="n"/>
+      <c r="BE127" s="24" t="n"/>
+      <c r="BF127" s="24" t="n"/>
+      <c r="BG127" s="24" t="n"/>
+      <c r="BH127" s="24" t="n"/>
+      <c r="BI127" s="24" t="n"/>
+      <c r="BJ127" s="25" t="n"/>
+      <c r="BK127" s="26" t="n"/>
+      <c r="BL127" s="27" t="n"/>
+      <c r="BM127" s="28" t="n"/>
+      <c r="BN127" s="28" t="n"/>
+      <c r="BO127" s="28" t="n"/>
+      <c r="BP127" s="25" t="n"/>
+      <c r="BQ127" s="27" t="n"/>
+      <c r="BR127" s="28" t="n"/>
+      <c r="BS127" s="28" t="n"/>
+      <c r="BT127" s="28" t="n"/>
+      <c r="BU127" s="25" t="n"/>
+      <c r="BV127" s="29" t="n"/>
+      <c r="BW127" s="24" t="n"/>
+      <c r="BX127" s="30" t="n"/>
+      <c r="BY127" s="27" t="n"/>
+      <c r="BZ127" s="24" t="n"/>
+      <c r="CA127" s="31" t="n"/>
+      <c r="CB127" s="24" t="n"/>
+      <c r="CC127" s="24" t="n"/>
+      <c r="CD127" s="24" t="n"/>
+      <c r="CE127" s="24" t="n"/>
+      <c r="CF127" s="24" t="n"/>
+      <c r="CG127" s="24" t="n"/>
+      <c r="CH127" s="24" t="n"/>
+      <c r="CI127" s="24" t="n"/>
+      <c r="CJ127" s="24" t="n"/>
+      <c r="CK127" s="24" t="n"/>
+      <c r="CL127" s="24" t="n"/>
+      <c r="CM127" s="24" t="n"/>
+      <c r="CN127" s="24" t="n"/>
+      <c r="CO127" s="24" t="n"/>
+      <c r="CP127" s="24" t="n"/>
+      <c r="CQ127" s="24" t="n"/>
+      <c r="CR127" s="24" t="n"/>
+      <c r="CS127" s="24" t="n"/>
+      <c r="CT127" s="24" t="n"/>
+      <c r="CU127" s="24" t="n"/>
+      <c r="CV127" s="24" t="n"/>
+      <c r="CW127" s="24" t="n"/>
+      <c r="CX127" s="24" t="n"/>
+      <c r="CY127" s="24" t="n"/>
+      <c r="CZ127" s="24" t="n"/>
+      <c r="DA127" s="24" t="n"/>
+      <c r="DB127" s="24" t="n"/>
+      <c r="DC127" s="24" t="n"/>
+      <c r="DD127" s="24" t="n"/>
+      <c r="DE127" s="24" t="n"/>
+      <c r="DF127" s="24" t="n"/>
+      <c r="DG127" s="24" t="n"/>
+      <c r="DH127" s="24" t="n"/>
+      <c r="DI127" s="24" t="n"/>
+      <c r="DJ127" s="24" t="n"/>
+      <c r="DK127" s="24" t="n"/>
+      <c r="DL127" s="24" t="n"/>
+      <c r="DM127" s="24" t="n"/>
+      <c r="DN127" s="24" t="n"/>
+      <c r="DO127" s="24" t="n"/>
+      <c r="DP127" s="24" t="n"/>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="24" t="inlineStr">
+        <is>
+          <t>3f591439037e44eb</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:30Z</t>
+        </is>
+      </c>
+      <c r="D128" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-alemic-danagu-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E128" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="G128" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="H128" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I128" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J128" s="25" t="n"/>
+      <c r="K128" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L128" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M128" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N128" s="28" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="O128" s="28" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="P128" s="28" t="n"/>
+      <c r="Q128" s="28" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="R128" s="26" t="n"/>
+      <c r="S128" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T128" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U128" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V128" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W128" s="26" t="n"/>
+      <c r="X128" s="26" t="n"/>
+      <c r="Y128" s="25" t="n"/>
+      <c r="Z128" s="26" t="n"/>
+      <c r="AA128" s="28" t="n"/>
+      <c r="AB128" s="28" t="n"/>
+      <c r="AC128" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" s="24" t="n"/>
+      <c r="AE128" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DZ3TVP4MW1 on aec-atp-alemic-danagu-2026-09-03 (short)</t>
+        </is>
+      </c>
+      <c r="AF128" s="31" t="n"/>
+      <c r="AG128" s="24" t="n"/>
+      <c r="AH128" s="24" t="n"/>
+      <c r="AI128" s="31" t="n"/>
+      <c r="AJ128" s="31" t="n"/>
+      <c r="AK128" s="24" t="n"/>
+      <c r="AL128" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM128" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN128" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO128" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP128" s="24" t="n"/>
+      <c r="AQ128" s="24" t="n"/>
+      <c r="AR128" s="24" t="n"/>
+      <c r="AS128" s="24" t="n"/>
+      <c r="AT128" s="24" t="n"/>
+      <c r="AU128" s="24" t="n"/>
+      <c r="AV128" s="24" t="n"/>
+      <c r="AW128" s="24" t="n"/>
+      <c r="AX128" s="24" t="n"/>
+      <c r="AY128" s="24" t="n"/>
+      <c r="AZ128" s="24" t="n"/>
+      <c r="BA128" s="24" t="n"/>
+      <c r="BB128" s="24" t="n"/>
+      <c r="BC128" s="24" t="n"/>
+      <c r="BD128" s="24" t="n"/>
+      <c r="BE128" s="24" t="n"/>
+      <c r="BF128" s="24" t="n"/>
+      <c r="BG128" s="24" t="n"/>
+      <c r="BH128" s="24" t="n"/>
+      <c r="BI128" s="24" t="n"/>
+      <c r="BJ128" s="25" t="n"/>
+      <c r="BK128" s="26" t="n"/>
+      <c r="BL128" s="27" t="n"/>
+      <c r="BM128" s="28" t="n"/>
+      <c r="BN128" s="28" t="n"/>
+      <c r="BO128" s="28" t="n"/>
+      <c r="BP128" s="25" t="n"/>
+      <c r="BQ128" s="27" t="n"/>
+      <c r="BR128" s="28" t="n"/>
+      <c r="BS128" s="28" t="n"/>
+      <c r="BT128" s="28" t="n"/>
+      <c r="BU128" s="25" t="n"/>
+      <c r="BV128" s="29" t="n"/>
+      <c r="BW128" s="24" t="n"/>
+      <c r="BX128" s="30" t="n"/>
+      <c r="BY128" s="27" t="n"/>
+      <c r="BZ128" s="24" t="n"/>
+      <c r="CA128" s="31" t="n"/>
+      <c r="CB128" s="24" t="n"/>
+      <c r="CC128" s="24" t="n"/>
+      <c r="CD128" s="24" t="n"/>
+      <c r="CE128" s="24" t="n"/>
+      <c r="CF128" s="24" t="n"/>
+      <c r="CG128" s="24" t="n"/>
+      <c r="CH128" s="24" t="n"/>
+      <c r="CI128" s="24" t="n"/>
+      <c r="CJ128" s="24" t="n"/>
+      <c r="CK128" s="24" t="n"/>
+      <c r="CL128" s="24" t="n"/>
+      <c r="CM128" s="24" t="n"/>
+      <c r="CN128" s="24" t="n"/>
+      <c r="CO128" s="24" t="n"/>
+      <c r="CP128" s="24" t="n"/>
+      <c r="CQ128" s="24" t="n"/>
+      <c r="CR128" s="24" t="n"/>
+      <c r="CS128" s="24" t="n"/>
+      <c r="CT128" s="24" t="n"/>
+      <c r="CU128" s="24" t="n"/>
+      <c r="CV128" s="24" t="n"/>
+      <c r="CW128" s="24" t="n"/>
+      <c r="CX128" s="24" t="n"/>
+      <c r="CY128" s="24" t="n"/>
+      <c r="CZ128" s="24" t="n"/>
+      <c r="DA128" s="24" t="n"/>
+      <c r="DB128" s="24" t="n"/>
+      <c r="DC128" s="24" t="n"/>
+      <c r="DD128" s="24" t="n"/>
+      <c r="DE128" s="24" t="n"/>
+      <c r="DF128" s="24" t="n"/>
+      <c r="DG128" s="24" t="n"/>
+      <c r="DH128" s="24" t="n"/>
+      <c r="DI128" s="24" t="n"/>
+      <c r="DJ128" s="24" t="n"/>
+      <c r="DK128" s="24" t="n"/>
+      <c r="DL128" s="24" t="n"/>
+      <c r="DM128" s="24" t="n"/>
+      <c r="DN128" s="24" t="n"/>
+      <c r="DO128" s="24" t="n"/>
+      <c r="DP128" s="24" t="n"/>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="24" t="inlineStr">
+        <is>
+          <t>cea26d7eb68f4fce</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="D129" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-valvac-fratia-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E129" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe</t>
+        </is>
+      </c>
+      <c r="G129" s="24" t="inlineStr">
+        <is>
+          <t>Valentin Vacherot</t>
+        </is>
+      </c>
+      <c r="H129" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I129" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J129" s="25" t="n"/>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M129" s="27" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="N129" s="28" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="O129" s="28" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="P129" s="28" t="n"/>
+      <c r="Q129" s="28" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="R129" s="26" t="n"/>
+      <c r="S129" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U129" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V129" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W129" s="26" t="n"/>
+      <c r="X129" s="26" t="n"/>
+      <c r="Y129" s="25" t="n"/>
+      <c r="Z129" s="26" t="n"/>
+      <c r="AA129" s="28" t="n"/>
+      <c r="AB129" s="28" t="n"/>
+      <c r="AC129" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" s="24" t="n"/>
+      <c r="AE129" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9E02GGBCMVG on aec-atp-valvac-fratia-2026-09-04 (short)</t>
+        </is>
+      </c>
+      <c r="AF129" s="31" t="n"/>
+      <c r="AG129" s="24" t="n"/>
+      <c r="AH129" s="24" t="n"/>
+      <c r="AI129" s="31" t="n"/>
+      <c r="AJ129" s="31" t="n"/>
+      <c r="AK129" s="24" t="n"/>
+      <c r="AL129" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM129" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN129" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO129" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP129" s="24" t="n"/>
+      <c r="AQ129" s="24" t="n"/>
+      <c r="AR129" s="24" t="n"/>
+      <c r="AS129" s="24" t="n"/>
+      <c r="AT129" s="24" t="n"/>
+      <c r="AU129" s="24" t="n"/>
+      <c r="AV129" s="24" t="n"/>
+      <c r="AW129" s="24" t="n"/>
+      <c r="AX129" s="24" t="n"/>
+      <c r="AY129" s="24" t="n"/>
+      <c r="AZ129" s="24" t="n"/>
+      <c r="BA129" s="24" t="n"/>
+      <c r="BB129" s="24" t="n"/>
+      <c r="BC129" s="24" t="n"/>
+      <c r="BD129" s="24" t="n"/>
+      <c r="BE129" s="24" t="n"/>
+      <c r="BF129" s="24" t="n"/>
+      <c r="BG129" s="24" t="n"/>
+      <c r="BH129" s="24" t="n"/>
+      <c r="BI129" s="24" t="n"/>
+      <c r="BJ129" s="25" t="n"/>
+      <c r="BK129" s="26" t="n"/>
+      <c r="BL129" s="27" t="n"/>
+      <c r="BM129" s="28" t="n"/>
+      <c r="BN129" s="28" t="n"/>
+      <c r="BO129" s="28" t="n"/>
+      <c r="BP129" s="25" t="n"/>
+      <c r="BQ129" s="27" t="n"/>
+      <c r="BR129" s="28" t="n"/>
+      <c r="BS129" s="28" t="n"/>
+      <c r="BT129" s="28" t="n"/>
+      <c r="BU129" s="25" t="n"/>
+      <c r="BV129" s="29" t="n"/>
+      <c r="BW129" s="24" t="n"/>
+      <c r="BX129" s="30" t="n"/>
+      <c r="BY129" s="27" t="n"/>
+      <c r="BZ129" s="24" t="n"/>
+      <c r="CA129" s="31" t="n"/>
+      <c r="CB129" s="24" t="n"/>
+      <c r="CC129" s="24" t="n"/>
+      <c r="CD129" s="24" t="n"/>
+      <c r="CE129" s="24" t="n"/>
+      <c r="CF129" s="24" t="n"/>
+      <c r="CG129" s="24" t="n"/>
+      <c r="CH129" s="24" t="n"/>
+      <c r="CI129" s="24" t="n"/>
+      <c r="CJ129" s="24" t="n"/>
+      <c r="CK129" s="24" t="n"/>
+      <c r="CL129" s="24" t="n"/>
+      <c r="CM129" s="24" t="n"/>
+      <c r="CN129" s="24" t="n"/>
+      <c r="CO129" s="24" t="n"/>
+      <c r="CP129" s="24" t="n"/>
+      <c r="CQ129" s="24" t="n"/>
+      <c r="CR129" s="24" t="n"/>
+      <c r="CS129" s="24" t="n"/>
+      <c r="CT129" s="24" t="n"/>
+      <c r="CU129" s="24" t="n"/>
+      <c r="CV129" s="24" t="n"/>
+      <c r="CW129" s="24" t="n"/>
+      <c r="CX129" s="24" t="n"/>
+      <c r="CY129" s="24" t="n"/>
+      <c r="CZ129" s="24" t="n"/>
+      <c r="DA129" s="24" t="n"/>
+      <c r="DB129" s="24" t="n"/>
+      <c r="DC129" s="24" t="n"/>
+      <c r="DD129" s="24" t="n"/>
+      <c r="DE129" s="24" t="n"/>
+      <c r="DF129" s="24" t="n"/>
+      <c r="DG129" s="24" t="n"/>
+      <c r="DH129" s="24" t="n"/>
+      <c r="DI129" s="24" t="n"/>
+      <c r="DJ129" s="24" t="n"/>
+      <c r="DK129" s="24" t="n"/>
+      <c r="DL129" s="24" t="n"/>
+      <c r="DM129" s="24" t="n"/>
+      <c r="DN129" s="24" t="n"/>
+      <c r="DO129" s="24" t="n"/>
+      <c r="DP129" s="24" t="n"/>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="24" t="inlineStr">
+        <is>
+          <t>dfd31228e10a49bc</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D130" s="24" t="inlineStr">
+        <is>
+          <t>aec-lol-doc-lds-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E130" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>Lodis</t>
+        </is>
+      </c>
+      <c r="G130" s="24" t="inlineStr">
+        <is>
+          <t>DOCISK</t>
+        </is>
+      </c>
+      <c r="H130" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I130" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J130" s="25" t="n"/>
+      <c r="K130" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M130" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N130" s="28" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O130" s="28" t="n">
+        <v>0.5829</v>
+      </c>
+      <c r="P130" s="28" t="n"/>
+      <c r="Q130" s="28" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="R130" s="26" t="n"/>
+      <c r="S130" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T130" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U130" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V130" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W130" s="26" t="n"/>
+      <c r="X130" s="26" t="n"/>
+      <c r="Y130" s="25" t="n"/>
+      <c r="Z130" s="26" t="n"/>
+      <c r="AA130" s="28" t="n"/>
+      <c r="AB130" s="28" t="n"/>
+      <c r="AC130" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" s="24" t="n"/>
+      <c r="AE130" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DZ3TX0AMW1 on aec-lol-doc-lds-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF130" s="31" t="n"/>
+      <c r="AG130" s="24" t="n"/>
+      <c r="AH130" s="24" t="n"/>
+      <c r="AI130" s="31" t="n"/>
+      <c r="AJ130" s="31" t="n"/>
+      <c r="AK130" s="24" t="n"/>
+      <c r="AL130" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM130" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN130" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO130" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP130" s="24" t="n"/>
+      <c r="AQ130" s="24" t="n"/>
+      <c r="AR130" s="24" t="n"/>
+      <c r="AS130" s="24" t="n"/>
+      <c r="AT130" s="24" t="n"/>
+      <c r="AU130" s="24" t="n"/>
+      <c r="AV130" s="24" t="n"/>
+      <c r="AW130" s="24" t="n"/>
+      <c r="AX130" s="24" t="n"/>
+      <c r="AY130" s="24" t="n"/>
+      <c r="AZ130" s="24" t="n"/>
+      <c r="BA130" s="24" t="n"/>
+      <c r="BB130" s="24" t="n"/>
+      <c r="BC130" s="24" t="n"/>
+      <c r="BD130" s="24" t="n"/>
+      <c r="BE130" s="24" t="n"/>
+      <c r="BF130" s="24" t="n"/>
+      <c r="BG130" s="24" t="n"/>
+      <c r="BH130" s="24" t="n"/>
+      <c r="BI130" s="24" t="n"/>
+      <c r="BJ130" s="25" t="n"/>
+      <c r="BK130" s="26" t="n"/>
+      <c r="BL130" s="27" t="n"/>
+      <c r="BM130" s="28" t="n"/>
+      <c r="BN130" s="28" t="n"/>
+      <c r="BO130" s="28" t="n"/>
+      <c r="BP130" s="25" t="n"/>
+      <c r="BQ130" s="27" t="n"/>
+      <c r="BR130" s="28" t="n"/>
+      <c r="BS130" s="28" t="n"/>
+      <c r="BT130" s="28" t="n"/>
+      <c r="BU130" s="25" t="n"/>
+      <c r="BV130" s="29" t="n"/>
+      <c r="BW130" s="24" t="n"/>
+      <c r="BX130" s="30" t="n"/>
+      <c r="BY130" s="27" t="n"/>
+      <c r="BZ130" s="24" t="n"/>
+      <c r="CA130" s="31" t="n"/>
+      <c r="CB130" s="24" t="n"/>
+      <c r="CC130" s="24" t="n"/>
+      <c r="CD130" s="24" t="n"/>
+      <c r="CE130" s="24" t="n"/>
+      <c r="CF130" s="24" t="n"/>
+      <c r="CG130" s="24" t="n"/>
+      <c r="CH130" s="24" t="n"/>
+      <c r="CI130" s="24" t="n"/>
+      <c r="CJ130" s="24" t="n"/>
+      <c r="CK130" s="24" t="n"/>
+      <c r="CL130" s="24" t="n"/>
+      <c r="CM130" s="24" t="n"/>
+      <c r="CN130" s="24" t="n"/>
+      <c r="CO130" s="24" t="n"/>
+      <c r="CP130" s="24" t="n"/>
+      <c r="CQ130" s="24" t="n"/>
+      <c r="CR130" s="24" t="n"/>
+      <c r="CS130" s="24" t="n"/>
+      <c r="CT130" s="24" t="n"/>
+      <c r="CU130" s="24" t="n"/>
+      <c r="CV130" s="24" t="n"/>
+      <c r="CW130" s="24" t="n"/>
+      <c r="CX130" s="24" t="n"/>
+      <c r="CY130" s="24" t="n"/>
+      <c r="CZ130" s="24" t="n"/>
+      <c r="DA130" s="24" t="n"/>
+      <c r="DB130" s="24" t="n"/>
+      <c r="DC130" s="24" t="n"/>
+      <c r="DD130" s="24" t="n"/>
+      <c r="DE130" s="24" t="n"/>
+      <c r="DF130" s="24" t="n"/>
+      <c r="DG130" s="24" t="n"/>
+      <c r="DH130" s="24" t="n"/>
+      <c r="DI130" s="24" t="n"/>
+      <c r="DJ130" s="24" t="n"/>
+      <c r="DK130" s="24" t="n"/>
+      <c r="DL130" s="24" t="n"/>
+      <c r="DM130" s="24" t="n"/>
+      <c r="DN130" s="24" t="n"/>
+      <c r="DO130" s="24" t="n"/>
+      <c r="DP130" s="24" t="n"/>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="24" t="inlineStr">
+        <is>
+          <t>dbdda061ddbd4e3a</t>
+        </is>
+      </c>
+      <c r="B131" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D131" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-nemi-bca-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E131" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="inlineStr">
+        <is>
+          <t>Betclic Apogee Esports</t>
+        </is>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga</t>
+        </is>
+      </c>
+      <c r="H131" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I131" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J131" s="25" t="n"/>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M131" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O131" s="28" t="n">
+        <v>0.6262</v>
+      </c>
+      <c r="P131" s="28" t="n"/>
+      <c r="Q131" s="28" t="n">
+        <v>0.1262</v>
+      </c>
+      <c r="R131" s="26" t="n"/>
+      <c r="S131" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T131" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U131" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W131" s="26" t="n"/>
+      <c r="X131" s="26" t="n"/>
+      <c r="Y131" s="25" t="n"/>
+      <c r="Z131" s="26" t="n"/>
+      <c r="AA131" s="28" t="n"/>
+      <c r="AB131" s="28" t="n"/>
+      <c r="AC131" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="24" t="n"/>
+      <c r="AE131" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DZEJJPPMVR on aec-cs2-nemi-bca-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF131" s="31" t="n"/>
+      <c r="AG131" s="24" t="n"/>
+      <c r="AH131" s="24" t="n"/>
+      <c r="AI131" s="31" t="n"/>
+      <c r="AJ131" s="31" t="n"/>
+      <c r="AK131" s="24" t="n"/>
+      <c r="AL131" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM131" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN131" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO131" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP131" s="24" t="n"/>
+      <c r="AQ131" s="24" t="n"/>
+      <c r="AR131" s="24" t="n"/>
+      <c r="AS131" s="24" t="n"/>
+      <c r="AT131" s="24" t="n"/>
+      <c r="AU131" s="24" t="n"/>
+      <c r="AV131" s="24" t="n"/>
+      <c r="AW131" s="24" t="n"/>
+      <c r="AX131" s="24" t="n"/>
+      <c r="AY131" s="24" t="n"/>
+      <c r="AZ131" s="24" t="n"/>
+      <c r="BA131" s="24" t="n"/>
+      <c r="BB131" s="24" t="n"/>
+      <c r="BC131" s="24" t="n"/>
+      <c r="BD131" s="24" t="n"/>
+      <c r="BE131" s="24" t="n"/>
+      <c r="BF131" s="24" t="n"/>
+      <c r="BG131" s="24" t="n"/>
+      <c r="BH131" s="24" t="n"/>
+      <c r="BI131" s="24" t="n"/>
+      <c r="BJ131" s="25" t="n"/>
+      <c r="BK131" s="26" t="n"/>
+      <c r="BL131" s="27" t="n"/>
+      <c r="BM131" s="28" t="n"/>
+      <c r="BN131" s="28" t="n"/>
+      <c r="BO131" s="28" t="n"/>
+      <c r="BP131" s="25" t="n"/>
+      <c r="BQ131" s="27" t="n"/>
+      <c r="BR131" s="28" t="n"/>
+      <c r="BS131" s="28" t="n"/>
+      <c r="BT131" s="28" t="n"/>
+      <c r="BU131" s="25" t="n"/>
+      <c r="BV131" s="29" t="n"/>
+      <c r="BW131" s="24" t="n"/>
+      <c r="BX131" s="30" t="n"/>
+      <c r="BY131" s="27" t="n"/>
+      <c r="BZ131" s="24" t="n"/>
+      <c r="CA131" s="31" t="n"/>
+      <c r="CB131" s="24" t="n"/>
+      <c r="CC131" s="24" t="n"/>
+      <c r="CD131" s="24" t="n"/>
+      <c r="CE131" s="24" t="n"/>
+      <c r="CF131" s="24" t="n"/>
+      <c r="CG131" s="24" t="n"/>
+      <c r="CH131" s="24" t="n"/>
+      <c r="CI131" s="24" t="n"/>
+      <c r="CJ131" s="24" t="n"/>
+      <c r="CK131" s="24" t="n"/>
+      <c r="CL131" s="24" t="n"/>
+      <c r="CM131" s="24" t="n"/>
+      <c r="CN131" s="24" t="n"/>
+      <c r="CO131" s="24" t="n"/>
+      <c r="CP131" s="24" t="n"/>
+      <c r="CQ131" s="24" t="n"/>
+      <c r="CR131" s="24" t="n"/>
+      <c r="CS131" s="24" t="n"/>
+      <c r="CT131" s="24" t="n"/>
+      <c r="CU131" s="24" t="n"/>
+      <c r="CV131" s="24" t="n"/>
+      <c r="CW131" s="24" t="n"/>
+      <c r="CX131" s="24" t="n"/>
+      <c r="CY131" s="24" t="n"/>
+      <c r="CZ131" s="24" t="n"/>
+      <c r="DA131" s="24" t="n"/>
+      <c r="DB131" s="24" t="n"/>
+      <c r="DC131" s="24" t="n"/>
+      <c r="DD131" s="24" t="n"/>
+      <c r="DE131" s="24" t="n"/>
+      <c r="DF131" s="24" t="n"/>
+      <c r="DG131" s="24" t="n"/>
+      <c r="DH131" s="24" t="n"/>
+      <c r="DI131" s="24" t="n"/>
+      <c r="DJ131" s="24" t="n"/>
+      <c r="DK131" s="24" t="n"/>
+      <c r="DL131" s="24" t="n"/>
+      <c r="DM131" s="24" t="n"/>
+      <c r="DN131" s="24" t="n"/>
+      <c r="DO131" s="24" t="n"/>
+      <c r="DP131" s="24" t="n"/>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="24" t="inlineStr">
+        <is>
+          <t>f4aeecd9aa98413d</t>
+        </is>
+      </c>
+      <c r="B132" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D132" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-sin-qua-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E132" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="inlineStr">
+        <is>
+          <t>QUAZAR</t>
+        </is>
+      </c>
+      <c r="G132" s="24" t="inlineStr">
+        <is>
+          <t>Sinners</t>
+        </is>
+      </c>
+      <c r="H132" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I132" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J132" s="25" t="n"/>
+      <c r="K132" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M132" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N132" s="28" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O132" s="28" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="P132" s="28" t="n"/>
+      <c r="Q132" s="28" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="R132" s="26" t="n"/>
+      <c r="S132" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T132" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U132" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V132" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W132" s="26" t="n"/>
+      <c r="X132" s="26" t="n"/>
+      <c r="Y132" s="25" t="n"/>
+      <c r="Z132" s="26" t="n"/>
+      <c r="AA132" s="28" t="n"/>
+      <c r="AB132" s="28" t="n"/>
+      <c r="AC132" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" s="24" t="n"/>
+      <c r="AE132" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DZNP1G6MVV on aec-cs2-sin-qua-2026-09-04 (short)</t>
+        </is>
+      </c>
+      <c r="AF132" s="31" t="n"/>
+      <c r="AG132" s="24" t="n"/>
+      <c r="AH132" s="24" t="n"/>
+      <c r="AI132" s="31" t="n"/>
+      <c r="AJ132" s="31" t="n"/>
+      <c r="AK132" s="24" t="n"/>
+      <c r="AL132" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM132" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN132" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO132" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP132" s="24" t="n"/>
+      <c r="AQ132" s="24" t="n"/>
+      <c r="AR132" s="24" t="n"/>
+      <c r="AS132" s="24" t="n"/>
+      <c r="AT132" s="24" t="n"/>
+      <c r="AU132" s="24" t="n"/>
+      <c r="AV132" s="24" t="n"/>
+      <c r="AW132" s="24" t="n"/>
+      <c r="AX132" s="24" t="n"/>
+      <c r="AY132" s="24" t="n"/>
+      <c r="AZ132" s="24" t="n"/>
+      <c r="BA132" s="24" t="n"/>
+      <c r="BB132" s="24" t="n"/>
+      <c r="BC132" s="24" t="n"/>
+      <c r="BD132" s="24" t="n"/>
+      <c r="BE132" s="24" t="n"/>
+      <c r="BF132" s="24" t="n"/>
+      <c r="BG132" s="24" t="n"/>
+      <c r="BH132" s="24" t="n"/>
+      <c r="BI132" s="24" t="n"/>
+      <c r="BJ132" s="25" t="n"/>
+      <c r="BK132" s="26" t="n"/>
+      <c r="BL132" s="27" t="n"/>
+      <c r="BM132" s="28" t="n"/>
+      <c r="BN132" s="28" t="n"/>
+      <c r="BO132" s="28" t="n"/>
+      <c r="BP132" s="25" t="n"/>
+      <c r="BQ132" s="27" t="n"/>
+      <c r="BR132" s="28" t="n"/>
+      <c r="BS132" s="28" t="n"/>
+      <c r="BT132" s="28" t="n"/>
+      <c r="BU132" s="25" t="n"/>
+      <c r="BV132" s="29" t="n"/>
+      <c r="BW132" s="24" t="n"/>
+      <c r="BX132" s="30" t="n"/>
+      <c r="BY132" s="27" t="n"/>
+      <c r="BZ132" s="24" t="n"/>
+      <c r="CA132" s="31" t="n"/>
+      <c r="CB132" s="24" t="n"/>
+      <c r="CC132" s="24" t="n"/>
+      <c r="CD132" s="24" t="n"/>
+      <c r="CE132" s="24" t="n"/>
+      <c r="CF132" s="24" t="n"/>
+      <c r="CG132" s="24" t="n"/>
+      <c r="CH132" s="24" t="n"/>
+      <c r="CI132" s="24" t="n"/>
+      <c r="CJ132" s="24" t="n"/>
+      <c r="CK132" s="24" t="n"/>
+      <c r="CL132" s="24" t="n"/>
+      <c r="CM132" s="24" t="n"/>
+      <c r="CN132" s="24" t="n"/>
+      <c r="CO132" s="24" t="n"/>
+      <c r="CP132" s="24" t="n"/>
+      <c r="CQ132" s="24" t="n"/>
+      <c r="CR132" s="24" t="n"/>
+      <c r="CS132" s="24" t="n"/>
+      <c r="CT132" s="24" t="n"/>
+      <c r="CU132" s="24" t="n"/>
+      <c r="CV132" s="24" t="n"/>
+      <c r="CW132" s="24" t="n"/>
+      <c r="CX132" s="24" t="n"/>
+      <c r="CY132" s="24" t="n"/>
+      <c r="CZ132" s="24" t="n"/>
+      <c r="DA132" s="24" t="n"/>
+      <c r="DB132" s="24" t="n"/>
+      <c r="DC132" s="24" t="n"/>
+      <c r="DD132" s="24" t="n"/>
+      <c r="DE132" s="24" t="n"/>
+      <c r="DF132" s="24" t="n"/>
+      <c r="DG132" s="24" t="n"/>
+      <c r="DH132" s="24" t="n"/>
+      <c r="DI132" s="24" t="n"/>
+      <c r="DJ132" s="24" t="n"/>
+      <c r="DK132" s="24" t="n"/>
+      <c r="DL132" s="24" t="n"/>
+      <c r="DM132" s="24" t="n"/>
+      <c r="DN132" s="24" t="n"/>
+      <c r="DO132" s="24" t="n"/>
+      <c r="DP132" s="24" t="n"/>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="24" t="inlineStr">
+        <is>
+          <t>73d88d492cd0402f</t>
+        </is>
+      </c>
+      <c r="B133" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:40:57.703355Z</t>
+        </is>
+      </c>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D133" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-mars-war-2026-09-05</t>
+        </is>
+      </c>
+      <c r="E133" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F133" s="24" t="inlineStr">
+        <is>
+          <t>Without a Roof</t>
+        </is>
+      </c>
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>Marsborne</t>
+        </is>
+      </c>
+      <c r="H133" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I133" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J133" s="25" t="n"/>
+      <c r="K133" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M133" s="27" t="n">
+        <v>1.8197</v>
+      </c>
+      <c r="N133" s="28" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="O133" s="28" t="n">
+        <v>0.6298</v>
+      </c>
+      <c r="P133" s="28" t="n"/>
+      <c r="Q133" s="28" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="R133" s="26" t="n"/>
+      <c r="S133" s="29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="T133" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U133" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V133" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W133" s="26" t="n"/>
+      <c r="X133" s="26" t="n"/>
+      <c r="Y133" s="25" t="n"/>
+      <c r="Z133" s="26" t="n"/>
+      <c r="AA133" s="28" t="n"/>
+      <c r="AB133" s="28" t="n"/>
+      <c r="AC133" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" s="24" t="n"/>
+      <c r="AE133" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9DZWAQW4MVK on aec-cs2-mars-war-2026-09-05 (long)</t>
+        </is>
+      </c>
+      <c r="AF133" s="31" t="n"/>
+      <c r="AG133" s="24" t="n"/>
+      <c r="AH133" s="24" t="n"/>
+      <c r="AI133" s="31" t="n"/>
+      <c r="AJ133" s="31" t="n"/>
+      <c r="AK133" s="24" t="n"/>
+      <c r="AL133" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM133" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN133" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO133" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP133" s="24" t="n"/>
+      <c r="AQ133" s="24" t="n"/>
+      <c r="AR133" s="24" t="n"/>
+      <c r="AS133" s="24" t="n"/>
+      <c r="AT133" s="24" t="n"/>
+      <c r="AU133" s="24" t="n"/>
+      <c r="AV133" s="24" t="n"/>
+      <c r="AW133" s="24" t="n"/>
+      <c r="AX133" s="24" t="n"/>
+      <c r="AY133" s="24" t="n"/>
+      <c r="AZ133" s="24" t="n"/>
+      <c r="BA133" s="24" t="n"/>
+      <c r="BB133" s="24" t="n"/>
+      <c r="BC133" s="24" t="n"/>
+      <c r="BD133" s="24" t="n"/>
+      <c r="BE133" s="24" t="n"/>
+      <c r="BF133" s="24" t="n"/>
+      <c r="BG133" s="24" t="n"/>
+      <c r="BH133" s="24" t="n"/>
+      <c r="BI133" s="24" t="n"/>
+      <c r="BJ133" s="25" t="n"/>
+      <c r="BK133" s="26" t="n"/>
+      <c r="BL133" s="27" t="n"/>
+      <c r="BM133" s="28" t="n"/>
+      <c r="BN133" s="28" t="n"/>
+      <c r="BO133" s="28" t="n"/>
+      <c r="BP133" s="25" t="n"/>
+      <c r="BQ133" s="27" t="n"/>
+      <c r="BR133" s="28" t="n"/>
+      <c r="BS133" s="28" t="n"/>
+      <c r="BT133" s="28" t="n"/>
+      <c r="BU133" s="25" t="n"/>
+      <c r="BV133" s="29" t="n"/>
+      <c r="BW133" s="24" t="n"/>
+      <c r="BX133" s="30" t="n"/>
+      <c r="BY133" s="27" t="n"/>
+      <c r="BZ133" s="24" t="n"/>
+      <c r="CA133" s="31" t="n"/>
+      <c r="CB133" s="24" t="n"/>
+      <c r="CC133" s="24" t="n"/>
+      <c r="CD133" s="24" t="n"/>
+      <c r="CE133" s="24" t="n"/>
+      <c r="CF133" s="24" t="n"/>
+      <c r="CG133" s="24" t="n"/>
+      <c r="CH133" s="24" t="n"/>
+      <c r="CI133" s="24" t="n"/>
+      <c r="CJ133" s="24" t="n"/>
+      <c r="CK133" s="24" t="n"/>
+      <c r="CL133" s="24" t="n"/>
+      <c r="CM133" s="24" t="n"/>
+      <c r="CN133" s="24" t="n"/>
+      <c r="CO133" s="24" t="n"/>
+      <c r="CP133" s="24" t="n"/>
+      <c r="CQ133" s="24" t="n"/>
+      <c r="CR133" s="24" t="n"/>
+      <c r="CS133" s="24" t="n"/>
+      <c r="CT133" s="24" t="n"/>
+      <c r="CU133" s="24" t="n"/>
+      <c r="CV133" s="24" t="n"/>
+      <c r="CW133" s="24" t="n"/>
+      <c r="CX133" s="24" t="n"/>
+      <c r="CY133" s="24" t="n"/>
+      <c r="CZ133" s="24" t="n"/>
+      <c r="DA133" s="24" t="n"/>
+      <c r="DB133" s="24" t="n"/>
+      <c r="DC133" s="24" t="n"/>
+      <c r="DD133" s="24" t="n"/>
+      <c r="DE133" s="24" t="n"/>
+      <c r="DF133" s="24" t="n"/>
+      <c r="DG133" s="24" t="n"/>
+      <c r="DH133" s="24" t="n"/>
+      <c r="DI133" s="24" t="n"/>
+      <c r="DJ133" s="24" t="n"/>
+      <c r="DK133" s="24" t="n"/>
+      <c r="DL133" s="24" t="n"/>
+      <c r="DM133" s="24" t="n"/>
+      <c r="DN133" s="24" t="n"/>
+      <c r="DO133" s="24" t="n"/>
+      <c r="DP133" s="24" t="n"/>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="24" t="inlineStr">
+        <is>
+          <t>90fd42882b864418</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T06:11:53.656768Z</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D134" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-jjh-33-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="G134" s="24" t="inlineStr">
+        <is>
+          <t>JiJieHao</t>
+        </is>
+      </c>
+      <c r="H134" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I134" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J134" s="25" t="n"/>
+      <c r="K134" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L134" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M134" s="27" t="n">
+        <v>1.7874</v>
+      </c>
+      <c r="N134" s="28" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="O134" s="28" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="P134" s="28" t="n"/>
+      <c r="Q134" s="28" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="R134" s="26" t="n"/>
+      <c r="S134" s="29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T134" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U134" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V134" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W134" s="26" t="n"/>
+      <c r="X134" s="26" t="n"/>
+      <c r="Y134" s="25" t="n"/>
+      <c r="Z134" s="26" t="n"/>
+      <c r="AA134" s="28" t="n"/>
+      <c r="AB134" s="28" t="n"/>
+      <c r="AC134" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="24" t="n"/>
+      <c r="AE134" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9F8KB5WCMVG on aec-cs2-jjh-33-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF134" s="31" t="n"/>
+      <c r="AG134" s="24" t="n"/>
+      <c r="AH134" s="24" t="n"/>
+      <c r="AI134" s="31" t="n"/>
+      <c r="AJ134" s="31" t="n"/>
+      <c r="AK134" s="24" t="n"/>
+      <c r="AL134" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM134" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN134" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO134" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP134" s="24" t="n"/>
+      <c r="AQ134" s="24" t="n"/>
+      <c r="AR134" s="24" t="n"/>
+      <c r="AS134" s="24" t="n"/>
+      <c r="AT134" s="24" t="n"/>
+      <c r="AU134" s="24" t="n"/>
+      <c r="AV134" s="24" t="n"/>
+      <c r="AW134" s="24" t="n"/>
+      <c r="AX134" s="24" t="n"/>
+      <c r="AY134" s="24" t="n"/>
+      <c r="AZ134" s="24" t="n"/>
+      <c r="BA134" s="24" t="n"/>
+      <c r="BB134" s="24" t="n"/>
+      <c r="BC134" s="24" t="n"/>
+      <c r="BD134" s="24" t="n"/>
+      <c r="BE134" s="24" t="n"/>
+      <c r="BF134" s="24" t="n"/>
+      <c r="BG134" s="24" t="n"/>
+      <c r="BH134" s="24" t="n"/>
+      <c r="BI134" s="24" t="n"/>
+      <c r="BJ134" s="25" t="n"/>
+      <c r="BK134" s="26" t="n"/>
+      <c r="BL134" s="27" t="n"/>
+      <c r="BM134" s="28" t="n"/>
+      <c r="BN134" s="28" t="n"/>
+      <c r="BO134" s="28" t="n"/>
+      <c r="BP134" s="25" t="n"/>
+      <c r="BQ134" s="27" t="n"/>
+      <c r="BR134" s="28" t="n"/>
+      <c r="BS134" s="28" t="n"/>
+      <c r="BT134" s="28" t="n"/>
+      <c r="BU134" s="25" t="n"/>
+      <c r="BV134" s="29" t="n"/>
+      <c r="BW134" s="24" t="n"/>
+      <c r="BX134" s="30" t="n"/>
+      <c r="BY134" s="27" t="n"/>
+      <c r="BZ134" s="24" t="n"/>
+      <c r="CA134" s="31" t="n"/>
+      <c r="CB134" s="24" t="n"/>
+      <c r="CC134" s="24" t="n"/>
+      <c r="CD134" s="24" t="n"/>
+      <c r="CE134" s="24" t="n"/>
+      <c r="CF134" s="24" t="n"/>
+      <c r="CG134" s="24" t="n"/>
+      <c r="CH134" s="24" t="n"/>
+      <c r="CI134" s="24" t="n"/>
+      <c r="CJ134" s="24" t="n"/>
+      <c r="CK134" s="24" t="n"/>
+      <c r="CL134" s="24" t="n"/>
+      <c r="CM134" s="24" t="n"/>
+      <c r="CN134" s="24" t="n"/>
+      <c r="CO134" s="24" t="n"/>
+      <c r="CP134" s="24" t="n"/>
+      <c r="CQ134" s="24" t="n"/>
+      <c r="CR134" s="24" t="n"/>
+      <c r="CS134" s="24" t="n"/>
+      <c r="CT134" s="24" t="n"/>
+      <c r="CU134" s="24" t="n"/>
+      <c r="CV134" s="24" t="n"/>
+      <c r="CW134" s="24" t="n"/>
+      <c r="CX134" s="24" t="n"/>
+      <c r="CY134" s="24" t="n"/>
+      <c r="CZ134" s="24" t="n"/>
+      <c r="DA134" s="24" t="n"/>
+      <c r="DB134" s="24" t="n"/>
+      <c r="DC134" s="24" t="n"/>
+      <c r="DD134" s="24" t="n"/>
+      <c r="DE134" s="24" t="n"/>
+      <c r="DF134" s="24" t="n"/>
+      <c r="DG134" s="24" t="n"/>
+      <c r="DH134" s="24" t="n"/>
+      <c r="DI134" s="24" t="n"/>
+      <c r="DJ134" s="24" t="n"/>
+      <c r="DK134" s="24" t="n"/>
+      <c r="DL134" s="24" t="n"/>
+      <c r="DM134" s="24" t="n"/>
+      <c r="DN134" s="24" t="n"/>
+      <c r="DO134" s="24" t="n"/>
+      <c r="DP134" s="24" t="n"/>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="24" t="inlineStr">
+        <is>
+          <t>7249021be14e4de5</t>
+        </is>
+      </c>
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D135" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-omg-qua-2026-09-03</t>
+        </is>
+      </c>
+      <c r="E135" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F135" s="24" t="inlineStr">
+        <is>
+          <t>QUAZAR</t>
+        </is>
+      </c>
+      <c r="G135" s="24" t="inlineStr">
+        <is>
+          <t>OMG</t>
+        </is>
+      </c>
+      <c r="H135" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I135" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J135" s="25" t="n"/>
+      <c r="K135" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M135" s="27" t="n">
+        <v>1.7874</v>
+      </c>
+      <c r="N135" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O135" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P135" s="28" t="n"/>
+      <c r="Q135" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="26" t="n"/>
+      <c r="S135" s="29" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="T135" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U135" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W135" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X135" s="26" t="n"/>
+      <c r="Y135" s="25" t="n"/>
+      <c r="Z135" s="26" t="n"/>
+      <c r="AA135" s="28" t="n"/>
+      <c r="AB135" s="28" t="n"/>
+      <c r="AC135" s="30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="AE135" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C8VMRB4Y8MVK on aec-cs2-omg-qua-2026-09-03 (short)</t>
+        </is>
+      </c>
+      <c r="AF135" s="31" t="n"/>
+      <c r="AG135" s="24" t="n"/>
+      <c r="AH135" s="24" t="n"/>
+      <c r="AI135" s="31" t="n"/>
+      <c r="AJ135" s="31" t="n"/>
+      <c r="AK135" s="24" t="n"/>
+      <c r="AL135" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM135" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN135" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO135" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP135" s="24" t="n"/>
+      <c r="AQ135" s="24" t="n"/>
+      <c r="AR135" s="24" t="n"/>
+      <c r="AS135" s="24" t="n"/>
+      <c r="AT135" s="24" t="n"/>
+      <c r="AU135" s="24" t="n"/>
+      <c r="AV135" s="24" t="n"/>
+      <c r="AW135" s="24" t="n"/>
+      <c r="AX135" s="24" t="n"/>
+      <c r="AY135" s="24" t="n"/>
+      <c r="AZ135" s="24" t="n"/>
+      <c r="BA135" s="24" t="n"/>
+      <c r="BB135" s="24" t="n"/>
+      <c r="BC135" s="24" t="n"/>
+      <c r="BD135" s="24" t="n"/>
+      <c r="BE135" s="24" t="n"/>
+      <c r="BF135" s="24" t="n"/>
+      <c r="BG135" s="24" t="n"/>
+      <c r="BH135" s="24" t="n"/>
+      <c r="BI135" s="24" t="n"/>
+      <c r="BJ135" s="25" t="n"/>
+      <c r="BK135" s="26" t="n"/>
+      <c r="BL135" s="27" t="n"/>
+      <c r="BM135" s="28" t="n"/>
+      <c r="BN135" s="28" t="n"/>
+      <c r="BO135" s="28" t="n"/>
+      <c r="BP135" s="25" t="n"/>
+      <c r="BQ135" s="27" t="n"/>
+      <c r="BR135" s="28" t="n"/>
+      <c r="BS135" s="28" t="n"/>
+      <c r="BT135" s="28" t="n"/>
+      <c r="BU135" s="25" t="n"/>
+      <c r="BV135" s="29" t="n"/>
+      <c r="BW135" s="24" t="n"/>
+      <c r="BX135" s="30" t="n"/>
+      <c r="BY135" s="27" t="n"/>
+      <c r="BZ135" s="24" t="n"/>
+      <c r="CA135" s="31" t="n"/>
+      <c r="CB135" s="24" t="n"/>
+      <c r="CC135" s="24" t="n"/>
+      <c r="CD135" s="24" t="n"/>
+      <c r="CE135" s="24" t="n"/>
+      <c r="CF135" s="24" t="n"/>
+      <c r="CG135" s="24" t="n"/>
+      <c r="CH135" s="24" t="n"/>
+      <c r="CI135" s="24" t="n"/>
+      <c r="CJ135" s="24" t="n"/>
+      <c r="CK135" s="24" t="n"/>
+      <c r="CL135" s="24" t="n"/>
+      <c r="CM135" s="24" t="n"/>
+      <c r="CN135" s="24" t="n"/>
+      <c r="CO135" s="24" t="n"/>
+      <c r="CP135" s="24" t="n"/>
+      <c r="CQ135" s="24" t="n"/>
+      <c r="CR135" s="24" t="n"/>
+      <c r="CS135" s="24" t="n"/>
+      <c r="CT135" s="24" t="n"/>
+      <c r="CU135" s="24" t="n"/>
+      <c r="CV135" s="24" t="n"/>
+      <c r="CW135" s="24" t="n"/>
+      <c r="CX135" s="24" t="n"/>
+      <c r="CY135" s="24" t="n"/>
+      <c r="CZ135" s="24" t="n"/>
+      <c r="DA135" s="24" t="n"/>
+      <c r="DB135" s="24" t="n"/>
+      <c r="DC135" s="24" t="n"/>
+      <c r="DD135" s="24" t="n"/>
+      <c r="DE135" s="24" t="n"/>
+      <c r="DF135" s="24" t="n"/>
+      <c r="DG135" s="24" t="n"/>
+      <c r="DH135" s="24" t="n"/>
+      <c r="DI135" s="24" t="n"/>
+      <c r="DJ135" s="24" t="n"/>
+      <c r="DK135" s="24" t="n"/>
+      <c r="DL135" s="24" t="n"/>
+      <c r="DM135" s="24" t="n"/>
+      <c r="DN135" s="24" t="n"/>
+      <c r="DO135" s="24" t="n"/>
+      <c r="DP135" s="24" t="n"/>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="24" t="inlineStr">
+        <is>
+          <t>2c8d598d287246b3</t>
+        </is>
+      </c>
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:17:52.157470Z</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T19:00Z</t>
+        </is>
+      </c>
+      <c r="D136" s="24" t="inlineStr">
+        <is>
+          <t>atc-epl-ips-liv-2026-09-04-ips</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F136" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="H136" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I136" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J136" s="25" t="n"/>
+      <c r="K136" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L136" s="26" t="n">
+        <v>525</v>
+      </c>
+      <c r="M136" s="27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N136" s="28" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O136" s="28" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="P136" s="28" t="n"/>
+      <c r="Q136" s="28" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="R136" s="26" t="n"/>
+      <c r="S136" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T136" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U136" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W136" s="26" t="n"/>
+      <c r="X136" s="26" t="n"/>
+      <c r="Y136" s="25" t="n"/>
+      <c r="Z136" s="26" t="n"/>
+      <c r="AA136" s="28" t="n"/>
+      <c r="AB136" s="28" t="n"/>
+      <c r="AC136" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="24" t="n"/>
+      <c r="AE136" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9G5E3E0GMVV on atc-epl-ips-liv-2026-09-04-ips (long)</t>
+        </is>
+      </c>
+      <c r="AF136" s="31" t="n"/>
+      <c r="AG136" s="24" t="n"/>
+      <c r="AH136" s="24" t="n"/>
+      <c r="AI136" s="31" t="n"/>
+      <c r="AJ136" s="31" t="n"/>
+      <c r="AK136" s="24" t="n"/>
+      <c r="AL136" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM136" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN136" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO136" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP136" s="24" t="n"/>
+      <c r="AQ136" s="24" t="n"/>
+      <c r="AR136" s="24" t="n"/>
+      <c r="AS136" s="24" t="n"/>
+      <c r="AT136" s="24" t="n"/>
+      <c r="AU136" s="24" t="n"/>
+      <c r="AV136" s="24" t="n"/>
+      <c r="AW136" s="24" t="n"/>
+      <c r="AX136" s="24" t="n"/>
+      <c r="AY136" s="24" t="n"/>
+      <c r="AZ136" s="24" t="n"/>
+      <c r="BA136" s="24" t="n"/>
+      <c r="BB136" s="24" t="n"/>
+      <c r="BC136" s="24" t="n"/>
+      <c r="BD136" s="24" t="n"/>
+      <c r="BE136" s="24" t="n"/>
+      <c r="BF136" s="24" t="n"/>
+      <c r="BG136" s="24" t="n"/>
+      <c r="BH136" s="24" t="n"/>
+      <c r="BI136" s="24" t="n"/>
+      <c r="BJ136" s="25" t="n"/>
+      <c r="BK136" s="26" t="n"/>
+      <c r="BL136" s="27" t="n"/>
+      <c r="BM136" s="28" t="n"/>
+      <c r="BN136" s="28" t="n"/>
+      <c r="BO136" s="28" t="n"/>
+      <c r="BP136" s="25" t="n"/>
+      <c r="BQ136" s="27" t="n"/>
+      <c r="BR136" s="28" t="n"/>
+      <c r="BS136" s="28" t="n"/>
+      <c r="BT136" s="28" t="n"/>
+      <c r="BU136" s="25" t="n"/>
+      <c r="BV136" s="29" t="n"/>
+      <c r="BW136" s="24" t="n"/>
+      <c r="BX136" s="30" t="n"/>
+      <c r="BY136" s="27" t="n"/>
+      <c r="BZ136" s="24" t="n"/>
+      <c r="CA136" s="31" t="n"/>
+      <c r="CB136" s="24" t="n"/>
+      <c r="CC136" s="24" t="n"/>
+      <c r="CD136" s="24" t="n"/>
+      <c r="CE136" s="24" t="n"/>
+      <c r="CF136" s="24" t="n"/>
+      <c r="CG136" s="24" t="n"/>
+      <c r="CH136" s="24" t="n"/>
+      <c r="CI136" s="24" t="n"/>
+      <c r="CJ136" s="24" t="n"/>
+      <c r="CK136" s="24" t="n"/>
+      <c r="CL136" s="24" t="n"/>
+      <c r="CM136" s="24" t="n"/>
+      <c r="CN136" s="24" t="n"/>
+      <c r="CO136" s="24" t="n"/>
+      <c r="CP136" s="24" t="n"/>
+      <c r="CQ136" s="24" t="n"/>
+      <c r="CR136" s="24" t="n"/>
+      <c r="CS136" s="24" t="n"/>
+      <c r="CT136" s="24" t="n"/>
+      <c r="CU136" s="24" t="n"/>
+      <c r="CV136" s="24" t="n"/>
+      <c r="CW136" s="24" t="n"/>
+      <c r="CX136" s="24" t="n"/>
+      <c r="CY136" s="24" t="n"/>
+      <c r="CZ136" s="24" t="n"/>
+      <c r="DA136" s="24" t="n"/>
+      <c r="DB136" s="24" t="n"/>
+      <c r="DC136" s="24" t="n"/>
+      <c r="DD136" s="24" t="n"/>
+      <c r="DE136" s="24" t="n"/>
+      <c r="DF136" s="24" t="n"/>
+      <c r="DG136" s="24" t="n"/>
+      <c r="DH136" s="24" t="n"/>
+      <c r="DI136" s="24" t="n"/>
+      <c r="DJ136" s="24" t="n"/>
+      <c r="DK136" s="24" t="n"/>
+      <c r="DL136" s="24" t="n"/>
+      <c r="DM136" s="24" t="n"/>
+      <c r="DN136" s="24" t="n"/>
+      <c r="DO136" s="24" t="n"/>
+      <c r="DP136" s="24" t="n"/>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="24" t="inlineStr">
+        <is>
+          <t>38dea559c2634cd8</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:17:52.157470Z</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T23:30Z</t>
+        </is>
+      </c>
+      <c r="D137" s="24" t="inlineStr">
+        <is>
+          <t>atc-brb-ath-vln-2026-09-04-ath</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="H137" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I137" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J137" s="25" t="n"/>
+      <c r="K137" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N137" s="28" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="O137" s="28" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="28" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="R137" s="26" t="n"/>
+      <c r="S137" s="29" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T137" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W137" s="26" t="n"/>
+      <c r="X137" s="26" t="n"/>
+      <c r="Y137" s="25" t="n"/>
+      <c r="Z137" s="26" t="n"/>
+      <c r="AA137" s="28" t="n"/>
+      <c r="AB137" s="28" t="n"/>
+      <c r="AC137" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="24" t="n"/>
+      <c r="AE137" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9G6FV07GMVG on atc-brb-ath-vln-2026-09-04-ath (long)</t>
+        </is>
+      </c>
+      <c r="AF137" s="31" t="n"/>
+      <c r="AG137" s="24" t="n"/>
+      <c r="AH137" s="24" t="n"/>
+      <c r="AI137" s="31" t="n"/>
+      <c r="AJ137" s="31" t="n"/>
+      <c r="AK137" s="24" t="n"/>
+      <c r="AL137" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM137" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN137" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO137" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP137" s="24" t="n"/>
+      <c r="AQ137" s="24" t="n"/>
+      <c r="AR137" s="24" t="n"/>
+      <c r="AS137" s="24" t="n"/>
+      <c r="AT137" s="24" t="n"/>
+      <c r="AU137" s="24" t="n"/>
+      <c r="AV137" s="24" t="n"/>
+      <c r="AW137" s="24" t="n"/>
+      <c r="AX137" s="24" t="n"/>
+      <c r="AY137" s="24" t="n"/>
+      <c r="AZ137" s="24" t="n"/>
+      <c r="BA137" s="24" t="n"/>
+      <c r="BB137" s="24" t="n"/>
+      <c r="BC137" s="24" t="n"/>
+      <c r="BD137" s="24" t="n"/>
+      <c r="BE137" s="24" t="n"/>
+      <c r="BF137" s="24" t="n"/>
+      <c r="BG137" s="24" t="n"/>
+      <c r="BH137" s="24" t="n"/>
+      <c r="BI137" s="24" t="n"/>
+      <c r="BJ137" s="25" t="n"/>
+      <c r="BK137" s="26" t="n"/>
+      <c r="BL137" s="27" t="n"/>
+      <c r="BM137" s="28" t="n"/>
+      <c r="BN137" s="28" t="n"/>
+      <c r="BO137" s="28" t="n"/>
+      <c r="BP137" s="25" t="n"/>
+      <c r="BQ137" s="27" t="n"/>
+      <c r="BR137" s="28" t="n"/>
+      <c r="BS137" s="28" t="n"/>
+      <c r="BT137" s="28" t="n"/>
+      <c r="BU137" s="25" t="n"/>
+      <c r="BV137" s="29" t="n"/>
+      <c r="BW137" s="24" t="n"/>
+      <c r="BX137" s="30" t="n"/>
+      <c r="BY137" s="27" t="n"/>
+      <c r="BZ137" s="24" t="n"/>
+      <c r="CA137" s="31" t="n"/>
+      <c r="CB137" s="24" t="n"/>
+      <c r="CC137" s="24" t="n"/>
+      <c r="CD137" s="24" t="n"/>
+      <c r="CE137" s="24" t="n"/>
+      <c r="CF137" s="24" t="n"/>
+      <c r="CG137" s="24" t="n"/>
+      <c r="CH137" s="24" t="n"/>
+      <c r="CI137" s="24" t="n"/>
+      <c r="CJ137" s="24" t="n"/>
+      <c r="CK137" s="24" t="n"/>
+      <c r="CL137" s="24" t="n"/>
+      <c r="CM137" s="24" t="n"/>
+      <c r="CN137" s="24" t="n"/>
+      <c r="CO137" s="24" t="n"/>
+      <c r="CP137" s="24" t="n"/>
+      <c r="CQ137" s="24" t="n"/>
+      <c r="CR137" s="24" t="n"/>
+      <c r="CS137" s="24" t="n"/>
+      <c r="CT137" s="24" t="n"/>
+      <c r="CU137" s="24" t="n"/>
+      <c r="CV137" s="24" t="n"/>
+      <c r="CW137" s="24" t="n"/>
+      <c r="CX137" s="24" t="n"/>
+      <c r="CY137" s="24" t="n"/>
+      <c r="CZ137" s="24" t="n"/>
+      <c r="DA137" s="24" t="n"/>
+      <c r="DB137" s="24" t="n"/>
+      <c r="DC137" s="24" t="n"/>
+      <c r="DD137" s="24" t="n"/>
+      <c r="DE137" s="24" t="n"/>
+      <c r="DF137" s="24" t="n"/>
+      <c r="DG137" s="24" t="n"/>
+      <c r="DH137" s="24" t="n"/>
+      <c r="DI137" s="24" t="n"/>
+      <c r="DJ137" s="24" t="n"/>
+      <c r="DK137" s="24" t="n"/>
+      <c r="DL137" s="24" t="n"/>
+      <c r="DM137" s="24" t="n"/>
+      <c r="DN137" s="24" t="n"/>
+      <c r="DO137" s="24" t="n"/>
+      <c r="DP137" s="24" t="n"/>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="24" t="inlineStr">
+        <is>
+          <t>9fd390111ad54428</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:17:52.157470Z</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:00Z</t>
+        </is>
+      </c>
+      <c r="D138" s="24" t="inlineStr">
+        <is>
+          <t>aec-atp-tometc-marnav-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>Mariano Navone</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>Tomas Martin Etcheverry</t>
+        </is>
+      </c>
+      <c r="H138" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I138" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J138" s="25" t="n"/>
+      <c r="K138" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M138" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N138" s="28" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="O138" s="28" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="28" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="R138" s="26" t="n"/>
+      <c r="S138" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U138" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="W138" s="26" t="n"/>
+      <c r="X138" s="26" t="n"/>
+      <c r="Y138" s="25" t="n"/>
+      <c r="Z138" s="26" t="n"/>
+      <c r="AA138" s="28" t="n"/>
+      <c r="AB138" s="28" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="24" t="n"/>
+      <c r="AE138" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order C9G5BCN52MVY on aec-atp-tometc-marnav-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF138" s="31" t="n"/>
+      <c r="AG138" s="24" t="n"/>
+      <c r="AH138" s="24" t="n"/>
+      <c r="AI138" s="31" t="n"/>
+      <c r="AJ138" s="31" t="n"/>
+      <c r="AK138" s="24" t="n"/>
+      <c r="AL138" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM138" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN138" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO138" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP138" s="24" t="n"/>
+      <c r="AQ138" s="24" t="n"/>
+      <c r="AR138" s="24" t="n"/>
+      <c r="AS138" s="24" t="n"/>
+      <c r="AT138" s="24" t="n"/>
+      <c r="AU138" s="24" t="n"/>
+      <c r="AV138" s="24" t="n"/>
+      <c r="AW138" s="24" t="n"/>
+      <c r="AX138" s="24" t="n"/>
+      <c r="AY138" s="24" t="n"/>
+      <c r="AZ138" s="24" t="n"/>
+      <c r="BA138" s="24" t="n"/>
+      <c r="BB138" s="24" t="n"/>
+      <c r="BC138" s="24" t="n"/>
+      <c r="BD138" s="24" t="n"/>
+      <c r="BE138" s="24" t="n"/>
+      <c r="BF138" s="24" t="n"/>
+      <c r="BG138" s="24" t="n"/>
+      <c r="BH138" s="24" t="n"/>
+      <c r="BI138" s="24" t="n"/>
+      <c r="BJ138" s="25" t="n"/>
+      <c r="BK138" s="26" t="n"/>
+      <c r="BL138" s="27" t="n"/>
+      <c r="BM138" s="28" t="n"/>
+      <c r="BN138" s="28" t="n"/>
+      <c r="BO138" s="28" t="n"/>
+      <c r="BP138" s="25" t="n"/>
+      <c r="BQ138" s="27" t="n"/>
+      <c r="BR138" s="28" t="n"/>
+      <c r="BS138" s="28" t="n"/>
+      <c r="BT138" s="28" t="n"/>
+      <c r="BU138" s="25" t="n"/>
+      <c r="BV138" s="29" t="n"/>
+      <c r="BW138" s="24" t="n"/>
+      <c r="BX138" s="30" t="n"/>
+      <c r="BY138" s="27" t="n"/>
+      <c r="BZ138" s="24" t="n"/>
+      <c r="CA138" s="31" t="n"/>
+      <c r="CB138" s="24" t="n"/>
+      <c r="CC138" s="24" t="n"/>
+      <c r="CD138" s="24" t="n"/>
+      <c r="CE138" s="24" t="n"/>
+      <c r="CF138" s="24" t="n"/>
+      <c r="CG138" s="24" t="n"/>
+      <c r="CH138" s="24" t="n"/>
+      <c r="CI138" s="24" t="n"/>
+      <c r="CJ138" s="24" t="n"/>
+      <c r="CK138" s="24" t="n"/>
+      <c r="CL138" s="24" t="n"/>
+      <c r="CM138" s="24" t="n"/>
+      <c r="CN138" s="24" t="n"/>
+      <c r="CO138" s="24" t="n"/>
+      <c r="CP138" s="24" t="n"/>
+      <c r="CQ138" s="24" t="n"/>
+      <c r="CR138" s="24" t="n"/>
+      <c r="CS138" s="24" t="n"/>
+      <c r="CT138" s="24" t="n"/>
+      <c r="CU138" s="24" t="n"/>
+      <c r="CV138" s="24" t="n"/>
+      <c r="CW138" s="24" t="n"/>
+      <c r="CX138" s="24" t="n"/>
+      <c r="CY138" s="24" t="n"/>
+      <c r="CZ138" s="24" t="n"/>
+      <c r="DA138" s="24" t="n"/>
+      <c r="DB138" s="24" t="n"/>
+      <c r="DC138" s="24" t="n"/>
+      <c r="DD138" s="24" t="n"/>
+      <c r="DE138" s="24" t="n"/>
+      <c r="DF138" s="24" t="n"/>
+      <c r="DG138" s="24" t="n"/>
+      <c r="DH138" s="24" t="n"/>
+      <c r="DI138" s="24" t="n"/>
+      <c r="DJ138" s="24" t="n"/>
+      <c r="DK138" s="24" t="n"/>
+      <c r="DL138" s="24" t="n"/>
+      <c r="DM138" s="24" t="n"/>
+      <c r="DN138" s="24" t="n"/>
+      <c r="DO138" s="24" t="n"/>
+      <c r="DP138" s="24" t="n"/>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
+        <is>
+          <t>PICK_HEALTHY</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T07:26:04.323753Z</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-04T19:26:04.323677Z</t>
+        </is>
+      </c>
+      <c r="D139" s="24" t="inlineStr">
+        <is>
+          <t>aec-cs2-alpha-beta-2026-09-04</t>
+        </is>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="H139" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I139" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J139" s="25" t="n"/>
+      <c r="K139" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L139" s="26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M139" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O139" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="R139" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" s="24" t="n"/>
+      <c r="U139" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="n"/>
+      <c r="W139" s="26" t="n"/>
+      <c r="X139" s="26" t="n"/>
+      <c r="Y139" s="25" t="n"/>
+      <c r="Z139" s="26" t="n"/>
+      <c r="AA139" s="28" t="n"/>
+      <c r="AB139" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="24" t="n"/>
+      <c r="AE139" s="31" t="inlineStr">
+        <is>
+          <t>Auto-Buyer order primary-healthy (0.0 sh @ $0.50) on aec-cs2-alpha-beta-2026-09-04 (long)</t>
+        </is>
+      </c>
+      <c r="AF139" s="31" t="inlineStr">
+        <is>
+          <t>Auto-executed Polymarket US order</t>
+        </is>
+      </c>
+      <c r="AG139" s="24" t="n"/>
+      <c r="AH139" s="24" t="n"/>
+      <c r="AI139" s="31" t="n"/>
+      <c r="AJ139" s="31" t="n"/>
+      <c r="AK139" s="24" t="n"/>
+      <c r="AL139" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM139" s="24" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="AN139" s="24" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="AO139" s="24" t="inlineStr">
+        <is>
+          <t>AUTO_BUYER_EXECUTION</t>
+        </is>
+      </c>
+      <c r="AP139" s="24" t="n"/>
+      <c r="AQ139" s="24" t="n"/>
+      <c r="AR139" s="24" t="n"/>
+      <c r="AS139" s="24" t="n"/>
+      <c r="AT139" s="24" t="n"/>
+      <c r="AU139" s="24" t="n"/>
+      <c r="AV139" s="24" t="n"/>
+      <c r="AW139" s="24" t="n"/>
+      <c r="AX139" s="24" t="n"/>
+      <c r="AY139" s="24" t="n"/>
+      <c r="AZ139" s="24" t="n"/>
+      <c r="BA139" s="24" t="n"/>
+      <c r="BB139" s="24" t="n"/>
+      <c r="BC139" s="24" t="n"/>
+      <c r="BD139" s="24" t="n"/>
+      <c r="BE139" s="24" t="n"/>
+      <c r="BF139" s="24" t="n"/>
+      <c r="BG139" s="24" t="n"/>
+      <c r="BH139" s="24" t="n"/>
+      <c r="BI139" s="24" t="n"/>
+      <c r="BJ139" s="25" t="n"/>
+      <c r="BK139" s="26" t="n"/>
+      <c r="BL139" s="27" t="n"/>
+      <c r="BM139" s="28" t="n"/>
+      <c r="BN139" s="28" t="n"/>
+      <c r="BO139" s="28" t="n"/>
+      <c r="BP139" s="25" t="n"/>
+      <c r="BQ139" s="27" t="n"/>
+      <c r="BR139" s="28" t="n"/>
+      <c r="BS139" s="28" t="n"/>
+      <c r="BT139" s="28" t="n"/>
+      <c r="BU139" s="25" t="n"/>
+      <c r="BV139" s="29" t="n"/>
+      <c r="BW139" s="24" t="n"/>
+      <c r="BX139" s="30" t="n"/>
+      <c r="BY139" s="27" t="n"/>
+      <c r="BZ139" s="24" t="n"/>
+      <c r="CA139" s="31" t="n"/>
+      <c r="CB139" s="24" t="n"/>
+      <c r="CC139" s="24" t="n"/>
+      <c r="CD139" s="24" t="n"/>
+      <c r="CE139" s="24" t="n"/>
+      <c r="CF139" s="24" t="n"/>
+      <c r="CG139" s="24" t="n"/>
+      <c r="CH139" s="24" t="n"/>
+      <c r="CI139" s="24" t="n"/>
+      <c r="CJ139" s="24" t="n"/>
+      <c r="CK139" s="24" t="n"/>
+      <c r="CL139" s="24" t="n"/>
+      <c r="CM139" s="24" t="n"/>
+      <c r="CN139" s="24" t="n"/>
+      <c r="CO139" s="24" t="n"/>
+      <c r="CP139" s="24" t="n"/>
+      <c r="CQ139" s="24" t="n"/>
+      <c r="CR139" s="24" t="n"/>
+      <c r="CS139" s="24" t="n"/>
+      <c r="CT139" s="24" t="n"/>
+      <c r="CU139" s="24" t="n"/>
+      <c r="CV139" s="24" t="n"/>
+      <c r="CW139" s="24" t="n"/>
+      <c r="CX139" s="24" t="n"/>
+      <c r="CY139" s="24" t="n"/>
+      <c r="CZ139" s="24" t="n"/>
+      <c r="DA139" s="24" t="n"/>
+      <c r="DB139" s="24" t="n"/>
+      <c r="DC139" s="24" t="n"/>
+      <c r="DD139" s="24" t="n"/>
+      <c r="DE139" s="24" t="n"/>
+      <c r="DF139" s="24" t="n"/>
+      <c r="DG139" s="24" t="n"/>
+      <c r="DH139" s="24" t="n"/>
+      <c r="DI139" s="24" t="n"/>
+      <c r="DJ139" s="24" t="n"/>
+      <c r="DK139" s="24" t="n"/>
+      <c r="DL139" s="24" t="n"/>
+      <c r="DM139" s="24" t="n"/>
+      <c r="DN139" s="24" t="n"/>
+      <c r="DO139" s="24" t="n"/>
+      <c r="DP139" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
